--- a/Astra Notes.xlsx
+++ b/Astra Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gwen\Documents\GitHub\Factorio-Astra-Asteroids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1B01BB-EB90-4DD7-A8A0-F9DD222D0B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78940830-3E3A-4EFE-B800-33687F1C58A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15165" yWindow="0" windowWidth="23235" windowHeight="21000" activeTab="3" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
+    <workbookView xWindow="13335" yWindow="510" windowWidth="24870" windowHeight="18090" activeTab="2" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="206">
   <si>
     <t>Metallic</t>
   </si>
@@ -685,7 +685,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,10 +784,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="66">
     <dxf>
       <fill>
         <patternFill patternType="lightDown">
@@ -796,6 +793,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="lightDown">
+          <fgColor rgb="FFFF99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i/>
@@ -813,9 +817,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -995,6 +996,12 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1010,50 +1017,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="63">
   <autoFilter ref="B3:AB25" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{B1A354A2-D591-4F7C-89E1-AB75527E5993}" name="Recipe"/>
-    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="63">
+    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="62">
       <calculatedColumnFormula>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="56">
+    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="55">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(J$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="55">
+    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="54">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(K$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="52">
+    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="51">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(N$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="51"/>
-    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="49"/>
-    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="45"/>
-    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="42"/>
-    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="41"/>
-    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="39"/>
-    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="38"/>
+    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="50"/>
+    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="48"/>
+    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="47"/>
+    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="46"/>
+    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="45"/>
+    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="44"/>
+    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="40"/>
+    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="39"/>
+    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1067,16 +1074,16 @@
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{EFD8865D-C9ED-4BA8-B73C-113EDAD68DA5}" name="chunk item"/>
-    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="37">
+    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="36">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{1A67492A-77CF-48AB-9609-594DA5CCF328}" name="name"/>
-    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="36">
+    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="35">
       <calculatedColumnFormula>"""space-material"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{A45CDEC7-39DE-4333-8E31-011D04DA2762}" name="order"/>
     <tableColumn id="6" xr3:uid="{499C643B-C1ED-4A32-BE42-9946CC52BC6E}" name="icon"/>
-    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="35">
+    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="34">
       <calculatedColumnFormula>1</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1092,11 +1099,11 @@
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9C8B2B85-651A-48F5-BE74-6B0CB5EC6401}" name="chunk"/>
-    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="34">
+    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="33">
       <calculatedColumnFormula>"""asteroid-chunk"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{5CB5E631-FE01-4CDD-A4B3-008A4C86A223}" name="name "/>
-    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable " dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable " dataDxfId="32"/>
     <tableColumn id="5" xr3:uid="{2D398BB0-41AE-40CE-AA0F-6FA6647FFA57}" name="order "/>
     <tableColumn id="6" xr3:uid="{82F86FA9-1FFF-4AFF-A528-DD559BDA3930}" name="icon "/>
   </tableColumns>
@@ -1105,41 +1112,41 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="B4:AG17" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="B4:AG17" totalsRowShown="0" headerRowDxfId="31">
   <autoFilter ref="B4:AG17" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{1C7B22C3-8503-40CA-B985-0F11F98EB3C6}" name="Recipe"/>
-    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="25"/>
-    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="24"/>
-    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="23"/>
-    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="22"/>
-    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="21"/>
-    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="20"/>
-    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="19"/>
-    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="18"/>
-    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="17"/>
-    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="16"/>
-    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="15"/>
-    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="11"/>
-    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="26"/>
+    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="21"/>
+    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="20"/>
+    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="19"/>
+    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="18"/>
+    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="17"/>
+    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="16"/>
+    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="15"/>
+    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="14"/>
+    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1"/>
     <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2"/>
     <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3"/>
     <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4"/>
-    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="5">
+    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="4">
       <calculatedColumnFormula array="1" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -1156,11 +1163,11 @@
   <autoFilter ref="H5:K15" xr:uid="{8FC02366-D4DD-41A4-8050-773DDA42B27E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{959EF51D-F84A-47B3-BB90-19C907903580}" name="name"/>
-    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="4">
+    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="65">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{214E8F8E-48B4-4BB8-B3A1-54F2A217D484}" name="amount"/>
-    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="64">
       <calculatedColumnFormula array="1">"    { " &amp; _xlfn.TEXTJOIN(", ", TRUE, Table1[[#Headers],[name]:[amount]] &amp; " = " &amp; Table1[[#This Row],[name]:[amount]]) &amp; " }"</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1487,21 +1494,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1887466F-79F7-46EC-9385-969031045057}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B3:AI41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="2" customWidth="1"/>
-    <col min="4" max="10" width="10.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="2" customWidth="1"/>
+    <col min="4" max="10" width="10.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="35.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="40.140625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="50.42578125" style="2" customWidth="1"/>
-    <col min="15" max="17" width="43.85546875" style="2" customWidth="1"/>
-    <col min="18" max="28" width="10.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="35.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="40.125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="50.375" style="2" customWidth="1"/>
+    <col min="15" max="17" width="43.875" style="2" customWidth="1"/>
+    <col min="18" max="28" width="10.375" style="2" customWidth="1"/>
     <col min="32" max="32" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:28" s="3" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:28" s="3" customFormat="1" ht="71.25" customHeight="1">
       <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
@@ -1584,7 +1591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:28">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1642,7 @@
       <c r="AA4" s="8"/>
       <c r="AB4" s="8"/>
     </row>
-    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:28">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -1686,7 +1693,7 @@
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:28">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -1737,7 +1744,7 @@
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
     </row>
-    <row r="7" spans="2:28" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:28" ht="27.75" customHeight="1">
       <c r="B7" t="s">
         <v>77</v>
       </c>
@@ -1896,7 +1903,7 @@
         <v xml:space="preserve"> - </v>
       </c>
     </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:28">
       <c r="B8" t="s">
         <v>62</v>
       </c>
@@ -1947,7 +1954,7 @@
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
     </row>
-    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:28">
       <c r="B9" t="s">
         <v>3</v>
       </c>
@@ -2000,7 +2007,7 @@
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
     </row>
-    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:28">
       <c r="B10" t="s">
         <v>4</v>
       </c>
@@ -2051,7 +2058,7 @@
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
     </row>
-    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:28">
       <c r="B11" t="s">
         <v>5</v>
       </c>
@@ -2110,7 +2117,7 @@
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
     </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:28">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -2165,7 +2172,7 @@
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
     </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:28">
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -2216,7 +2223,7 @@
       </c>
       <c r="AB13" s="8"/>
     </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:28">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -2269,7 +2276,7 @@
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
     </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:28">
       <c r="B15" t="s">
         <v>15</v>
       </c>
@@ -2322,7 +2329,7 @@
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
     </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:28">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -2375,7 +2382,7 @@
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35">
       <c r="B17" t="s">
         <v>69</v>
       </c>
@@ -2532,7 +2539,7 @@
         <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8 }</v>
       </c>
     </row>
-    <row r="18" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35">
       <c r="B18" t="s">
         <v>20</v>
       </c>
@@ -2581,7 +2588,7 @@
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:35">
       <c r="B19" t="s">
         <v>21</v>
       </c>
@@ -2638,7 +2645,7 @@
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
     </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:35">
       <c r="B20" t="s">
         <v>22</v>
       </c>
@@ -2693,7 +2700,7 @@
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
     </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:35">
       <c r="B21" t="s">
         <v>24</v>
       </c>
@@ -2746,7 +2753,7 @@
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
     </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:35">
       <c r="B22" t="s">
         <v>25</v>
       </c>
@@ -2799,7 +2806,7 @@
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
     </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:35">
       <c r="B23" t="s">
         <v>26</v>
       </c>
@@ -2853,7 +2860,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:35">
       <c r="B24" t="s">
         <v>27</v>
       </c>
@@ -2905,7 +2912,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:35">
       <c r="B25" t="s">
         <v>28</v>
       </c>
@@ -2957,12 +2964,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:35">
       <c r="AE26">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:35">
       <c r="L28" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(L7, "}", ","), "amount_max = "), ",", , , , 0)</f>
         <v xml:space="preserve">15  </v>
@@ -2971,43 +2978,43 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:35">
       <c r="L29" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(L7, "}", ","), "amount_min = "), ",", , , , 0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:35">
       <c r="L30" s="2" t="e">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(L7, "}", ","), "amount = "), ",", , , , 0)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:35">
       <c r="L31" s="2" t="e">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(L7, "}", ","), "probability = "), ",", , , , 0)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="14:14">
       <c r="N38" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "amount_max = "), ",", , , , 0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="14:14">
       <c r="N39" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "amount_min = "), ",", , , , 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="14:14">
       <c r="N40" s="2" t="e">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "amount = "), ",", , , , 0)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="14:14">
       <c r="N41" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "probability = "), ",", , , , 0)</f>
         <v>0.25</v>
@@ -3031,27 +3038,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04493FD2-BC79-4DE4-945B-7AF801A57BBD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B1:O19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="3" max="3" width="13.375" customWidth="1"/>
     <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="54.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.75" customWidth="1"/>
+    <col min="11" max="11" width="16.625" customWidth="1"/>
     <col min="12" max="12" width="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="52.5703125" customWidth="1"/>
+    <col min="13" max="13" width="52.625" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="54.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" ht="15">
       <c r="B1" s="5"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15">
       <c r="B3" t="s">
         <v>35</v>
       </c>
@@ -3092,7 +3099,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15">
       <c r="B4" t="s">
         <v>40</v>
       </c>
@@ -3137,7 +3144,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15">
       <c r="B5" t="s">
         <v>50</v>
       </c>
@@ -3182,7 +3189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15">
       <c r="B6" t="s">
         <v>36</v>
       </c>
@@ -3227,7 +3234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15">
       <c r="B7" t="s">
         <v>129</v>
       </c>
@@ -3272,19 +3279,19 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" ht="15">
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" ht="15">
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="12:12" ht="15">
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="12:12" ht="15">
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="12:12" ht="15">
       <c r="L19" s="6"/>
     </row>
   </sheetData>
@@ -3300,36 +3307,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA672A5-FC41-4490-AF8C-1F6ADD4F213B}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:AJ49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="66.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.140625" style="2" customWidth="1"/>
-    <col min="9" max="12" width="35.140625" style="2" customWidth="1"/>
-    <col min="13" max="28" width="9.42578125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="82.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="62.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="62.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="118.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.75" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="66.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.125" style="2" customWidth="1"/>
+    <col min="9" max="12" width="35.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.125" style="2" customWidth="1"/>
+    <col min="15" max="28" width="9.375" style="2" customWidth="1"/>
+    <col min="29" max="29" width="64.625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="82.375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="62.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="62.75" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="118.875" customWidth="1"/>
     <col min="36" max="36" width="64" customWidth="1"/>
     <col min="37" max="37" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:36">
       <c r="I2" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:36">
       <c r="F3" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:36" s="1" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:36" s="1" customFormat="1" ht="52.5" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
@@ -3427,7 +3436,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:36">
       <c r="B5" t="s">
         <v>62</v>
       </c>
@@ -3475,7 +3484,7 @@
         <v>{ { type = "item", name = "nauvis_asteroid_chunk_item", amount = 1 } }</v>
       </c>
     </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:36">
       <c r="B6" t="s">
         <v>69</v>
       </c>
@@ -3518,7 +3527,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:36">
       <c r="B7" t="s">
         <v>77</v>
       </c>
@@ -3555,7 +3564,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:36">
       <c r="B8" t="s">
         <v>78</v>
       </c>
@@ -3568,6 +3577,9 @@
       <c r="E8" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="G8" s="2" t="s">
         <v>60</v>
       </c>
@@ -3577,22 +3589,31 @@
       <c r="I8" s="2" t="s">
         <v>90</v>
       </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="AC8" t="s">
         <v>93</v>
       </c>
       <c r="AD8" t="s">
         <v>94</v>
       </c>
-      <c r="AG8" t="e" cm="1">
+      <c r="AG8" t="str" cm="1">
         <f t="array" ref="AG8" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.25">
+        <v>{ { type = "item", name = "vulcanic_asteroid_chunk_item", amount = 1 } }</v>
+      </c>
+    </row>
+    <row r="9" spans="2:36">
       <c r="B9" t="s">
         <v>79</v>
       </c>
@@ -3626,7 +3647,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:36">
       <c r="B10" t="s">
         <v>80</v>
       </c>
@@ -3669,7 +3690,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:36">
       <c r="B11" t="s">
         <v>103</v>
       </c>
@@ -3706,7 +3727,7 @@
         <v>{ { type = "item", name = "vulcanic_asteroid_chunk_item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:36">
       <c r="B12" t="s">
         <v>153</v>
       </c>
@@ -3737,7 +3758,7 @@
         <v>{ { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:36">
       <c r="B13" t="s">
         <v>152</v>
       </c>
@@ -3768,7 +3789,7 @@
         <v>{ { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:36">
       <c r="B14" t="s">
         <v>154</v>
       </c>
@@ -3823,7 +3844,7 @@
         <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:36">
       <c r="B15" t="s">
         <v>155</v>
       </c>
@@ -3890,7 +3911,7 @@
         <v>{ { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:36">
       <c r="B16" t="s">
         <v>156</v>
       </c>
@@ -3921,7 +3942,7 @@
         <v>{ { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:33">
       <c r="B17" t="s">
         <v>157</v>
       </c>
@@ -3952,82 +3973,82 @@
         <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
       </c>
     </row>
-    <row r="34" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="30:30">
       <c r="AD34" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="30:30">
       <c r="AD35" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="30:30">
       <c r="AD36" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="30:30">
       <c r="AD37" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="30:30">
       <c r="AD38" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="30:30">
       <c r="AD39" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="30:30">
       <c r="AD40" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="30:30">
       <c r="AD41" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="30:30">
       <c r="AD42" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="43" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="30:30">
       <c r="AD43" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="30:30">
       <c r="AD44" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="30:30">
       <c r="AD45" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="30:30">
       <c r="AD46" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="47" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="30:30">
       <c r="AD47" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="30:30">
       <c r="AD48" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="30:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="30:30">
       <c r="AD49" t="s">
         <v>146</v>
       </c>
@@ -4042,8 +4063,8 @@
       <formula>LEN($C5) &gt; 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:AG14">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:AG8">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4057,17 +4078,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A8318C-CA68-4EB8-AA36-1FC23F5E77D3}">
   <dimension ref="B2:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.125" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11">
       <c r="K2" t="str">
         <f>"{ 
 " &amp;
@@ -4089,7 +4110,7 @@
 }</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="15">
       <c r="B5" s="10"/>
       <c r="C5" s="11" t="s">
         <v>194</v>
@@ -4109,7 +4130,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" ht="15">
       <c r="B6" s="10"/>
       <c r="C6" s="11" t="s">
         <v>175</v>
@@ -4135,7 +4156,7 @@
         <v xml:space="preserve">    { name = "space-platform-foundation", type = "item", amount = 500 }</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="15">
       <c r="B7" s="10"/>
       <c r="C7" s="11" t="s">
         <v>178</v>
@@ -4161,7 +4182,7 @@
         <v xml:space="preserve">    { name = "solar-panel", type = "item", amount = 20 }</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" ht="15">
       <c r="B8" s="10"/>
       <c r="C8" s="11" t="s">
         <v>180</v>
@@ -4187,7 +4208,7 @@
         <v xml:space="preserve">    { name = "astra-simple-crusher", type = "item", amount = 4 }</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" ht="15">
       <c r="B9" s="10"/>
       <c r="C9" s="11" t="s">
         <v>182</v>
@@ -4213,7 +4234,7 @@
         <v xml:space="preserve">    { name = "astra-simple-asteroid-collector", type = "item", amount = 6 }</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" ht="15">
       <c r="B10" s="10"/>
       <c r="C10" s="11" t="s">
         <v>184</v>
@@ -4239,7 +4260,7 @@
         <v xml:space="preserve">    { name = "inserter", type = "item", amount = 6 }</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" ht="15">
       <c r="B11" s="10"/>
       <c r="C11" s="11" t="s">
         <v>185</v>
@@ -4265,7 +4286,7 @@
         <v xml:space="preserve">    { name = "electric-furnace", type = "item", amount = 8 }</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" ht="15">
       <c r="B12" s="10"/>
       <c r="C12" s="11" t="s">
         <v>187</v>
@@ -4291,7 +4312,7 @@
         <v xml:space="preserve">    { name = "assembling-machine-1", type = "item", amount = 2 }</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" ht="15">
       <c r="B13" s="10"/>
       <c r="C13" s="11" t="s">
         <v>189</v>
@@ -4317,7 +4338,7 @@
         <v xml:space="preserve">    { name = "iron-plate", type = "item", amount = 50 }</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" ht="15">
       <c r="B14" s="10"/>
       <c r="C14" s="11" t="s">
         <v>191</v>
@@ -4343,7 +4364,7 @@
         <v xml:space="preserve">    { name = "efficiency-module-2", type = "item", amount = 6 }</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" ht="15">
       <c r="B15" s="10"/>
       <c r="C15" s="11" t="s">
         <v>192</v>
@@ -4369,7 +4390,7 @@
         <v xml:space="preserve">    { name = "transport-belt", type = "item", amount = 40 }</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" ht="15">
       <c r="B16" s="10"/>
       <c r="C16" s="11" t="s">
         <v>173</v>
@@ -4377,19 +4398,19 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5">
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5">
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>

--- a/Astra Notes.xlsx
+++ b/Astra Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gwen\Documents\GitHub\Factorio-Astra-Asteroids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78940830-3E3A-4EFE-B800-33687F1C58A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90A9371-19CA-4D14-8C46-DEFD66685BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13335" yWindow="510" windowWidth="24870" windowHeight="18090" activeTab="2" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
+    <workbookView xWindow="4320" yWindow="240" windowWidth="33195" windowHeight="18090" activeTab="1" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="Recipies" sheetId="3" r:id="rId3"/>
     <sheet name="ItemListGen" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="advRecipeCopy">Recipies!$G$5</definedName>
+    <definedName name="baseRecipeCopy">Recipies!$G$4</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,8 +44,9 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -52,16 +57,40 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="2">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="2">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="257">
   <si>
     <t>Metallic</t>
   </si>
@@ -168,54 +197,9 @@
     <t>stack_size</t>
   </si>
   <si>
-    <t>chunk item</t>
-  </si>
-  <si>
-    <t>Sunrise Sasparillaroid</t>
-  </si>
-  <si>
-    <t>"Sunrise_Sasparillaroid_Chunk_Item"</t>
-  </si>
-  <si>
-    <t>"s"</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/nauvis-asteroid-chunk.png"</t>
-  </si>
-  <si>
-    <t>Crude Asteroid</t>
-  </si>
-  <si>
-    <t>"crude_asteroid_chunk_item"</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/crude-asteroid-chunk.png"</t>
-  </si>
-  <si>
     <t>"f"</t>
   </si>
   <si>
-    <t xml:space="preserve">name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">minable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">order </t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon </t>
-  </si>
-  <si>
-    <t>chunk</t>
-  </si>
-  <si>
-    <t>"nauvis_asteroid_chunk"</t>
-  </si>
-  <si>
-    <t>Nauvis Asteroid</t>
-  </si>
-  <si>
     <t>"n"</t>
   </si>
   <si>
@@ -225,24 +209,9 @@
     <t>{mining_time = 0.2, result = "crude_asteroid_chunk_item"}</t>
   </si>
   <si>
-    <t>"Sunrise_Sasparillaroid_Chunk"</t>
-  </si>
-  <si>
-    <t>"crude_asteroid_chunk"</t>
-  </si>
-  <si>
-    <t>"nauvis_asteroid_chunk_item"</t>
-  </si>
-  <si>
     <t>enabled</t>
   </si>
   <si>
-    <t>"nauvis_asteroid_chunk_crushing"</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/nauvis-asteroid-chunk-crushing.png"</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
@@ -267,33 +236,15 @@
     <t>Results 4</t>
   </si>
   <si>
-    <t>{ type = "item", name = "stone", amount_min = 5, amount_max = 10 }</t>
-  </si>
-  <si>
     <t>Adv Nauvis Crushing</t>
   </si>
   <si>
-    <t>"nauvis_asteroid_chunk_crushing_adv"</t>
-  </si>
-  <si>
     <t>{ type = "item", name = "stone", amount_min = 4, amount_max = 8 }</t>
   </si>
   <si>
     <t>{ type = "item", name = "uranium-ore", amount_min = 0, amount_max = 4, probability = 0.25}</t>
   </si>
   <si>
-    <t>"crude_asteroid_chunk_crushing"</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/crude-asteroid-chunk-crushing.png"</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15 }</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "coal", amount_min = 5, amount_max = 15  }</t>
-  </si>
-  <si>
     <t>Crude Asteroid Crushing</t>
   </si>
   <si>
@@ -306,84 +257,30 @@
     <t>Basic Gleba Crushing</t>
   </si>
   <si>
-    <t>"vulcanus_asteroid_chunk_crushing"</t>
-  </si>
-  <si>
-    <t>"fulgoran_asteroid_chunk_crushing"</t>
-  </si>
-  <si>
-    <t>"gleba_asteroid_chunk_crushing"</t>
-  </si>
-  <si>
     <t>Unwritten?</t>
   </si>
   <si>
-    <t>"__Astra-Asteroids__/graphics/vulcanic-asteroid-chunk-crushing.png"</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/fulgoran-asteroid-chunk-crushing.png"</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/gleba-asteroid-chunk-crushing.png"</t>
-  </si>
-  <si>
     <t>nauvis_asteroid_chunk_item</t>
   </si>
   <si>
     <t>crude_asteroid_chunk_item</t>
   </si>
   <si>
-    <t>vulcanic_asteroid_chunk_item</t>
-  </si>
-  <si>
-    <t>fulgoran_asteroid_chunk_item</t>
-  </si>
-  <si>
     <t>gleba_asteroid_chunk_item</t>
   </si>
   <si>
-    <t>{ type = "item", name = "stone", amount_min = 4, amount_max = 6 }</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "tungsten-ore", amount_min = 2, amount_max = 5, probability = 0.5}</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "scrap", amount_min = 2, amount_max = 8 }</t>
-  </si>
-  <si>
     <t>energy_required</t>
   </si>
   <si>
-    <t>{ type = "item", name = "stone", amount_min = 3, amount_max = 5 }</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "yumako-seed", amount = 1, probability = 0.05}</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "jellynut-seed", amount = 1, probability = 0.05}</t>
-  </si>
-  <si>
-    <t>{ type = "item", name = "spoilage",  amount_min = 0, amount_max = 4 }</t>
-  </si>
-  <si>
     <t>Ingredient 1</t>
   </si>
   <si>
     <t>Ingredient 2</t>
   </si>
   <si>
-    <t>Special Vulcanic Crushing</t>
-  </si>
-  <si>
-    <t>"vulcanus_special_crushing"</t>
-  </si>
-  <si>
     <t>metallic-astroid-chunk</t>
   </si>
   <si>
-    <t>{mining_time = 0.2, result = "Sunrise_Sasparillaroid_Chunk_Item"}</t>
-  </si>
-  <si>
     <t>Ingredient String</t>
   </si>
   <si>
@@ -450,18 +347,6 @@
     <t>solid-fuel</t>
   </si>
   <si>
-    <t>Volcanic Asteroid</t>
-  </si>
-  <si>
-    <t>"__Astra-Asteroids__/graphics/volcanic-asteroid-chunk.png"</t>
-  </si>
-  <si>
-    <t>"volcanic_asteroid_chunk"</t>
-  </si>
-  <si>
-    <t>"volcanic_asteroid_chunk_item"</t>
-  </si>
-  <si>
     <t>{mining_time = 0.2, result = "volcanic_asteroid_chunk_item"}</t>
   </si>
   <si>
@@ -516,9 +401,6 @@
     <t>Result_4_name</t>
   </si>
   <si>
-    <t>uranium_ore</t>
-  </si>
-  <si>
     <t>Carbonic asteroid crushing</t>
   </si>
   <si>
@@ -679,13 +561,751 @@
   </si>
   <si>
     <t>line items</t>
+  </si>
+  <si>
+    <t>Result_1_type</t>
+  </si>
+  <si>
+    <t>Result_2_type</t>
+  </si>
+  <si>
+    <t>Result_3_type</t>
+  </si>
+  <si>
+    <t>Result_4_type</t>
+  </si>
+  <si>
+    <t>fluid</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>Adv Vulcanis Crushing</t>
+  </si>
+  <si>
+    <t>Adv Gleba Crushing</t>
+  </si>
+  <si>
+    <t>Adv Fulgoran Crushing</t>
+  </si>
+  <si>
+    <t>1Special Nauvis Crushing</t>
+  </si>
+  <si>
+    <t>1Special Fulgoran Crushing</t>
+  </si>
+  <si>
+    <t>1Special Gleba Crushing</t>
+  </si>
+  <si>
+    <t>1Special Vulcanic Crushing</t>
+  </si>
+  <si>
+    <t>holmium-ore</t>
+  </si>
+  <si>
+    <t>heavy-oil</t>
+  </si>
+  <si>
+    <t>holmium-solution</t>
+  </si>
+  <si>
+    <t>"crude-asteroid-chunk-crushing"</t>
+  </si>
+  <si>
+    <t>"vulcanus-asteroid-chunk-crushing"</t>
+  </si>
+  <si>
+    <t>"nauvis-asteroid-chunk-crushing"</t>
+  </si>
+  <si>
+    <t>"gleba-asteroid-chunk-crushing"</t>
+  </si>
+  <si>
+    <t>"fulgoran-asteroid-chunk-crushing"</t>
+  </si>
+  <si>
+    <t>"nauvis-asteroid-chunk-crushing-adv"</t>
+  </si>
+  <si>
+    <t>"gleba-asteroid-chunk-crushing-adv"</t>
+  </si>
+  <si>
+    <t>"vulcanus-special-crushing"</t>
+  </si>
+  <si>
+    <t>"vulcanis-asteroid-chunk-crushing-adv"</t>
+  </si>
+  <si>
+    <t>"nauvis-special-crushing"</t>
+  </si>
+  <si>
+    <t>"gleba-special-crushing"</t>
+  </si>
+  <si>
+    <t>"fulgoran-special-crushing"</t>
+  </si>
+  <si>
+    <t>"fulgoran-asteroid-chunk-crushing-adv"</t>
+  </si>
+  <si>
+    <t>"g"</t>
+  </si>
+  <si>
+    <t>"a"</t>
+  </si>
+  <si>
+    <t>Results String</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
+    { type = "item", name = "vulcanic_asteroid_chunk_item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
+    { type = "item", name = "nauvis_asteroid_chunk_item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
+    { type = "item", name = "fulgoran_asteroid_chunk_item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "vulcanic_asteroid_chunk_item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
+    { type = "item", name = "nauvis_asteroid_chunk_item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
+    { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
+    { type = "item", name = "fulgoran_asteroid_chunk_item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
+}</t>
+  </si>
+  <si>
+    <t>{ 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+}</t>
+  </si>
+  <si>
+    <t>Variable's Name</t>
+  </si>
+  <si>
+    <t>crude_asteroid_chunk_crushing</t>
+  </si>
+  <si>
+    <t>vulcanus_asteroid_chunk_crushing</t>
+  </si>
+  <si>
+    <t>nauvis_asteroid_chunk_crushing</t>
+  </si>
+  <si>
+    <t>fulgoran_asteroid_chunk_crushing</t>
+  </si>
+  <si>
+    <t>vulcanis_asteroid_chunk_crushing_adv</t>
+  </si>
+  <si>
+    <t>nauvis_asteroid_chunk_crushing_adv</t>
+  </si>
+  <si>
+    <t>fulgoran_asteroid_chunk_crushing_adv</t>
+  </si>
+  <si>
+    <t>vulcanus_special_crushing</t>
+  </si>
+  <si>
+    <t>fulgoran_special_crushing</t>
+  </si>
+  <si>
+    <t>Whole String</t>
+  </si>
+  <si>
+    <t>crude-asteroid-chunk-item</t>
+  </si>
+  <si>
+    <t>vulcanic-asteroid-chunk-item</t>
+  </si>
+  <si>
+    <t>nauvis-asteroid-chunk-item</t>
+  </si>
+  <si>
+    <t>gleba-asteroid-chunk-item</t>
+  </si>
+  <si>
+    <t>fulgoran-asteroid-chunk-item</t>
+  </si>
+  <si>
+    <t>carbonic-asteroid-chunk-item</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/gleba_crushing_basic.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/crude_crushing_basic.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"</t>
+  </si>
+  <si>
+    <r>
+      <t>table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>deepcopy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFA657"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"asteroid-chunk"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>][</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"metallic-asteroid-chunk"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>deepcopy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFA657"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>item</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"metallic-asteroid-chunk"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>deepcopy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFA657"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>recipe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"metallic-asteroid-crushing"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>deepcopy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFA657"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>recipe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"advanced-metallic-asteroid-crushing"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>])</t>
+    </r>
+  </si>
+  <si>
+    <t>gleba_special_crushing</t>
+  </si>
+  <si>
+    <t>nauvis_special_crushing</t>
+  </si>
+  <si>
+    <t>gleba_asteroid_chunk_crushing_adv</t>
+  </si>
+  <si>
+    <t>gleba_asteroid_chunk_crushing</t>
+  </si>
+  <si>
+    <t>Advanced?</t>
+  </si>
+  <si>
+    <t>initialize</t>
+  </si>
+  <si>
+    <t>recipe settings</t>
+  </si>
+  <si>
+    <t>"gleba-asteroid-chunk-item"</t>
+  </si>
+  <si>
+    <t>"fulgoran-asteroid-chunk-item"</t>
+  </si>
+  <si>
+    <t>"crude-asteroid-chunk-item"</t>
+  </si>
+  <si>
+    <t>"nauvis-asteroid-chunk-item"</t>
+  </si>
+  <si>
+    <t>"vulcanic-asteroid-chunk-item"</t>
+  </si>
+  <si>
+    <t>"crude-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"nauvis-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"vulcanic-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"gleba-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"fulgoran-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>crude_asteroid_chunk</t>
+  </si>
+  <si>
+    <t>nauvis_asteroid_chunk</t>
+  </si>
+  <si>
+    <t>gleba_asteroid_chunk</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"</t>
+  </si>
+  <si>
+    <t>"__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "gleba-asteroid-chunk-item"}</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "fulgoran-asteroid-chunk-item"}</t>
+  </si>
+  <si>
+    <t>vulcanus_asteroid_chunk_item</t>
+  </si>
+  <si>
+    <t>fulgora_asteroid_chunk_item</t>
+  </si>
+  <si>
+    <t>vulcanus_asteroid_chunk</t>
+  </si>
+  <si>
+    <t>fulgora_asteroid_chunk</t>
+  </si>
+  <si>
+    <t>full string</t>
+  </si>
+  <si>
+    <t>minable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -728,16 +1348,71 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF79C0FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD2A8FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFA657"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA5D6FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -745,11 +1420,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -780,24 +1470,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="78">
     <dxf>
-      <fill>
-        <patternFill patternType="lightDown">
-          <fgColor rgb="FFFF99FF"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="lightDown">
-          <fgColor rgb="FFFF99FF"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -817,85 +1521,41 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1003,6 +1663,90 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1016,75 +1760,145 @@
 </styleSheet>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+  <rv s="0">
+    <v>13</v>
+    <v>3</v>
+  </rv>
+  <rv s="1">
+    <v>13</v>
+    <v>1</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="propagated" t="b"/>
+  </s>
+</rvStructures>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="47">
   <autoFilter ref="B3:AB25" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{B1A354A2-D591-4F7C-89E1-AB75527E5993}" name="Recipe"/>
-    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="62">
+    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="46">
       <calculatedColumnFormula>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="55">
+    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="39">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(J$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="54">
+    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="38">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(K$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="51">
+    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="35">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(N$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="50"/>
-    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="48"/>
-    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="47"/>
-    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="46"/>
-    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="45"/>
-    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="44"/>
-    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="43"/>
-    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="40"/>
-    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="39"/>
-    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="38"/>
-    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="37"/>
+    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="34"/>
+    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="32"/>
+    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="30"/>
+    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="29"/>
+    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="28"/>
+    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="26"/>
+    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="24"/>
+    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="23"/>
+    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50716056-6DAF-4F3B-B82E-A4E69F0450D7}" name="Table5" displayName="Table5" ref="B3:H7" totalsRowShown="0">
-  <autoFilter ref="B3:H7" xr:uid="{50716056-6DAF-4F3B-B82E-A4E69F0450D7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H6">
-    <sortCondition ref="B3:B6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50716056-6DAF-4F3B-B82E-A4E69F0450D7}" name="Chunk_Items" displayName="Chunk_Items" ref="B8:I13" totalsRowShown="0">
+  <autoFilter ref="B8:I13" xr:uid="{50716056-6DAF-4F3B-B82E-A4E69F0450D7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:H13">
+    <sortCondition ref="B8:B13"/>
   </sortState>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EFD8865D-C9ED-4BA8-B73C-113EDAD68DA5}" name="chunk item"/>
-    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="36">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{EFD8865D-C9ED-4BA8-B73C-113EDAD68DA5}" name="Variable's Name"/>
+    <tableColumn id="3" xr3:uid="{1A67492A-77CF-48AB-9609-594DA5CCF328}" name="name"/>
+    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="20">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1A67492A-77CF-48AB-9609-594DA5CCF328}" name="name"/>
-    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="35">
+    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="19">
       <calculatedColumnFormula>"""space-material"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{A45CDEC7-39DE-4333-8E31-011D04DA2762}" name="order"/>
     <tableColumn id="6" xr3:uid="{499C643B-C1ED-4A32-BE42-9946CC52BC6E}" name="icon"/>
-    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="34">
+    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="18">
       <calculatedColumnFormula>1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{9145470B-0772-4705-8B45-24698F613F56}" name="full string" dataDxfId="1">
+      <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1092,66 +1906,117 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6D95CADF-49B1-4F25-9D20-A564B80F80A3}" name="Table57" displayName="Table57" ref="J3:O7" totalsRowShown="0">
-  <autoFilter ref="J3:O7" xr:uid="{6D95CADF-49B1-4F25-9D20-A564B80F80A3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J4:O6">
-    <sortCondition ref="J3:J6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6D95CADF-49B1-4F25-9D20-A564B80F80A3}" name="Chunks" displayName="Chunks" ref="K8:Q13" totalsRowShown="0">
+  <autoFilter ref="K8:Q13" xr:uid="{6D95CADF-49B1-4F25-9D20-A564B80F80A3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K9:P10">
+    <sortCondition ref="K8:K10"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9C8B2B85-651A-48F5-BE74-6B0CB5EC6401}" name="chunk"/>
-    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="33">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{9C8B2B85-651A-48F5-BE74-6B0CB5EC6401}" name="Variable's Name"/>
+    <tableColumn id="3" xr3:uid="{5CB5E631-FE01-4CDD-A4B3-008A4C86A223}" name="name"/>
+    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="5">
       <calculatedColumnFormula>"""asteroid-chunk"""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5CB5E631-FE01-4CDD-A4B3-008A4C86A223}" name="name "/>
-    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable " dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{2D398BB0-41AE-40CE-AA0F-6FA6647FFA57}" name="order "/>
-    <tableColumn id="6" xr3:uid="{82F86FA9-1FFF-4AFF-A528-DD559BDA3930}" name="icon "/>
+    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{2D398BB0-41AE-40CE-AA0F-6FA6647FFA57}" name="order"/>
+    <tableColumn id="6" xr3:uid="{82F86FA9-1FFF-4AFF-A528-DD559BDA3930}" name="icon"/>
+    <tableColumn id="7" xr3:uid="{8D2BAF1D-A998-4CFE-AE20-A7C5A809314F}" name="full string" dataDxfId="0">
+      <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
+", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="B4:AG17" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="B4:AG17" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}"/>
-  <tableColumns count="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="C7:AP26" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="C7:AP26" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:AN26">
+    <sortCondition descending="1" ref="C7:C26"/>
+  </sortState>
+  <tableColumns count="40">
     <tableColumn id="1" xr3:uid="{1C7B22C3-8503-40CA-B985-0F11F98EB3C6}" name="Recipe"/>
-    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="26"/>
-    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="21"/>
-    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="20"/>
-    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="19"/>
-    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="18"/>
-    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="17"/>
-    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="16"/>
-    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="15"/>
-    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="14"/>
-    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1"/>
-    <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2"/>
-    <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3"/>
-    <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4"/>
-    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="4">
+    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="76"/>
+    <tableColumn id="41" xr3:uid="{6E5608DA-75C3-48D4-92AF-824B8C6B9141}" name="Advanced?" dataDxfId="10">
+      <calculatedColumnFormula>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="39" xr3:uid="{D73BFE2A-2B7F-460C-B8F4-2293AE8F1CDF}" name="Variable's Name" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="72"/>
+    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{8EF822E8-07FB-4876-8800-25F2A9B81873}" name="Result_1_type" dataDxfId="70"/>
+    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="69"/>
+    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="68"/>
+    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="67"/>
+    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="66"/>
+    <tableColumn id="34" xr3:uid="{F666EFD4-EFAB-4ED2-9F8C-93F381615487}" name="Result_2_type" dataDxfId="65"/>
+    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="64"/>
+    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="63"/>
+    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="62"/>
+    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="61"/>
+    <tableColumn id="35" xr3:uid="{29FDA9C5-AC15-474C-B065-A8F35BA59418}" name="Result_3_type" dataDxfId="60"/>
+    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="59"/>
+    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="58"/>
+    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="57"/>
+    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="56"/>
+    <tableColumn id="36" xr3:uid="{5C2D1484-E711-4E82-92DB-57B04BD66315}" name="Result_4_type" dataDxfId="55"/>
+    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="54"/>
+    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="53"/>
+    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="52"/>
+    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1" dataDxfId="50">
+      <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2" dataDxfId="49">
+      <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3" dataDxfId="48">
+      <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4" dataDxfId="14">
+      <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="13">
       <calculatedColumnFormula array="1" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="37" xr3:uid="{D9725653-650B-4E33-86E4-FA48D30F5455}" name="Results String" dataDxfId="12">
+      <calculatedColumnFormula array="1" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="40" xr3:uid="{6A447D5A-EAF2-404F-A826-F6177D7B50D6}" name="Whole String" dataDxfId="11">
+      <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1163,11 +2028,11 @@
   <autoFilter ref="H5:K15" xr:uid="{8FC02366-D4DD-41A4-8050-773DDA42B27E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{959EF51D-F84A-47B3-BB90-19C907903580}" name="name"/>
-    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="65">
+    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="17">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{214E8F8E-48B4-4BB8-B3A1-54F2A217D484}" name="amount"/>
-    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="64">
+    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="16">
       <calculatedColumnFormula array="1">"    { " &amp; _xlfn.TEXTJOIN(", ", TRUE, Table1[[#Headers],[name]:[amount]] &amp; " = " &amp; Table1[[#This Row],[name]:[amount]]) &amp; " }"</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1513,64 +2378,64 @@
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>7</v>
@@ -1746,7 +2611,7 @@
     </row>
     <row r="7" spans="2:28" ht="27.75" customHeight="1">
       <c r="B7" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2">
         <f>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</f>
@@ -1798,13 +2663,13 @@
         <f t="array" ref="K7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(K$3, _xlpm.recipeResults))), " - ") )</f>
-        <v>{ type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15 }</v>
+        <v>{ type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 }</v>
       </c>
       <c r="L7" s="9" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(L$3, _xlpm.recipeResults))), " - ") )</f>
-        <v>{ type = "item", name = "coal", amount_min = 5, amount_max = 15  }</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="M7" s="8" t="str" cm="1">
         <f t="array" ref="M7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
@@ -1905,7 +2770,7 @@
     </row>
     <row r="8" spans="2:28">
       <c r="B8" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2">
         <f>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</f>
@@ -1937,7 +2802,7 @@
         <f t="array" ref="N8">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(N$3, _xlpm.recipeResults))), " - ") )</f>
-        <v xml:space="preserve"> - </v>
+        <v>{ type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -2384,7 +3249,7 @@
     </row>
     <row r="17" spans="2:35">
       <c r="B17" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</f>
@@ -2441,13 +3306,13 @@
         <f t="array" ref="M17">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(M$3, _xlpm.recipeResults))), " - ") )</f>
-        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8 }</v>
+        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }</v>
       </c>
       <c r="N17" s="8" t="str" cm="1">
         <f t="array" ref="N17">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(N$3, _xlpm.recipeResults))), " - ") )</f>
-        <v>{ type = "item", name = "uranium-ore", amount_min = 0, amount_max = 4, probability = 0.25}</v>
+        <v>{ type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }</v>
       </c>
       <c r="O17" s="8" t="str" cm="1">
         <f t="array" ref="O17">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
@@ -2520,23 +3385,25 @@
         <v xml:space="preserve"> - </v>
       </c>
       <c r="AE17" t="str" cm="1">
-        <f t="array" ref="AE17:AH17">_xlfn._xlws.FILTER( _xlfn._xlws.FILTER(Table7[], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
+        <f t="array" ref="AE17:AI17">_xlfn._xlws.FILTER( _xlfn._xlws.FILTER(Table7[], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
          ISNUMBER(SEARCH("Results", Table7[#Headers])) )</f>
-        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8 }</v>
+        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }</v>
       </c>
       <c r="AF17" t="str">
-        <v>{ type = "item", name = "uranium-ore", amount_min = 0, amount_max = 4, probability = 0.25}</v>
-      </c>
-      <c r="AG17">
+        <v>{ type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }</v>
+      </c>
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="str" cm="1">
-        <f t="array" ref="AI17">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
-     _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(Table4[[#Headers],[stone]], _xlpm.recipeResults))) )</f>
-        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8 }</v>
+      <c r="AH17" t="str">
+        <v>{ type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
       </c>
     </row>
     <row r="18" spans="2:35">
@@ -2587,6 +3454,11 @@
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
+      <c r="AI18" t="e" cm="1" vm="1">
+        <f t="array" ref="AI18">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
+     _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(Table4[[#Headers],[stone]], _xlpm.recipeResults))) )</f>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="19" spans="2:35">
       <c r="B19" t="s">
@@ -2857,7 +3729,7 @@
         <v>13</v>
       </c>
       <c r="AE23" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="2:35">
@@ -2909,7 +3781,7 @@
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
       <c r="AE24" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="2:35">
@@ -2970,18 +3842,18 @@
       </c>
     </row>
     <row r="28" spans="2:35">
-      <c r="L28" s="2" t="str">
+      <c r="L28" s="2" t="e">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(L7, "}", ","), "amount_max = "), ",", , , , 0)</f>
-        <v xml:space="preserve">15  </v>
+        <v>#N/A</v>
       </c>
       <c r="AE28" s="7" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:35">
-      <c r="L29" s="2" t="str">
+      <c r="L29" s="2" t="e">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(L7, "}", ","), "amount_min = "), ",", , , , 0)</f>
-        <v>5</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="2:35">
@@ -2999,13 +3871,13 @@
     <row r="38" spans="14:14">
       <c r="N38" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "amount_max = "), ",", , , , 0)</f>
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="14:14">
       <c r="N39" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "amount_min = "), ",", , , , 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="14:14">
@@ -3017,7 +3889,7 @@
     <row r="41" spans="14:14">
       <c r="N41" s="2" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(SUBSTITUTE(N17, "}", ","), "probability = "), ",", , , , 0)</f>
-        <v>0.25</v>
+        <v xml:space="preserve">0.4 </v>
       </c>
     </row>
   </sheetData>
@@ -3037,7 +3909,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04493FD2-BC79-4DE4-945B-7AF801A57BBD}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B1:O19"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="23.75" customWidth="1"/>
@@ -3047,252 +3919,510 @@
     <col min="6" max="6" width="8.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.75" customWidth="1"/>
-    <col min="11" max="11" width="16.625" customWidth="1"/>
-    <col min="12" max="12" width="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="52.625" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="54.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="23.75" customWidth="1"/>
+    <col min="12" max="12" width="16.625" customWidth="1"/>
+    <col min="13" max="13" width="35" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="52.625" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="54.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1">
       <c r="B1" s="5"/>
     </row>
-    <row r="3" spans="2:15">
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="2" spans="1:17" ht="24" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="18" t="str" cm="1">
+        <f t="array" ref="B2">_xlfn.TEXTJOIN("
+", TRUE, "local " &amp; Chunk_Items[Variable''s Name] &amp; " = " &amp; $B$6)</f>
+        <v>local crude_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])
+local nauvis_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])
+local vulcanus_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])
+local gleba_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])
+local fulgora_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])</v>
+      </c>
+      <c r="J2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K2" s="18" t="str" cm="1">
+        <f t="array" ref="K2">_xlfn.TEXTJOIN("
+", TRUE, "local " &amp; Chunks[Variable''s Name] &amp; " = " &amp; $K$6)</f>
+        <v>local crude_asteroid_chunk = table.deepcopy(data.raw["asteroid-chunk"]["metallic-asteroid-chunk"])
+local nauvis_asteroid_chunk = table.deepcopy(data.raw["asteroid-chunk"]["metallic-asteroid-chunk"])
+local vulcanus_asteroid_chunk = table.deepcopy(data.raw["asteroid-chunk"]["metallic-asteroid-chunk"])
+local gleba_asteroid_chunk = table.deepcopy(data.raw["asteroid-chunk"]["metallic-asteroid-chunk"])
+local fulgora_asteroid_chunk = table.deepcopy(data.raw["asteroid-chunk"]["metallic-asteroid-chunk"])</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" thickTop="1" thickBot="1"/>
+    <row r="4" spans="1:17" ht="19.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="13" t="str">
+        <f>_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[full string])</f>
+        <v>crude_asteroid_chunk_item.name = "crude-asteroid-chunk-item"
+crude_asteroid_chunk_item.type = "item"
+crude_asteroid_chunk_item.subgroup = "space-material"
+crude_asteroid_chunk_item.order = "f"
+crude_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"
+crude_asteroid_chunk_item.stack_size = 1
+nauvis_asteroid_chunk_item.name = "nauvis-asteroid-chunk-item"
+nauvis_asteroid_chunk_item.type = "item"
+nauvis_asteroid_chunk_item.subgroup = "space-material"
+nauvis_asteroid_chunk_item.order = "f"
+nauvis_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"
+nauvis_asteroid_chunk_item.stack_size = 1
+vulcanus_asteroid_chunk_item.name = "vulcanic-asteroid-chunk-item"
+vulcanus_asteroid_chunk_item.type = "item"
+vulcanus_asteroid_chunk_item.subgroup = "space-material"
+vulcanus_asteroid_chunk_item.order = "v"
+vulcanus_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"
+vulcanus_asteroid_chunk_item.stack_size = 1
+gleba_asteroid_chunk_item.name = "gleba-asteroid-chunk-item"
+gleba_asteroid_chunk_item.type = "item"
+gleba_asteroid_chunk_item.subgroup = "space-material"
+gleba_asteroid_chunk_item.order = "g"
+gleba_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"
+gleba_asteroid_chunk_item.stack_size = 1
+fulgora_asteroid_chunk_item.name = "fulgoran-asteroid-chunk-item"
+fulgora_asteroid_chunk_item.type = "item"
+fulgora_asteroid_chunk_item.subgroup = "space-material"
+fulgora_asteroid_chunk_item.order = "f"
+fulgora_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"
+fulgora_asteroid_chunk_item.stack_size = 1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>233</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f>_xlfn.TEXTJOIN("
+", TRUE, Chunks[full string])</f>
+        <v>crude_asteroid_chunk.name = "crude-asteroid-chunk"
+crude_asteroid_chunk.type = "asteroid-chunk"
+crude_asteroid_chunk.minable = {mining_time = 0.2, result = "crude_asteroid_chunk_item"}
+crude_asteroid_chunk.order = "f"
+crude_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"
+nauvis_asteroid_chunk.name = "nauvis-asteroid-chunk"
+nauvis_asteroid_chunk.type = "asteroid-chunk"
+nauvis_asteroid_chunk.minable = {mining_time = 0.2, result = "nauvis_asteroid_chunk_item"}
+nauvis_asteroid_chunk.order = "n"
+nauvis_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"
+vulcanus_asteroid_chunk.name = "vulcanic-asteroid-chunk"
+vulcanus_asteroid_chunk.type = "asteroid-chunk"
+vulcanus_asteroid_chunk.minable = {mining_time = 0.2, result = "volcanic_asteroid_chunk_item"}
+vulcanus_asteroid_chunk.order = "v"
+vulcanus_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"
+gleba_asteroid_chunk.name = "gleba-asteroid-chunk"
+gleba_asteroid_chunk.type = "asteroid-chunk"
+gleba_asteroid_chunk.minable = {mining_time = 0.2, result = "gleba-asteroid-chunk-item"}
+gleba_asteroid_chunk.order = "g"
+gleba_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"
+fulgora_asteroid_chunk.name = "fulgoran-asteroid-chunk"
+fulgora_asteroid_chunk.type = "asteroid-chunk"
+fulgora_asteroid_chunk.minable = {mining_time = 0.2, result = "fulgoran-asteroid-chunk-item"}
+fulgora_asteroid_chunk.order = "f"
+fulgora_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" thickTop="1">
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:17" ht="15">
+      <c r="B6" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="K6" s="14" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>255</v>
+      </c>
+      <c r="K8" t="s">
+        <v>198</v>
+      </c>
+      <c r="L8" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s">
+        <v>256</v>
+      </c>
+      <c r="O8" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="P8" t="s">
         <v>33</v>
       </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15">
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="str">
+      <c r="Q8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" t="str">
         <f>"""item"""</f>
         <v>"item"</v>
       </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="str">
+      <c r="E9" t="str">
         <f>"""space-material"""</f>
         <v>"space-material"</v>
       </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4">
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>220</v>
+      </c>
+      <c r="H9">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" t="str">
+      <c r="I9" t="str" cm="1">
+        <f t="array" ref="I9">_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
+        <v>crude_asteroid_chunk_item.name = "crude-asteroid-chunk-item"
+crude_asteroid_chunk_item.type = "item"
+crude_asteroid_chunk_item.subgroup = "space-material"
+crude_asteroid_chunk_item.order = "f"
+crude_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"
+crude_asteroid_chunk_item.stack_size = 1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>244</v>
+      </c>
+      <c r="L9" t="s">
+        <v>239</v>
+      </c>
+      <c r="M9" t="str">
         <f>"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
-      <c r="L4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15">
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="str">
+      <c r="N9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q9" t="str" cm="1">
+        <f t="array" ref="Q9">_xlfn.TEXTJOIN("
+", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
+        <v>crude_asteroid_chunk.name = "crude-asteroid-chunk"
+crude_asteroid_chunk.type = "asteroid-chunk"
+crude_asteroid_chunk.minable = {mining_time = 0.2, result = "crude_asteroid_chunk_item"}
+crude_asteroid_chunk.order = "f"
+crude_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" t="str">
         <f>"""item"""</f>
         <v>"item"</v>
       </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" t="str">
+      <c r="E10" t="str">
         <f>"""space-material"""</f>
         <v>"space-material"</v>
       </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5">
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H10">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="J5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" t="str">
+      <c r="I10" t="str" cm="1">
+        <f t="array" ref="I10">_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
+        <v>nauvis_asteroid_chunk_item.name = "nauvis-asteroid-chunk-item"
+nauvis_asteroid_chunk_item.type = "item"
+nauvis_asteroid_chunk_item.subgroup = "space-material"
+nauvis_asteroid_chunk_item.order = "f"
+nauvis_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"
+nauvis_asteroid_chunk_item.stack_size = 1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>245</v>
+      </c>
+      <c r="L10" t="s">
+        <v>240</v>
+      </c>
+      <c r="M10" t="str">
         <f>"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
-      <c r="L5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="B6" t="s">
+      <c r="N10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="str">
+      <c r="P10" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q10" t="str" cm="1">
+        <f t="array" ref="Q10">_xlfn.TEXTJOIN("
+", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
+        <v>nauvis_asteroid_chunk.name = "nauvis-asteroid-chunk"
+nauvis_asteroid_chunk.type = "asteroid-chunk"
+nauvis_asteroid_chunk.minable = {mining_time = 0.2, result = "nauvis_asteroid_chunk_item"}
+nauvis_asteroid_chunk.order = "n"
+nauvis_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="B11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" t="str">
         <f>"""item"""</f>
         <v>"item"</v>
       </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="E11" t="str">
         <f>"""space-material"""</f>
         <v>"space-material"</v>
       </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6">
+      <c r="F11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="str">
+      <c r="I11" t="str" cm="1">
+        <f t="array" ref="I11">_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
+        <v>vulcanus_asteroid_chunk_item.name = "vulcanic-asteroid-chunk-item"
+vulcanus_asteroid_chunk_item.type = "item"
+vulcanus_asteroid_chunk_item.subgroup = "space-material"
+vulcanus_asteroid_chunk_item.order = "v"
+vulcanus_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"
+vulcanus_asteroid_chunk_item.stack_size = 1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>253</v>
+      </c>
+      <c r="L11" t="s">
+        <v>241</v>
+      </c>
+      <c r="M11" t="str">
         <f>"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
-      <c r="L6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" t="s">
-        <v>106</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15">
-      <c r="B7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" t="str">
+      <c r="N11" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q11" t="str" cm="1">
+        <f t="array" ref="Q11">_xlfn.TEXTJOIN("
+", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
+        <v>vulcanus_asteroid_chunk.name = "vulcanic-asteroid-chunk"
+vulcanus_asteroid_chunk.type = "asteroid-chunk"
+vulcanus_asteroid_chunk.minable = {mining_time = 0.2, result = "volcanic_asteroid_chunk_item"}
+vulcanus_asteroid_chunk.order = "v"
+vulcanus_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="12" t="str">
         <f>"""item"""</f>
         <v>"item"</v>
       </c>
-      <c r="D7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" t="str">
+      <c r="E12" s="12" t="str">
         <f>"""space-material"""</f>
         <v>"space-material"</v>
       </c>
-      <c r="F7" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7">
+      <c r="F12" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="12">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="J7" t="s">
-        <v>129</v>
-      </c>
-      <c r="K7" t="str">
-        <f>"""asteroid-chunk"""</f>
+      <c r="I12" s="12" t="str" cm="1">
+        <f t="array" ref="I12">_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
+        <v>gleba_asteroid_chunk_item.name = "gleba-asteroid-chunk-item"
+gleba_asteroid_chunk_item.type = "item"
+gleba_asteroid_chunk_item.subgroup = "space-material"
+gleba_asteroid_chunk_item.order = "g"
+gleba_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"
+gleba_asteroid_chunk_item.stack_size = 1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>246</v>
+      </c>
+      <c r="L12" t="s">
+        <v>242</v>
+      </c>
+      <c r="M12" s="12" t="str">
+        <f t="shared" ref="M12:M13" si="0">"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
-      <c r="L7" t="s">
-        <v>131</v>
-      </c>
-      <c r="M7" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" t="s">
-        <v>134</v>
-      </c>
-      <c r="O7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" ht="15">
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="2:15" ht="15">
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="12:12" ht="15">
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="12:12" ht="15">
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="12:12" ht="15">
-      <c r="L19" s="6"/>
+      <c r="N12" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="O12" t="s">
+        <v>186</v>
+      </c>
+      <c r="P12" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q12" t="str" cm="1">
+        <f t="array" ref="Q12">_xlfn.TEXTJOIN("
+", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
+        <v>gleba_asteroid_chunk.name = "gleba-asteroid-chunk"
+gleba_asteroid_chunk.type = "asteroid-chunk"
+gleba_asteroid_chunk.minable = {mining_time = 0.2, result = "gleba-asteroid-chunk-item"}
+gleba_asteroid_chunk.order = "g"
+gleba_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="B13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="12" t="str">
+        <f>"""item"""</f>
+        <v>"item"</v>
+      </c>
+      <c r="E13" s="12" t="str">
+        <f>"""space-material"""</f>
+        <v>"space-material"</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>248</v>
+      </c>
+      <c r="H13" s="12">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="12" t="str" cm="1">
+        <f t="array" ref="I13">_xlfn.TEXTJOIN("
+", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
+        <v>fulgora_asteroid_chunk_item.name = "fulgoran-asteroid-chunk-item"
+fulgora_asteroid_chunk_item.type = "item"
+fulgora_asteroid_chunk_item.subgroup = "space-material"
+fulgora_asteroid_chunk_item.order = "f"
+fulgora_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"
+fulgora_asteroid_chunk_item.stack_size = 1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>254</v>
+      </c>
+      <c r="L13" t="s">
+        <v>243</v>
+      </c>
+      <c r="M13" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>"asteroid-chunk"</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="O13" t="s">
+        <v>35</v>
+      </c>
+      <c r="P13" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q13" t="str" cm="1">
+        <f t="array" ref="Q13">_xlfn.TEXTJOIN("
+", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
+        <v>fulgora_asteroid_chunk.name = "fulgoran-asteroid-chunk"
+fulgora_asteroid_chunk.type = "asteroid-chunk"
+fulgora_asteroid_chunk.minable = {mining_time = 0.2, result = "fulgoran-asteroid-chunk-item"}
+fulgora_asteroid_chunk.order = "f"
+fulgora_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"</v>
+      </c>
+    </row>
+    <row r="19" spans="13:13" ht="15">
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="13:13" ht="15">
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="13:13" ht="15">
+      <c r="M21" s="6"/>
+    </row>
+    <row r="22" spans="13:13" ht="15">
+      <c r="M22" s="6"/>
+    </row>
+    <row r="23" spans="13:13" ht="15">
+      <c r="M23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3306,766 +4436,3043 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA672A5-FC41-4490-AF8C-1F6ADD4F213B}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:AJ49"/>
+  <dimension ref="B1:AQ58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.75" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="66.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.125" style="2" customWidth="1"/>
-    <col min="9" max="12" width="35.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.125" style="2" customWidth="1"/>
-    <col min="15" max="28" width="9.375" style="2" customWidth="1"/>
-    <col min="29" max="29" width="64.625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="82.375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="62.125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="62.75" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="118.875" customWidth="1"/>
-    <col min="36" max="36" width="64" customWidth="1"/>
-    <col min="37" max="37" width="27" customWidth="1"/>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="23.125" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="63.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
+    <col min="11" max="12" width="11.125" style="2" customWidth="1"/>
+    <col min="13" max="14" width="27.5" style="2" customWidth="1"/>
+    <col min="15" max="16" width="8.5" style="2" customWidth="1"/>
+    <col min="17" max="18" width="9.375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.125" style="2" customWidth="1"/>
+    <col min="20" max="22" width="9.375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="10.75" style="2" customWidth="1"/>
+    <col min="24" max="27" width="9.375" style="2" customWidth="1"/>
+    <col min="28" max="28" width="20.5" style="2" customWidth="1"/>
+    <col min="29" max="32" width="9.375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="15.5" style="2" customWidth="1"/>
+    <col min="34" max="35" width="9.375" style="2" customWidth="1"/>
+    <col min="36" max="36" width="11.25" style="2" hidden="1" customWidth="1"/>
+    <col min="37" max="39" width="11.25" hidden="1" customWidth="1"/>
+    <col min="40" max="42" width="45.875" customWidth="1"/>
+    <col min="44" max="44" width="64" customWidth="1"/>
+    <col min="45" max="45" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:36">
-      <c r="I2" s="2" t="s">
+    <row r="1" spans="2:43" ht="16.5" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:43" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="18" t="str" cm="1">
+        <f t="array" ref="C2">_xlfn.TEXTJOIN("
+", TRUE, _xlfn._xlws.FILTER("local " &amp; Table7[Variable''s Name] &amp; " = " &amp; IF(Table7[Advanced?], advRecipeCopy, baseRecipeCopy), ISBLANK(Table7[Unwritten?])))</f>
+        <v>local crude_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
+local vulcanus_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
+local nauvis_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
+local fulgoran_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
+local vulcanis_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
+local nauvis_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
+local fulgoran_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
+local vulcanus_special_crushing = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
+local fulgoran_special_crushing = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])</v>
+      </c>
+    </row>
+    <row r="3" spans="2:43" ht="16.5" customHeight="1" thickTop="1" thickBot="1"/>
+    <row r="4" spans="2:43" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="13" t="str" cm="1">
+        <f t="array" ref="C4">_xlfn.TEXTJOIN("
+", TRUE, _xlfn._xlws.FILTER(Table7[Whole String], ISBLANK(Table7[Unwritten?])))</f>
+        <v>crude_asteroid_chunk_crushing.name = "crude-asteroid-chunk-crushing"
+crude_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+crude_asteroid_chunk_crushing.order = "a"
+crude_asteroid_chunk_crushing.enabled = false
+crude_asteroid_chunk_crushing.energy_required = 2
+crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "crude-asteroid-chunk-item", amount = 1 } }
+crude_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+}
+vulcanus_asteroid_chunk_crushing.name = "vulcanus-asteroid-chunk-crushing"
+vulcanus_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanus_asteroid_chunk_crushing.order = "v"
+vulcanus_asteroid_chunk_crushing.enabled = false
+vulcanus_asteroid_chunk_crushing.energy_required = 2
+vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanus_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
+    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+nauvis_asteroid_chunk_crushing.name = "nauvis-asteroid-chunk-crushing"
+nauvis_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
+nauvis_asteroid_chunk_crushing.order = "n"
+nauvis_asteroid_chunk_crushing.enabled = false
+nauvis_asteroid_chunk_crushing.energy_required = 2
+nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+fulgoran_asteroid_chunk_crushing.name = "fulgoran-asteroid-chunk-crushing"
+fulgoran_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_asteroid_chunk_crushing.order = "f"
+fulgoran_asteroid_chunk_crushing.enabled = false
+fulgoran_asteroid_chunk_crushing.energy_required = 2
+fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
+    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+vulcanis_asteroid_chunk_crushing_adv.name = "vulcanis-asteroid-chunk-crushing-adv"
+vulcanis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanis_asteroid_chunk_crushing_adv.order = "v"
+vulcanis_asteroid_chunk_crushing_adv.enabled = false
+vulcanis_asteroid_chunk_crushing_adv.energy_required = 5
+vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanis_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+nauvis_asteroid_chunk_crushing_adv.name = "nauvis-asteroid-chunk-crushing-adv"
+nauvis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
+nauvis_asteroid_chunk_crushing_adv.order = "n"
+nauvis_asteroid_chunk_crushing_adv.enabled = false
+nauvis_asteroid_chunk_crushing_adv.energy_required = 5
+nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+fulgoran_asteroid_chunk_crushing_adv.name = "fulgoran-asteroid-chunk-crushing-adv"
+fulgoran_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_asteroid_chunk_crushing_adv.order = "f"
+fulgoran_asteroid_chunk_crushing_adv.enabled = false
+fulgoran_asteroid_chunk_crushing_adv.energy_required = 5
+fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
+    { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
+    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+vulcanus_special_crushing.name = "vulcanus-special-crushing"
+vulcanus_special_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanus_special_crushing.order = "v"
+vulcanus_special_crushing.enabled = false
+vulcanus_special_crushing.energy_required = 5
+vulcanus_special_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
+vulcanus_special_crushing.results = { 
+    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
+}
+fulgoran_special_crushing.name = "fulgoran-special-crushing"
+fulgoran_special_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_special_crushing.order = "f"
+fulgoran_special_crushing.enabled = false
+fulgoran_special_crushing.energy_required = 10
+fulgoran_special_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk-item", amount = 1 } }
+fulgoran_special_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+}</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="2:43" ht="16.5" customHeight="1" thickTop="1">
+      <c r="G5" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="2:43">
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:43" s="1" customFormat="1" ht="52.5" customHeight="1">
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" spans="2:36">
-      <c r="F3" s="2" t="s">
+      <c r="N7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN7" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="2:36" s="1" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36">
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="AO7" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG5" t="str" cm="1">
-        <f t="array" ref="AG5" xml:space="preserve"> "{ " &amp;
+      <c r="L8" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="2">
+        <v>5</v>
+      </c>
+      <c r="S8" s="2">
+        <v>5</v>
+      </c>
+      <c r="T8" s="2">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="W8" s="2">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AJ8" t="str" cm="1">
+        <f t="array" ref="AJ8">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "ice", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+      <c r="AK8" t="str" cm="1">
+        <f t="array" ref="AK8">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+      <c r="AL8" t="b" cm="1">
+        <f t="array" ref="AL8">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b" cm="1">
+        <f t="array" ref="AM8">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="15" t="str" cm="1">
+        <f t="array" ref="AN8" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "nauvis_asteroid_chunk_item", amount = 1 } }</v>
-      </c>
-      <c r="AJ5" t="str" cm="1">
-        <f t="array" ref="AJ5" xml:space="preserve"> "{ " &amp;
+        <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO8" s="15" t="str" cm="1">
+        <f t="array" ref="AO8" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "ice", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+}</v>
+      </c>
+      <c r="AP8" s="16" t="str" cm="1">
+        <f t="array" ref="AP8">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>.name = "oxide-asteroid-crushing"
+.icon = "__space-age__\graphics\icons\oxide-asteroid-crushing.png"
+.order = 
+.enabled = false
+.energy_required = 2
+.ingredients = { { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }
+.results = { 
+    { type = "item", name = "ice", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+}</v>
+      </c>
+      <c r="AQ8" t="str" cm="1">
+        <f t="array" ref="AQ8" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "nauvis_asteroid_chunk_item", amount = 1 } }</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36">
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="2">
-        <v>5</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG6" t="e" cm="1">
-        <f t="array" ref="AG6" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="7" spans="2:36">
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="2">
+        <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
+      </c>
+    </row>
+    <row r="9" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="2">
         <v>2</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG7" t="e" cm="1">
-        <f t="array" ref="AG7" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="8" spans="2:36">
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="2">
-        <v>2</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG8" t="str" cm="1">
-        <f t="array" ref="AG8" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>{ { type = "item", name = "vulcanic_asteroid_chunk_item", amount = 1 } }</v>
-      </c>
-    </row>
-    <row r="9" spans="2:36">
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG9" t="e" cm="1">
-        <f t="array" ref="AG9" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="2:36">
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG10" t="e" cm="1">
-        <f t="array" ref="AG10" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="11" spans="2:36">
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="2">
-        <v>5</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="str" cm="1">
-        <f t="array" ref="AG11" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>{ { type = "item", name = "vulcanic_asteroid_chunk_item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
-      </c>
-    </row>
-    <row r="12" spans="2:36">
-      <c r="B12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="2">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="str" cm="1">
-        <f t="array" ref="AG12" xml:space="preserve"> "{ " &amp;
+      <c r="L9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="b" cm="1">
+        <f t="array" ref="AJ9">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AK9" t="b" cm="1">
+        <f t="array" ref="AK9">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL9" t="b" cm="1">
+        <f t="array" ref="AL9">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM9" t="b" cm="1">
+        <f t="array" ref="AM9">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="15" t="str" cm="1">
+        <f t="array" ref="AN9" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
         <v>{ { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
-    </row>
-    <row r="13" spans="2:36">
-      <c r="B13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="AO9" s="15" t="e" cm="1" vm="1">
+        <f t="array" ref="AO9" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP9" s="16" t="e" cm="1" vm="2">
+        <f t="array" ref="AP9">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="2">
         <v>2</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG13" t="str" cm="1">
-        <f t="array" ref="AG13" xml:space="preserve"> "{ " &amp;
+      <c r="L10" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R10" s="2">
+        <v>5</v>
+      </c>
+      <c r="S10" s="2">
+        <v>15</v>
+      </c>
+      <c r="T10" s="2">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W10" s="2">
+        <v>5</v>
+      </c>
+      <c r="X10" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="str" cm="1">
+        <f t="array" ref="AJ10">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 }</v>
+      </c>
+      <c r="AK10" t="b" cm="1">
+        <f t="array" ref="AK10">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL10" t="b" cm="1">
+        <f t="array" ref="AL10">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM10" t="b" cm="1">
+        <f t="array" ref="AM10">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="15" t="str" cm="1">
+        <f t="array" ref="AN10" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "crude-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO10" s="15" t="str" cm="1">
+        <f t="array" ref="AO10" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+}</v>
+      </c>
+      <c r="AP10" s="16" t="str" cm="1">
+        <f t="array" ref="AP10">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>crude_asteroid_chunk_crushing.name = "crude-asteroid-chunk-crushing"
+crude_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+crude_asteroid_chunk_crushing.order = "a"
+crude_asteroid_chunk_crushing.enabled = false
+crude_asteroid_chunk_crushing.energy_required = 2
+crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "crude-asteroid-chunk-item", amount = 1 } }
+crude_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+}</v>
+      </c>
+    </row>
+    <row r="11" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="b" cm="1">
+        <f t="array" ref="AJ11">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AK11" t="b" cm="1">
+        <f t="array" ref="AK11">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" t="b" cm="1">
+        <f t="array" ref="AL11">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM11" t="b" cm="1">
+        <f t="array" ref="AM11">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="15" t="str" cm="1">
+        <f t="array" ref="AN11" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
         <v>{ { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
-    </row>
-    <row r="14" spans="2:36">
-      <c r="B14" t="s">
-        <v>154</v>
+      <c r="AO11" s="15" t="e" cm="1" vm="1">
+        <f t="array" ref="AO11" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP11" s="16" t="e" cm="1" vm="2">
+        <f t="array" ref="AP11">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="2">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R12" s="2">
+        <v>4</v>
+      </c>
+      <c r="S12" s="2">
+        <v>6</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W12" s="2">
+        <v>1</v>
+      </c>
+      <c r="X12" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ12" t="str" cm="1">
+        <f t="array" ref="AJ12">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }</v>
+      </c>
+      <c r="AK12" t="str" cm="1">
+        <f t="array" ref="AK12">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }</v>
+      </c>
+      <c r="AL12" t="b" cm="1">
+        <f t="array" ref="AL12">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM12" t="str" cm="1">
+        <f t="array" ref="AM12">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN12" s="15" t="str" cm="1">
+        <f t="array" ref="AN12" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO12" s="15" t="str" cm="1">
+        <f t="array" ref="AO12" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
+    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP12" s="16" t="str" cm="1">
+        <f t="array" ref="AP12">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>vulcanus_asteroid_chunk_crushing.name = "vulcanus-asteroid-chunk-crushing"
+vulcanus_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanus_asteroid_chunk_crushing.order = "v"
+vulcanus_asteroid_chunk_crushing.enabled = false
+vulcanus_asteroid_chunk_crushing.energy_required = 2
+vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanus_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
+    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="13" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="2">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R13" s="2">
+        <v>5</v>
+      </c>
+      <c r="S13" s="2">
+        <v>10</v>
+      </c>
+      <c r="T13" s="2">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W13" s="2">
+        <v>1</v>
+      </c>
+      <c r="X13" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AG13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ13" t="str" cm="1">
+        <f t="array" ref="AJ13">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }</v>
+      </c>
+      <c r="AK13" t="str" cm="1">
+        <f t="array" ref="AK13">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }</v>
+      </c>
+      <c r="AL13" t="b" cm="1">
+        <f t="array" ref="AL13">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM13" t="str" cm="1">
+        <f t="array" ref="AM13">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN13" s="15" t="str" cm="1">
+        <f t="array" ref="AN13" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO13" s="15" t="str" cm="1">
+        <f t="array" ref="AO13" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP13" s="16" t="str" cm="1">
+        <f t="array" ref="AP13">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>nauvis_asteroid_chunk_crushing.name = "nauvis-asteroid-chunk-crushing"
+nauvis_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
+nauvis_asteroid_chunk_crushing.order = "n"
+nauvis_asteroid_chunk_crushing.enabled = false
+nauvis_asteroid_chunk_crushing.energy_required = 2
+nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="14" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C14" t="s">
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>169</v>
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" s="2">
+        <v>176</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="2">
         <v>2</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
-      <c r="M14" s="2" t="s">
+      <c r="L14" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="2">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" s="2">
+        <v>3</v>
+      </c>
+      <c r="S14" s="2">
+        <v>5</v>
+      </c>
+      <c r="T14" s="2">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="W14" s="2">
+        <v>1</v>
+      </c>
+      <c r="X14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ14" t="str" cm="1">
+        <f t="array" ref="AJ14">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 3, amount_max = 5, probability = 1 }</v>
+      </c>
+      <c r="AK14" t="str" cm="1">
+        <f t="array" ref="AK14">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AL14" t="str" cm="1">
+        <f t="array" ref="AL14">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AM14" t="str" cm="1">
+        <f t="array" ref="AM14">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN14" s="15" t="str" cm="1">
+        <f t="array" ref="AN14" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO14" s="15" t="str" cm="1">
+        <f t="array" ref="AO14" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 3, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP14" s="16" t="str" cm="1">
+        <f t="array" ref="AP14">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>gleba_asteroid_chunk_crushing.name = "gleba-asteroid-chunk-crushing"
+gleba_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/gleba_crushing_basic.png"
+gleba_asteroid_chunk_crushing.order = "g"
+gleba_asteroid_chunk_crushing.enabled = false
+gleba_asteroid_chunk_crushing.energy_required = 2
+gleba_asteroid_chunk_crushing.ingredients = { { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }
+gleba_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 3, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="15" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="2">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R15" s="2">
+        <v>4</v>
+      </c>
+      <c r="S15" s="2">
+        <v>6</v>
+      </c>
+      <c r="T15" s="2">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W15" s="2">
+        <v>2</v>
+      </c>
+      <c r="X15" s="2">
+        <v>12</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ15" t="str" cm="1">
+        <f t="array" ref="AJ15">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }</v>
+      </c>
+      <c r="AK15" t="str" cm="1">
+        <f t="array" ref="AK15">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }</v>
+      </c>
+      <c r="AL15" t="b" cm="1">
+        <f t="array" ref="AL15">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM15" t="str" cm="1">
+        <f t="array" ref="AM15">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN15" s="15" t="str" cm="1">
+        <f t="array" ref="AN15" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO15" s="15" t="str" cm="1">
+        <f t="array" ref="AO15" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
+    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP15" s="16" t="str" cm="1">
+        <f t="array" ref="AP15">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>fulgoran_asteroid_chunk_crushing.name = "fulgoran-asteroid-chunk-crushing"
+fulgoran_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_asteroid_chunk_crushing.order = "f"
+fulgoran_asteroid_chunk_crushing.enabled = false
+fulgoran_asteroid_chunk_crushing.energy_required = 2
+fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
+    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="16" spans="2:43" ht="18.75" customHeight="1">
+      <c r="C16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="N14" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q14" s="2">
+      <c r="J16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="2">
         <v>5</v>
       </c>
-      <c r="R14" s="2">
-        <v>5</v>
-      </c>
-      <c r="S14" s="2">
-        <v>1</v>
-      </c>
-      <c r="T14" s="2">
-        <v>1</v>
-      </c>
-      <c r="U14" s="2">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AG14" t="str" cm="1">
-        <f t="array" ref="AG14" xml:space="preserve"> "{ " &amp;
+      <c r="L16" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="2">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R16" s="2">
+        <v>3</v>
+      </c>
+      <c r="S16" s="2">
+        <v>3</v>
+      </c>
+      <c r="T16" s="2">
+        <v>1</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W16" s="2">
+        <v>2</v>
+      </c>
+      <c r="X16" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ16" t="str" cm="1">
+        <f t="array" ref="AJ16">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "ice", amount_min = 3, amount_max = 3, probability = 1 }</v>
+      </c>
+      <c r="AK16" t="str" cm="1">
+        <f t="array" ref="AK16">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 }</v>
+      </c>
+      <c r="AL16" t="str" cm="1">
+        <f t="array" ref="AL16">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AM16" t="str" cm="1">
+        <f t="array" ref="AM16">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "", amount_min = "", amount_max = "", probability = "" }</v>
+      </c>
+      <c r="AN16" s="15" t="str" cm="1">
+        <f t="array" ref="AN16" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
         <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
       </c>
-    </row>
-    <row r="15" spans="2:36">
-      <c r="B15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="2">
+      <c r="AO16" s="15" t="str" cm="1">
+        <f t="array" ref="AO16" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "ice", amount_min = 3, amount_max = 3, probability = 1 }, 
+    { type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 }, 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
+}</v>
+      </c>
+      <c r="AP16" s="16" t="str" cm="1">
+        <f t="array" ref="AP16">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>.name = "advanced-oxide-asteroid-crushing"
+.icon = "__space-age__\graphics\icons\advanced-oxide-asteroid-crushing.png"
+.order = 
+.enabled = false
+.energy_required = 5
+.ingredients = { { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }
+.results = { 
+    { type = "item", name = "ice", amount_min = 3, amount_max = 3, probability = 1 }, 
+    { type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 }, 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
+}</v>
+      </c>
+    </row>
+    <row r="17" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="2">
         <v>5</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q15" s="2">
+      <c r="L17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="2">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R17" s="2">
         <v>10</v>
       </c>
-      <c r="R15" s="2">
+      <c r="S17" s="2">
         <v>10</v>
       </c>
-      <c r="S15" s="2">
-        <v>1</v>
-      </c>
-      <c r="T15" s="2">
+      <c r="T17" s="2">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W17" s="2">
         <v>4</v>
       </c>
-      <c r="U15" s="2">
+      <c r="X17" s="2">
         <v>4</v>
       </c>
-      <c r="V15" s="2">
-        <v>1</v>
-      </c>
-      <c r="W15" s="2">
-        <v>1</v>
-      </c>
-      <c r="X15" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="2">
+      <c r="Y17" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="2">
         <v>0.05</v>
       </c>
-      <c r="AG15" t="str" cm="1">
-        <f t="array" ref="AG15" xml:space="preserve"> "{ " &amp;
+      <c r="AE17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ17" t="str" cm="1">
+        <f t="array" ref="AJ17">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "iron-ore", amount_min = 10, amount_max = 10, probability = 1 }</v>
+      </c>
+      <c r="AK17" t="str" cm="1">
+        <f t="array" ref="AK17">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 }</v>
+      </c>
+      <c r="AL17" t="str" cm="1">
+        <f t="array" ref="AL17">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AM17" t="str" cm="1">
+        <f t="array" ref="AM17">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "", amount_min = "", amount_max = "", probability = "" }</v>
+      </c>
+      <c r="AN17" s="15" t="str" cm="1">
+        <f t="array" ref="AN17" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
         <v>{ { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
-    </row>
-    <row r="16" spans="2:36">
-      <c r="B16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="AO17" s="15" t="str" cm="1">
+        <f t="array" ref="AO17" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "iron-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 }, 
+    { type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
+}</v>
+      </c>
+      <c r="AP17" s="16" t="str" cm="1">
+        <f t="array" ref="AP17">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>.name = "advanced-metallic-asteroid-crushing"
+.icon = "__space-age__\graphics\icons\advanced-metallic-asteroid-crushing.png"
+.order = 
+.enabled = false
+.energy_required = 5
+.ingredients = { { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
+.results = { 
+    { type = "item", name = "iron-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 }, 
+    { type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
+}</v>
+      </c>
+    </row>
+    <row r="18" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="2">
+        <v>5</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="2">
+      <c r="Q18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R18" s="2">
         <v>5</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="str" cm="1">
-        <f t="array" ref="AG16" xml:space="preserve"> "{ " &amp;
+      <c r="S18" s="2">
+        <v>5</v>
+      </c>
+      <c r="T18" s="2">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="W18" s="2">
+        <v>2</v>
+      </c>
+      <c r="X18" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ18" t="str" cm="1">
+        <f t="array" ref="AJ18">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+      <c r="AK18" t="str" cm="1">
+        <f t="array" ref="AK18">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 }</v>
+      </c>
+      <c r="AL18" t="str" cm="1">
+        <f t="array" ref="AL18">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "carbonic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AM18" t="str" cm="1">
+        <f t="array" ref="AM18">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "", amount_min = "", amount_max = "", probability = "" }</v>
+      </c>
+      <c r="AN18" s="15" t="str" cm="1">
+        <f t="array" ref="AN18" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
         <v>{ { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
-    </row>
-    <row r="17" spans="2:33">
-      <c r="B17" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="AO18" s="15" t="str" cm="1">
+        <f t="array" ref="AO18" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 }, 
+    { type = "item", name = "carbonic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
+}</v>
+      </c>
+      <c r="AP18" s="16" t="str" cm="1">
+        <f t="array" ref="AP18">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>.name = "advanced-carbonic-asteroid-crushing"
+.icon = "__space-age__\graphics\icons\advanced-carbonic-asteroid-crushing.png"
+.order = 
+.enabled = false
+.energy_required = 5
+.ingredients = { { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }
+.results = { 
+    { type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 }, 
+    { type = "item", name = "carbonic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
+}</v>
+      </c>
+    </row>
+    <row r="19" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C19" t="s">
         <v>163</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="2">
+      <c r="E19" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="2">
         <v>5</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG17" t="str" cm="1">
-        <f t="array" ref="AG17" xml:space="preserve"> "{ " &amp;
+      <c r="L19" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="2">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R19" s="2">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2">
+        <v>8</v>
+      </c>
+      <c r="T19" s="2">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W19" s="2">
+        <v>10</v>
+      </c>
+      <c r="X19" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ19" t="str" cm="1">
+        <f t="array" ref="AJ19">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }</v>
+      </c>
+      <c r="AK19" t="str" cm="1">
+        <f t="array" ref="AK19">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }</v>
+      </c>
+      <c r="AL19" t="b" cm="1">
+        <f t="array" ref="AL19">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" t="str" cm="1">
+        <f t="array" ref="AM19">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN19" s="15" t="str" cm="1">
+        <f t="array" ref="AN19" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
-      </c>
-    </row>
-    <row r="34" spans="30:30">
-      <c r="AD34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="30:30">
-      <c r="AD35" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="30:30">
-      <c r="AD36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="30:30">
-      <c r="AD37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="30:30">
-      <c r="AD38" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="30:30">
-      <c r="AD39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="30:30">
-      <c r="AD40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="30:30">
-      <c r="AD41" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="30:30">
-      <c r="AD42" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="30:30">
-      <c r="AD43" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="30:30">
-      <c r="AD44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" spans="30:30">
-      <c r="AD45" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="46" spans="30:30">
-      <c r="AD46" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="47" spans="30:30">
-      <c r="AD47" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="30:30">
-      <c r="AD48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" spans="30:30">
-      <c r="AD49" t="s">
-        <v>146</v>
+        <v>{ { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO19" s="15" t="str" cm="1">
+        <f t="array" ref="AO19" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP19" s="16" t="str" cm="1">
+        <f t="array" ref="AP19">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>vulcanis_asteroid_chunk_crushing_adv.name = "vulcanis-asteroid-chunk-crushing-adv"
+vulcanis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanis_asteroid_chunk_crushing_adv.order = "v"
+vulcanis_asteroid_chunk_crushing_adv.enabled = false
+vulcanis_asteroid_chunk_crushing_adv.energy_required = 5
+vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanis_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="20" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="2">
+        <v>5</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" s="2">
+        <v>4</v>
+      </c>
+      <c r="S20" s="2">
+        <v>8</v>
+      </c>
+      <c r="T20" s="2">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W20" s="2">
+        <v>1</v>
+      </c>
+      <c r="X20" s="2">
+        <v>13</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF20" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AG20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ20" t="str" cm="1">
+        <f t="array" ref="AJ20">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }</v>
+      </c>
+      <c r="AK20" t="str" cm="1">
+        <f t="array" ref="AK20">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }</v>
+      </c>
+      <c r="AL20" t="b" cm="1">
+        <f t="array" ref="AL20">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM20" t="str" cm="1">
+        <f t="array" ref="AM20">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN20" s="15" t="str" cm="1">
+        <f t="array" ref="AN20" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO20" s="15" t="str" cm="1">
+        <f t="array" ref="AO20" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP20" s="16" t="str" cm="1">
+        <f t="array" ref="AP20">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>nauvis_asteroid_chunk_crushing_adv.name = "nauvis-asteroid-chunk-crushing-adv"
+nauvis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
+nauvis_asteroid_chunk_crushing_adv.order = "n"
+nauvis_asteroid_chunk_crushing_adv.enabled = false
+nauvis_asteroid_chunk_crushing_adv.energy_required = 5
+nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
+    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="21" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="2">
+        <v>5</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF21" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI21" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ21" t="b" cm="1">
+        <f t="array" ref="AJ21">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AK21" t="b" cm="1">
+        <f t="array" ref="AK21">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL21" t="b" cm="1">
+        <f t="array" ref="AL21">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM21" t="str" cm="1">
+        <f t="array" ref="AM21">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN21" s="15" t="str" cm="1">
+        <f t="array" ref="AN21" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO21" s="15" t="str" cm="1">
+        <f t="array" ref="AO21" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP21" s="16" t="str" cm="1">
+        <f t="array" ref="AP21">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>gleba_asteroid_chunk_crushing_adv.name = "gleba-asteroid-chunk-crushing-adv"
+gleba_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/gleba_crushing_basic.png"
+gleba_asteroid_chunk_crushing_adv.order = "g"
+gleba_asteroid_chunk_crushing_adv.enabled = false
+gleba_asteroid_chunk_crushing_adv.energy_required = 5
+gleba_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }
+gleba_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="22" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="2">
+        <v>5</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R22" s="2">
+        <v>4</v>
+      </c>
+      <c r="S22" s="2">
+        <v>6</v>
+      </c>
+      <c r="T22" s="2">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W22" s="2">
+        <v>35</v>
+      </c>
+      <c r="X22" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ22" t="str" cm="1">
+        <f t="array" ref="AJ22">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }</v>
+      </c>
+      <c r="AK22" t="str" cm="1">
+        <f t="array" ref="AK22">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }</v>
+      </c>
+      <c r="AL22" t="str" cm="1">
+        <f t="array" ref="AL22">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }</v>
+      </c>
+      <c r="AM22" t="str" cm="1">
+        <f t="array" ref="AM22">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN22" s="15" t="str" cm="1">
+        <f t="array" ref="AN22" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO22" s="15" t="str" cm="1">
+        <f t="array" ref="AO22" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
+    { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
+    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP22" s="16" t="str" cm="1">
+        <f t="array" ref="AP22">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>fulgoran_asteroid_chunk_crushing_adv.name = "fulgoran-asteroid-chunk-crushing-adv"
+fulgoran_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_asteroid_chunk_crushing_adv.order = "f"
+fulgoran_asteroid_chunk_crushing_adv.enabled = false
+fulgoran_asteroid_chunk_crushing_adv.energy_required = 5
+fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
+    { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
+    { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
+    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="23" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C23" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="2">
+        <v>5</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="N23" s="2">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="R23" s="2">
+        <v>2000</v>
+      </c>
+      <c r="S23" s="2">
+        <v>2000</v>
+      </c>
+      <c r="T23" s="2">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23" s="2">
+        <v>12</v>
+      </c>
+      <c r="X23" s="2">
+        <v>12</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="str" cm="1">
+        <f t="array" ref="AJ23">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }</v>
+      </c>
+      <c r="AK23" t="str" cm="1">
+        <f t="array" ref="AK23">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 }</v>
+      </c>
+      <c r="AL23" t="b" cm="1">
+        <f t="array" ref="AL23">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM23" t="b" cm="1">
+        <f t="array" ref="AM23">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="15" t="str" cm="1">
+        <f t="array" ref="AN23" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO23" s="15" t="str" cm="1">
+        <f t="array" ref="AO23" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
+}</v>
+      </c>
+      <c r="AP23" s="16" t="str" cm="1">
+        <f t="array" ref="AP23">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>vulcanus_special_crushing.name = "vulcanus-special-crushing"
+vulcanus_special_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanus_special_crushing.order = "v"
+vulcanus_special_crushing.enabled = false
+vulcanus_special_crushing.energy_required = 5
+vulcanus_special_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
+vulcanus_special_crushing.results = { 
+    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
+}</v>
+      </c>
+    </row>
+    <row r="24" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24" s="2">
+        <v>5</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="M24" s="17"/>
+      <c r="N24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="b" cm="1">
+        <f t="array" ref="AJ24">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AK24" t="b" cm="1">
+        <f t="array" ref="AK24">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL24" t="b" cm="1">
+        <f t="array" ref="AL24">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM24" t="b" cm="1">
+        <f t="array" ref="AM24">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="15" t="str" cm="1">
+        <f t="array" ref="AN24" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO24" s="15" t="e" cm="1" vm="1">
+        <f t="array" ref="AO24" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP24" s="16" t="e" cm="1" vm="2">
+        <f t="array" ref="AP24">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C25" t="s">
+        <v>168</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="2">
+        <v>10</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="M25" s="17"/>
+      <c r="N25" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="b" cm="1">
+        <f t="array" ref="AJ25">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b" cm="1">
+        <f t="array" ref="AK25">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" t="b" cm="1">
+        <f t="array" ref="AL25">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" t="b" cm="1">
+        <f t="array" ref="AM25">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="15" t="str" cm="1">
+        <f t="array" ref="AN25" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO25" s="15" t="e" cm="1" vm="1">
+        <f t="array" ref="AO25" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP25" s="16" t="e" cm="1" vm="2">
+        <f t="array" ref="AP25">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K26" s="2">
+        <v>10</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R26" s="2">
+        <v>5</v>
+      </c>
+      <c r="S26" s="2">
+        <v>5</v>
+      </c>
+      <c r="T26" s="2">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="W26" s="2">
+        <v>20</v>
+      </c>
+      <c r="X26" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="str" cm="1">
+        <f t="array" ref="AJ26">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+      <c r="AK26" t="str" cm="1">
+        <f t="array" ref="AK26">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }</v>
+      </c>
+      <c r="AL26" t="str" cm="1">
+        <f t="array" ref="AL26">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 }</v>
+      </c>
+      <c r="AM26" t="b" cm="1">
+        <f t="array" ref="AM26">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN26" s="15" t="str" cm="1">
+        <f t="array" ref="AN26" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk-item", amount = 1 } }</v>
+      </c>
+      <c r="AO26" s="15" t="str" cm="1">
+        <f t="array" ref="AO26" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+}</v>
+      </c>
+      <c r="AP26" s="16" t="str" cm="1">
+        <f t="array" ref="AP26">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>fulgoran_special_crushing.name = "fulgoran-special-crushing"
+fulgoran_special_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_special_crushing.order = "f"
+fulgoran_special_crushing.enabled = false
+fulgoran_special_crushing.energy_required = 10
+fulgoran_special_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk-item", amount = 1 } }
+fulgoran_special_crushing.results = { 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+}</v>
+      </c>
+    </row>
+    <row r="31" spans="3:42">
+      <c r="E31" s="17"/>
+    </row>
+    <row r="32" spans="3:42">
+      <c r="E32" s="17"/>
+    </row>
+    <row r="33" spans="5:42">
+      <c r="E33" s="17"/>
+    </row>
+    <row r="34" spans="5:42">
+      <c r="E34" s="17"/>
+      <c r="AP34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="5:42">
+      <c r="E35" s="17"/>
+      <c r="O35" s="2" t="str" cm="1">
+        <f t="array" ref="O35">_xlfn.TEXTJOIN(", ", TRUE, IF(NOT(ISNUMBER(P35:V35)), """" &amp; P35:V35 &amp; """", P35:V35))</f>
+        <v>"item", "ice", 5, 5, 1, "item", "oxide-asteroid-chunk"</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R35" s="2">
+        <v>5</v>
+      </c>
+      <c r="S35" s="2">
+        <v>5</v>
+      </c>
+      <c r="T35" s="2">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="5:42">
+      <c r="E36" s="17"/>
+      <c r="O36" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE, P36:V36)</f>
+        <v>item, iron-ore, 10, 10, 1, item, copper-ore</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R36" s="2">
+        <v>10</v>
+      </c>
+      <c r="S36" s="2">
+        <v>10</v>
+      </c>
+      <c r="T36" s="2">
+        <v>1</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="5:42">
+      <c r="E37" s="17"/>
+      <c r="AP37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="5:42">
+      <c r="E38" s="17"/>
+      <c r="AP38" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="5:42">
+      <c r="E39" s="17"/>
+      <c r="AP39" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="5:42">
+      <c r="E40" s="17"/>
+      <c r="AP40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" spans="5:42">
+      <c r="E41" s="17"/>
+      <c r="AP41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="5:42">
+      <c r="E42" s="17"/>
+      <c r="AP42" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="5:42">
+      <c r="AL43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="5:42">
+      <c r="AL44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="5:42">
+      <c r="AL45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="5:42">
+      <c r="AL46" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="5:42">
+      <c r="AL47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="5:42">
+      <c r="AL48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="38:38">
+      <c r="AL49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="38:38">
+      <c r="AL50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="38:38">
+      <c r="AL51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="38:38">
+      <c r="AL52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="38:38">
+      <c r="AL53" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="38:38">
+      <c r="AL54" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="38:38">
+      <c r="AL55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="38:38">
+      <c r="AL56" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="38:38">
+      <c r="AL57" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="38:38">
+      <c r="AL58" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AD38:AD49">
-    <sortCondition ref="AD38:AD49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AL47:AL58">
+    <sortCondition ref="AL47:AL58"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B5:AF17">
+  <conditionalFormatting sqref="AA14:AM14 F8:AM13 F14:Y14 C8:E26 F15:AM26 AP8:AP26">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>LEN($C5) &gt; 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:AG8">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>TRUE</formula>
+      <formula>LEN($D8) &gt; 0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4077,6 +7484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A8318C-CA68-4EB8-AA36-1FC23F5E77D3}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:K19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -4113,7 +7521,7 @@
     <row r="5" spans="2:11" ht="15">
       <c r="B5" s="10"/>
       <c r="C5" s="11" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -4124,25 +7532,25 @@
         <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="K5" t="s">
-        <v>205</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="15">
       <c r="B6" s="10"/>
       <c r="C6" s="11" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" ref="I6:I15" si="0">"""item"""</f>
@@ -4159,16 +7567,16 @@
     <row r="7" spans="2:11" ht="15">
       <c r="B7" s="10"/>
       <c r="C7" s="11" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="H7" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
@@ -4185,16 +7593,16 @@
     <row r="8" spans="2:11" ht="15">
       <c r="B8" s="10"/>
       <c r="C8" s="11" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="0"/>
@@ -4211,16 +7619,16 @@
     <row r="9" spans="2:11" ht="15">
       <c r="B9" s="10"/>
       <c r="C9" s="11" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="0"/>
@@ -4237,16 +7645,16 @@
     <row r="10" spans="2:11" ht="15">
       <c r="B10" s="10"/>
       <c r="C10" s="11" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="0"/>
@@ -4263,16 +7671,16 @@
     <row r="11" spans="2:11" ht="15">
       <c r="B11" s="10"/>
       <c r="C11" s="11" t="s">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="H11" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="0"/>
@@ -4289,16 +7697,16 @@
     <row r="12" spans="2:11" ht="15">
       <c r="B12" s="10"/>
       <c r="C12" s="11" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
@@ -4315,16 +7723,16 @@
     <row r="13" spans="2:11" ht="15">
       <c r="B13" s="10"/>
       <c r="C13" s="11" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="H13" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="0"/>
@@ -4341,16 +7749,16 @@
     <row r="14" spans="2:11" ht="15">
       <c r="B14" s="10"/>
       <c r="C14" s="11" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="0"/>
@@ -4367,16 +7775,16 @@
     <row r="15" spans="2:11" ht="15">
       <c r="B15" s="10"/>
       <c r="C15" s="11" t="s">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="H15" t="s">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="0"/>
@@ -4393,7 +7801,7 @@
     <row r="16" spans="2:11" ht="15">
       <c r="B16" s="10"/>
       <c r="C16" s="11" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>

--- a/Astra Notes.xlsx
+++ b/Astra Notes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gwen\Documents\GitHub\Factorio-Astra-Asteroids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noyok\source\repos\Factorio\Factorio-Astra-Asteroids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90A9371-19CA-4D14-8C46-DEFD66685BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3419AE86-DD3D-4054-8C8F-DFBD54D261FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="240" windowWidth="33195" windowHeight="18090" activeTab="1" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -72,25 +72,35 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="255">
   <si>
     <t>Metallic</t>
   </si>
@@ -203,12 +213,6 @@
     <t>"n"</t>
   </si>
   <si>
-    <t>{mining_time = 0.2, result = "nauvis_asteroid_chunk_item"}</t>
-  </si>
-  <si>
-    <t>{mining_time = 0.2, result = "crude_asteroid_chunk_item"}</t>
-  </si>
-  <si>
     <t>enabled</t>
   </si>
   <si>
@@ -347,9 +351,6 @@
     <t>solid-fuel</t>
   </si>
   <si>
-    <t>{mining_time = 0.2, result = "volcanic_asteroid_chunk_item"}</t>
-  </si>
-  <si>
     <t>"v"</t>
   </si>
   <si>
@@ -609,45 +610,6 @@
   </si>
   <si>
     <t>holmium-solution</t>
-  </si>
-  <si>
-    <t>"crude-asteroid-chunk-crushing"</t>
-  </si>
-  <si>
-    <t>"vulcanus-asteroid-chunk-crushing"</t>
-  </si>
-  <si>
-    <t>"nauvis-asteroid-chunk-crushing"</t>
-  </si>
-  <si>
-    <t>"gleba-asteroid-chunk-crushing"</t>
-  </si>
-  <si>
-    <t>"fulgoran-asteroid-chunk-crushing"</t>
-  </si>
-  <si>
-    <t>"nauvis-asteroid-chunk-crushing-adv"</t>
-  </si>
-  <si>
-    <t>"gleba-asteroid-chunk-crushing-adv"</t>
-  </si>
-  <si>
-    <t>"vulcanus-special-crushing"</t>
-  </si>
-  <si>
-    <t>"vulcanis-asteroid-chunk-crushing-adv"</t>
-  </si>
-  <si>
-    <t>"nauvis-special-crushing"</t>
-  </si>
-  <si>
-    <t>"gleba-special-crushing"</t>
-  </si>
-  <si>
-    <t>"fulgoran-special-crushing"</t>
-  </si>
-  <si>
-    <t>"fulgoran-asteroid-chunk-crushing-adv"</t>
   </si>
   <si>
     <t>"g"</t>
@@ -751,24 +713,6 @@
   </si>
   <si>
     <t>Whole String</t>
-  </si>
-  <si>
-    <t>crude-asteroid-chunk-item</t>
-  </si>
-  <si>
-    <t>vulcanic-asteroid-chunk-item</t>
-  </si>
-  <si>
-    <t>nauvis-asteroid-chunk-item</t>
-  </si>
-  <si>
-    <t>gleba-asteroid-chunk-item</t>
-  </si>
-  <si>
-    <t>fulgoran-asteroid-chunk-item</t>
-  </si>
-  <si>
-    <t>carbonic-asteroid-chunk-item</t>
   </si>
   <si>
     <t>"__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"</t>
@@ -1232,36 +1176,6 @@
     <t>recipe settings</t>
   </si>
   <si>
-    <t>"gleba-asteroid-chunk-item"</t>
-  </si>
-  <si>
-    <t>"fulgoran-asteroid-chunk-item"</t>
-  </si>
-  <si>
-    <t>"crude-asteroid-chunk-item"</t>
-  </si>
-  <si>
-    <t>"nauvis-asteroid-chunk-item"</t>
-  </si>
-  <si>
-    <t>"vulcanic-asteroid-chunk-item"</t>
-  </si>
-  <si>
-    <t>"crude-asteroid-chunk"</t>
-  </si>
-  <si>
-    <t>"nauvis-asteroid-chunk"</t>
-  </si>
-  <si>
-    <t>"vulcanic-asteroid-chunk"</t>
-  </si>
-  <si>
-    <t>"gleba-asteroid-chunk"</t>
-  </si>
-  <si>
-    <t>"fulgoran-asteroid-chunk"</t>
-  </si>
-  <si>
     <t>crude_asteroid_chunk</t>
   </si>
   <si>
@@ -1277,12 +1191,6 @@
     <t>"__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"</t>
   </si>
   <si>
-    <t>{mining_time = 0.2, result = "gleba-asteroid-chunk-item"}</t>
-  </si>
-  <si>
-    <t>{mining_time = 0.2, result = "fulgoran-asteroid-chunk-item"}</t>
-  </si>
-  <si>
     <t>vulcanus_asteroid_chunk_item</t>
   </si>
   <si>
@@ -1299,6 +1207,102 @@
   </si>
   <si>
     <t>minable</t>
+  </si>
+  <si>
+    <t>"astra-crude-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"astra-nauvis-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"astra-vulcanic-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"astra-gleba-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>"astra-fulgoran-asteroid-chunk"</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "astra-crude-asteroid-chunk"}</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "astra-nauvis-asteroid-chunk"}</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "astra-volcanic-asteroid-chunk"}</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "astra-gleba-asteroid-chunk"}</t>
+  </si>
+  <si>
+    <t>{mining_time = 0.2, result = "astra-fulgoran-asteroid-chunk"}</t>
+  </si>
+  <si>
+    <t>astra-crude-asteroid-chunk</t>
+  </si>
+  <si>
+    <t>astra-vulcanic-asteroid-chunk</t>
+  </si>
+  <si>
+    <t>astra-nauvis-asteroid-chunk</t>
+  </si>
+  <si>
+    <t>astra-gleba-asteroid-chunk</t>
+  </si>
+  <si>
+    <t>astra-fulgoran-asteroid-chunk</t>
+  </si>
+  <si>
+    <t>"astra-vulcanus-special-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-nauvis-special-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-gleba-special-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-fulgoran-special-crushing"</t>
+  </si>
+  <si>
+    <t>astra-oilstone</t>
+  </si>
+  <si>
+    <t>Adv Crude Crushing</t>
+  </si>
+  <si>
+    <t>crude_asteroid_chunk_crushing_adv</t>
+  </si>
+  <si>
+    <t>"astra-advanced-crude-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-advanced-vulcanis-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-crude-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-vulcanus-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-nauvis-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-gleba-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-fulgoran-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-advanced-nauvis-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-advanced-gleba-asteroid-crushing"</t>
+  </si>
+  <si>
+    <t>"astra-advanced-fulgoran-asteroid-crushing"</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1470,7 +1474,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1492,17 +1495,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="78">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1524,22 +1531,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1555,9 +1546,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1567,10 +1555,104 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
@@ -1667,85 +1749,16 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1801,12 +1814,18 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
+    <v>1</v>
+    <v>8</v>
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="1">
     <v>13</v>
     <v>3</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>13</v>
     <v>1</v>
   </rv>
@@ -1814,7 +1833,13 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
   <s t="_error">
     <k n="errorType" t="i"/>
     <k n="subType" t="i"/>
@@ -1827,50 +1852,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="70">
   <autoFilter ref="B3:AB25" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{B1A354A2-D591-4F7C-89E1-AB75527E5993}" name="Recipe"/>
-    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="46">
+    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="69">
       <calculatedColumnFormula>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="39">
+    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="62">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(J$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="38">
+    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="61">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(K$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="35">
+    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="58">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(N$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="32"/>
-    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="30"/>
-    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="29"/>
-    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="28"/>
-    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="27"/>
-    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="24"/>
-    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="23"/>
-    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="21"/>
+    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="57"/>
+    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="55"/>
+    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="52"/>
+    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="51"/>
+    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="50"/>
+    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="49"/>
+    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="48"/>
+    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="47"/>
+    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="46"/>
+    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="45"/>
+    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1885,18 +1910,18 @@
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{EFD8865D-C9ED-4BA8-B73C-113EDAD68DA5}" name="Variable's Name"/>
     <tableColumn id="3" xr3:uid="{1A67492A-77CF-48AB-9609-594DA5CCF328}" name="name"/>
-    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="20">
+    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="77">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="19">
+    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="76">
       <calculatedColumnFormula>"""space-material"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{A45CDEC7-39DE-4333-8E31-011D04DA2762}" name="order"/>
     <tableColumn id="6" xr3:uid="{499C643B-C1ED-4A32-BE42-9946CC52BC6E}" name="icon"/>
-    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="18">
+    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="75">
       <calculatedColumnFormula>1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9145470B-0772-4705-8B45-24698F613F56}" name="full string" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{9145470B-0772-4705-8B45-24698F613F56}" name="full string" dataDxfId="74">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</calculatedColumnFormula>
     </tableColumn>
@@ -1914,13 +1939,13 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9C8B2B85-651A-48F5-BE74-6B0CB5EC6401}" name="Variable's Name"/>
     <tableColumn id="3" xr3:uid="{5CB5E631-FE01-4CDD-A4B3-008A4C86A223}" name="name"/>
-    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="73">
       <calculatedColumnFormula>"""asteroid-chunk"""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable" dataDxfId="72"/>
     <tableColumn id="5" xr3:uid="{2D398BB0-41AE-40CE-AA0F-6FA6647FFA57}" name="order"/>
     <tableColumn id="6" xr3:uid="{82F86FA9-1FFF-4AFF-A528-DD559BDA3930}" name="icon"/>
-    <tableColumn id="7" xr3:uid="{8D2BAF1D-A998-4CFE-AE20-A7C5A809314F}" name="full string" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{8D2BAF1D-A998-4CFE-AE20-A7C5A809314F}" name="full string" dataDxfId="71">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</calculatedColumnFormula>
     </tableColumn>
@@ -1930,89 +1955,89 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="C7:AP26" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="C7:AP26" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:AN26">
-    <sortCondition descending="1" ref="C7:C26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="C7:AP27" totalsRowShown="0" headerRowDxfId="43">
+  <autoFilter ref="C7:AP27" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:AN27">
+    <sortCondition descending="1" ref="C7:C27"/>
   </sortState>
   <tableColumns count="40">
     <tableColumn id="1" xr3:uid="{1C7B22C3-8503-40CA-B985-0F11F98EB3C6}" name="Recipe"/>
-    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="76"/>
-    <tableColumn id="41" xr3:uid="{6E5608DA-75C3-48D4-92AF-824B8C6B9141}" name="Advanced?" dataDxfId="10">
+    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="42"/>
+    <tableColumn id="41" xr3:uid="{6E5608DA-75C3-48D4-92AF-824B8C6B9141}" name="Advanced?" dataDxfId="41">
       <calculatedColumnFormula>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{D73BFE2A-2B7F-460C-B8F4-2293AE8F1CDF}" name="Variable's Name" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="72"/>
-    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{8EF822E8-07FB-4876-8800-25F2A9B81873}" name="Result_1_type" dataDxfId="70"/>
-    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="69"/>
-    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="68"/>
-    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="67"/>
-    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="66"/>
-    <tableColumn id="34" xr3:uid="{F666EFD4-EFAB-4ED2-9F8C-93F381615487}" name="Result_2_type" dataDxfId="65"/>
-    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="64"/>
-    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="63"/>
-    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="62"/>
-    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="61"/>
-    <tableColumn id="35" xr3:uid="{29FDA9C5-AC15-474C-B065-A8F35BA59418}" name="Result_3_type" dataDxfId="60"/>
-    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="59"/>
-    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="58"/>
-    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="57"/>
-    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="56"/>
-    <tableColumn id="36" xr3:uid="{5C2D1484-E711-4E82-92DB-57B04BD66315}" name="Result_4_type" dataDxfId="55"/>
-    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="54"/>
-    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="53"/>
-    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="52"/>
-    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1" dataDxfId="50">
+    <tableColumn id="39" xr3:uid="{D73BFE2A-2B7F-460C-B8F4-2293AE8F1CDF}" name="Variable's Name" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="36"/>
+    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{8EF822E8-07FB-4876-8800-25F2A9B81873}" name="Result_1_type" dataDxfId="30"/>
+    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="29"/>
+    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="28"/>
+    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="27"/>
+    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="26"/>
+    <tableColumn id="34" xr3:uid="{F666EFD4-EFAB-4ED2-9F8C-93F381615487}" name="Result_2_type" dataDxfId="25"/>
+    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="24"/>
+    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="23"/>
+    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="21"/>
+    <tableColumn id="35" xr3:uid="{29FDA9C5-AC15-474C-B065-A8F35BA59418}" name="Result_3_type" dataDxfId="20"/>
+    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="19"/>
+    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="18"/>
+    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="16"/>
+    <tableColumn id="36" xr3:uid="{5C2D1484-E711-4E82-92DB-57B04BD66315}" name="Result_4_type" dataDxfId="15"/>
+    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1" dataDxfId="10">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2" dataDxfId="49">
+    <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2" dataDxfId="9">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3" dataDxfId="48">
+    <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3" dataDxfId="8">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4" dataDxfId="14">
+    <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4" dataDxfId="7">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="13">
+    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="6">
       <calculatedColumnFormula array="1" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{D9725653-650B-4E33-86E4-FA48D30F5455}" name="Results String" dataDxfId="12">
+    <tableColumn id="37" xr3:uid="{D9725653-650B-4E33-86E4-FA48D30F5455}" name="Results String" dataDxfId="5">
       <calculatedColumnFormula array="1" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{6A447D5A-EAF2-404F-A826-F6177D7B50D6}" name="Whole String" dataDxfId="11">
+    <tableColumn id="40" xr3:uid="{6A447D5A-EAF2-404F-A826-F6177D7B50D6}" name="Whole String" dataDxfId="4">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -2028,11 +2053,11 @@
   <autoFilter ref="H5:K15" xr:uid="{8FC02366-D4DD-41A4-8050-773DDA42B27E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{959EF51D-F84A-47B3-BB90-19C907903580}" name="name"/>
-    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="17">
+    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="3">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{214E8F8E-48B4-4BB8-B3A1-54F2A217D484}" name="amount"/>
-    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="16">
+    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="2">
       <calculatedColumnFormula array="1">"    { " &amp; _xlfn.TEXTJOIN(", ", TRUE, Table1[[#Headers],[name]:[amount]] &amp; " = " &amp; Table1[[#This Row],[name]:[amount]]) &amp; " }"</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2378,64 +2403,64 @@
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>7</v>
@@ -2611,7 +2636,7 @@
     </row>
     <row r="7" spans="2:28" ht="27.75" customHeight="1">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2">
         <f>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</f>
@@ -2663,7 +2688,7 @@
         <f t="array" ref="K7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(K$3, _xlpm.recipeResults))), " - ") )</f>
-        <v>{ type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 }</v>
+        <v xml:space="preserve"> - </v>
       </c>
       <c r="L7" s="9" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
@@ -2671,11 +2696,11 @@
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(L$3, _xlpm.recipeResults))), " - ") )</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="M7" s="8" t="str" cm="1">
-        <f t="array" ref="M7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
+      <c r="M7" s="8" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="M7" ca="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(M$3, _xlpm.recipeResults))), " - ") )</f>
-        <v xml:space="preserve"> - </v>
+        <v>#VALUE!</v>
       </c>
       <c r="N7" s="8" t="str" cm="1">
         <f t="array" ref="N7">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
@@ -2770,7 +2795,7 @@
     </row>
     <row r="8" spans="2:28">
       <c r="B8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2">
         <f>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</f>
@@ -3249,7 +3274,7 @@
     </row>
     <row r="17" spans="2:35">
       <c r="B17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2">
         <f>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</f>
@@ -3396,13 +3421,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="str">
-        <v>{ type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+        <v>{ type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
       </c>
       <c r="AI17" t="str">
         <v>{ 
     { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
@@ -3454,7 +3479,7 @@
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-      <c r="AI18" t="e" cm="1" vm="1">
+      <c r="AI18" t="e" cm="1" vm="2">
         <f t="array" ref="AI18">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(Table4[[#Headers],[stone]], _xlpm.recipeResults))) )</f>
         <v>#VALUE!</v>
@@ -3729,7 +3754,7 @@
         <v>13</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:35">
@@ -3781,7 +3806,7 @@
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
       <c r="AE24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="2:35">
@@ -3847,7 +3872,7 @@
         <v>#N/A</v>
       </c>
       <c r="AE28" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="2:35">
@@ -3895,7 +3920,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B17:AB17">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3913,13 +3938,13 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="3" max="3" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="27.875" customWidth="1"/>
     <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="16.75" customWidth="1"/>
     <col min="11" max="11" width="23.75" customWidth="1"/>
     <col min="12" max="12" width="16.625" customWidth="1"/>
     <col min="13" max="13" width="35" bestFit="1" customWidth="1"/>
@@ -3933,9 +3958,9 @@
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B2" s="18" t="str" cm="1">
+        <v>210</v>
+      </c>
+      <c r="B2" s="17" t="str" cm="1">
         <f t="array" ref="B2">_xlfn.TEXTJOIN("
 ", TRUE, "local " &amp; Chunk_Items[Variable''s Name] &amp; " = " &amp; $B$6)</f>
         <v>local crude_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])
@@ -3945,9 +3970,9 @@
 local fulgora_asteroid_chunk_item = table.deepcopy(data.raw.item["metallic-asteroid-chunk"])</v>
       </c>
       <c r="J2" t="s">
-        <v>232</v>
-      </c>
-      <c r="K2" s="18" t="str" cm="1">
+        <v>210</v>
+      </c>
+      <c r="K2" s="17" t="str" cm="1">
         <f t="array" ref="K2">_xlfn.TEXTJOIN("
 ", TRUE, "local " &amp; Chunks[Variable''s Name] &amp; " = " &amp; $K$6)</f>
         <v>local crude_asteroid_chunk = table.deepcopy(data.raw["asteroid-chunk"]["metallic-asteroid-chunk"])
@@ -3960,36 +3985,36 @@
     <row r="3" spans="1:17" ht="15.75" thickTop="1" thickBot="1"/>
     <row r="4" spans="1:17" ht="19.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B4" s="13" t="str">
+        <v>211</v>
+      </c>
+      <c r="B4" s="12" t="str">
         <f>_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[full string])</f>
-        <v>crude_asteroid_chunk_item.name = "crude-asteroid-chunk-item"
+        <v>crude_asteroid_chunk_item.name = "astra-crude-asteroid-chunk"
 crude_asteroid_chunk_item.type = "item"
 crude_asteroid_chunk_item.subgroup = "space-material"
 crude_asteroid_chunk_item.order = "f"
 crude_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"
 crude_asteroid_chunk_item.stack_size = 1
-nauvis_asteroid_chunk_item.name = "nauvis-asteroid-chunk-item"
+nauvis_asteroid_chunk_item.name = "astra-nauvis-asteroid-chunk"
 nauvis_asteroid_chunk_item.type = "item"
 nauvis_asteroid_chunk_item.subgroup = "space-material"
 nauvis_asteroid_chunk_item.order = "f"
 nauvis_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"
 nauvis_asteroid_chunk_item.stack_size = 1
-vulcanus_asteroid_chunk_item.name = "vulcanic-asteroid-chunk-item"
+vulcanus_asteroid_chunk_item.name = "astra-vulcanic-asteroid-chunk"
 vulcanus_asteroid_chunk_item.type = "item"
 vulcanus_asteroid_chunk_item.subgroup = "space-material"
 vulcanus_asteroid_chunk_item.order = "v"
 vulcanus_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"
 vulcanus_asteroid_chunk_item.stack_size = 1
-gleba_asteroid_chunk_item.name = "gleba-asteroid-chunk-item"
+gleba_asteroid_chunk_item.name = "astra-gleba-asteroid-chunk"
 gleba_asteroid_chunk_item.type = "item"
 gleba_asteroid_chunk_item.subgroup = "space-material"
 gleba_asteroid_chunk_item.order = "g"
 gleba_asteroid_chunk_item.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"
 gleba_asteroid_chunk_item.stack_size = 1
-fulgora_asteroid_chunk_item.name = "fulgoran-asteroid-chunk-item"
+fulgora_asteroid_chunk_item.name = "astra-fulgoran-asteroid-chunk"
 fulgora_asteroid_chunk_item.type = "item"
 fulgora_asteroid_chunk_item.subgroup = "space-material"
 fulgora_asteroid_chunk_item.order = "f"
@@ -3997,34 +4022,34 @@
 fulgora_asteroid_chunk_item.stack_size = 1</v>
       </c>
       <c r="J4" t="s">
-        <v>233</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>211</v>
+      </c>
+      <c r="K4" s="12" t="str">
         <f>_xlfn.TEXTJOIN("
 ", TRUE, Chunks[full string])</f>
-        <v>crude_asteroid_chunk.name = "crude-asteroid-chunk"
+        <v>crude_asteroid_chunk.name = "astra-crude-asteroid-chunk"
 crude_asteroid_chunk.type = "asteroid-chunk"
-crude_asteroid_chunk.minable = {mining_time = 0.2, result = "crude_asteroid_chunk_item"}
+crude_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-crude-asteroid-chunk"}
 crude_asteroid_chunk.order = "f"
 crude_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"
-nauvis_asteroid_chunk.name = "nauvis-asteroid-chunk"
+nauvis_asteroid_chunk.name = "astra-nauvis-asteroid-chunk"
 nauvis_asteroid_chunk.type = "asteroid-chunk"
-nauvis_asteroid_chunk.minable = {mining_time = 0.2, result = "nauvis_asteroid_chunk_item"}
+nauvis_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-nauvis-asteroid-chunk"}
 nauvis_asteroid_chunk.order = "n"
 nauvis_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"
-vulcanus_asteroid_chunk.name = "vulcanic-asteroid-chunk"
+vulcanus_asteroid_chunk.name = "astra-vulcanic-asteroid-chunk"
 vulcanus_asteroid_chunk.type = "asteroid-chunk"
-vulcanus_asteroid_chunk.minable = {mining_time = 0.2, result = "volcanic_asteroid_chunk_item"}
+vulcanus_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-volcanic-asteroid-chunk"}
 vulcanus_asteroid_chunk.order = "v"
 vulcanus_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"
-gleba_asteroid_chunk.name = "gleba-asteroid-chunk"
+gleba_asteroid_chunk.name = "astra-gleba-asteroid-chunk"
 gleba_asteroid_chunk.type = "asteroid-chunk"
-gleba_asteroid_chunk.minable = {mining_time = 0.2, result = "gleba-asteroid-chunk-item"}
+gleba_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-gleba-asteroid-chunk"}
 gleba_asteroid_chunk.order = "g"
 gleba_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"
-fulgora_asteroid_chunk.name = "fulgoran-asteroid-chunk"
+fulgora_asteroid_chunk.name = "astra-fulgoran-asteroid-chunk"
 fulgora_asteroid_chunk.type = "asteroid-chunk"
-fulgora_asteroid_chunk.minable = {mining_time = 0.2, result = "fulgoran-asteroid-chunk-item"}
+fulgora_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-fulgoran-asteroid-chunk"}
 fulgora_asteroid_chunk.order = "f"
 fulgora_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"</v>
       </c>
@@ -4033,18 +4058,18 @@
       <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:17" ht="15">
-      <c r="B6" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="K6" s="14" t="s">
-        <v>223</v>
+      <c r="B6" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="K6" s="13" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="B8" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
@@ -4065,10 +4090,10 @@
         <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="K8" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
@@ -4077,7 +4102,7 @@
         <v>29</v>
       </c>
       <c r="N8" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="O8" t="s">
         <v>32</v>
@@ -4086,15 +4111,15 @@
         <v>33</v>
       </c>
       <c r="Q8" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="B9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D9" t="str">
         <f>"""item"""</f>
@@ -4108,7 +4133,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="H9">
         <f>1</f>
@@ -4117,7 +4142,7 @@
       <c r="I9" t="str" cm="1">
         <f t="array" ref="I9">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
-        <v>crude_asteroid_chunk_item.name = "crude-asteroid-chunk-item"
+        <v>crude_asteroid_chunk_item.name = "astra-crude-asteroid-chunk"
 crude_asteroid_chunk_item.type = "item"
 crude_asteroid_chunk_item.subgroup = "space-material"
 crude_asteroid_chunk_item.order = "f"
@@ -4125,40 +4150,40 @@
 crude_asteroid_chunk_item.stack_size = 1</v>
       </c>
       <c r="K9" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="L9" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="M9" t="str">
         <f>"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="O9" t="s">
         <v>35</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="Q9" t="str" cm="1">
         <f t="array" ref="Q9">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
-        <v>crude_asteroid_chunk.name = "crude-asteroid-chunk"
+        <v>crude_asteroid_chunk.name = "astra-crude-asteroid-chunk"
 crude_asteroid_chunk.type = "asteroid-chunk"
-crude_asteroid_chunk.minable = {mining_time = 0.2, result = "crude_asteroid_chunk_item"}
+crude_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-crude-asteroid-chunk"}
 crude_asteroid_chunk.order = "f"
 crude_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/crude_asteroid_chunk.png"</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="B10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D10" t="str">
         <f>"""item"""</f>
@@ -4172,7 +4197,7 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="H10">
         <f>1</f>
@@ -4181,7 +4206,7 @@
       <c r="I10" t="str" cm="1">
         <f t="array" ref="I10">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
-        <v>nauvis_asteroid_chunk_item.name = "nauvis-asteroid-chunk-item"
+        <v>nauvis_asteroid_chunk_item.name = "astra-nauvis-asteroid-chunk"
 nauvis_asteroid_chunk_item.type = "item"
 nauvis_asteroid_chunk_item.subgroup = "space-material"
 nauvis_asteroid_chunk_item.order = "f"
@@ -4189,40 +4214,40 @@
 nauvis_asteroid_chunk_item.stack_size = 1</v>
       </c>
       <c r="K10" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="L10" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M10" t="str">
         <f>"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
       <c r="N10" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="O10" t="s">
         <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="Q10" t="str" cm="1">
         <f t="array" ref="Q10">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
-        <v>nauvis_asteroid_chunk.name = "nauvis-asteroid-chunk"
+        <v>nauvis_asteroid_chunk.name = "astra-nauvis-asteroid-chunk"
 nauvis_asteroid_chunk.type = "asteroid-chunk"
-nauvis_asteroid_chunk.minable = {mining_time = 0.2, result = "nauvis_asteroid_chunk_item"}
+nauvis_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-nauvis-asteroid-chunk"}
 nauvis_asteroid_chunk.order = "n"
 nauvis_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/nauvis_asteroid_chunk.png"</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="B11" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="C11" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D11" t="str">
         <f>"""item"""</f>
@@ -4233,10 +4258,10 @@
         <v>"space-material"</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="H11">
         <f>1</f>
@@ -4245,7 +4270,7 @@
       <c r="I11" t="str" cm="1">
         <f t="array" ref="I11">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
-        <v>vulcanus_asteroid_chunk_item.name = "vulcanic-asteroid-chunk-item"
+        <v>vulcanus_asteroid_chunk_item.name = "astra-vulcanic-asteroid-chunk"
 vulcanus_asteroid_chunk_item.type = "item"
 vulcanus_asteroid_chunk_item.subgroup = "space-material"
 vulcanus_asteroid_chunk_item.order = "v"
@@ -4253,63 +4278,63 @@
 vulcanus_asteroid_chunk_item.stack_size = 1</v>
       </c>
       <c r="K11" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="L11" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="M11" t="str">
         <f>"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
       <c r="N11" t="s">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="O11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="Q11" t="str" cm="1">
         <f t="array" ref="Q11">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
-        <v>vulcanus_asteroid_chunk.name = "vulcanic-asteroid-chunk"
+        <v>vulcanus_asteroid_chunk.name = "astra-vulcanic-asteroid-chunk"
 vulcanus_asteroid_chunk.type = "asteroid-chunk"
-vulcanus_asteroid_chunk.minable = {mining_time = 0.2, result = "volcanic_asteroid_chunk_item"}
+vulcanus_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-volcanic-asteroid-chunk"}
 vulcanus_asteroid_chunk.order = "v"
 vulcanus_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/vulcanus_asteroid_chunk.png"</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="B12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>234</v>
-      </c>
-      <c r="D12" s="12" t="str">
+        <v>226</v>
+      </c>
+      <c r="D12" t="str">
         <f>"""item"""</f>
         <v>"item"</v>
       </c>
-      <c r="E12" s="12" t="str">
+      <c r="E12" t="str">
         <f>"""space-material"""</f>
         <v>"space-material"</v>
       </c>
       <c r="F12" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="G12" t="s">
-        <v>247</v>
-      </c>
-      <c r="H12" s="12">
+        <v>215</v>
+      </c>
+      <c r="H12">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I12" s="12" t="str" cm="1">
+      <c r="I12" t="str" cm="1">
         <f t="array" ref="I12">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
-        <v>gleba_asteroid_chunk_item.name = "gleba-asteroid-chunk-item"
+        <v>gleba_asteroid_chunk_item.name = "astra-gleba-asteroid-chunk"
 gleba_asteroid_chunk_item.type = "item"
 gleba_asteroid_chunk_item.subgroup = "space-material"
 gleba_asteroid_chunk_item.order = "g"
@@ -4317,46 +4342,46 @@
 gleba_asteroid_chunk_item.stack_size = 1</v>
       </c>
       <c r="K12" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="L12" t="s">
-        <v>242</v>
-      </c>
-      <c r="M12" s="12" t="str">
+        <v>226</v>
+      </c>
+      <c r="M12" t="str">
         <f t="shared" ref="M12:M13" si="0">"""asteroid-chunk"""</f>
         <v>"asteroid-chunk"</v>
       </c>
-      <c r="N12" s="12" t="s">
-        <v>249</v>
+      <c r="N12" t="s">
+        <v>231</v>
       </c>
       <c r="O12" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="Q12" t="str" cm="1">
         <f t="array" ref="Q12">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
-        <v>gleba_asteroid_chunk.name = "gleba-asteroid-chunk"
+        <v>gleba_asteroid_chunk.name = "astra-gleba-asteroid-chunk"
 gleba_asteroid_chunk.type = "asteroid-chunk"
-gleba_asteroid_chunk.minable = {mining_time = 0.2, result = "gleba-asteroid-chunk-item"}
+gleba_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-gleba-asteroid-chunk"}
 gleba_asteroid_chunk.order = "g"
 gleba_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/gleba_asteroid_chunk.png"</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="B13" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" s="12" t="str">
+        <v>227</v>
+      </c>
+      <c r="D13" t="str">
         <f>"""item"""</f>
         <v>"item"</v>
       </c>
-      <c r="E13" s="12" t="str">
+      <c r="E13" t="str">
         <f>"""space-material"""</f>
         <v>"space-material"</v>
       </c>
@@ -4364,16 +4389,16 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>248</v>
-      </c>
-      <c r="H13" s="12">
+        <v>216</v>
+      </c>
+      <c r="H13">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="I13" s="12" t="str" cm="1">
+      <c r="I13" t="str" cm="1">
         <f t="array" ref="I13">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</f>
-        <v>fulgora_asteroid_chunk_item.name = "fulgoran-asteroid-chunk-item"
+        <v>fulgora_asteroid_chunk_item.name = "astra-fulgoran-asteroid-chunk"
 fulgora_asteroid_chunk_item.type = "item"
 fulgora_asteroid_chunk_item.subgroup = "space-material"
 fulgora_asteroid_chunk_item.order = "f"
@@ -4381,30 +4406,30 @@
 fulgora_asteroid_chunk_item.stack_size = 1</v>
       </c>
       <c r="K13" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="L13" t="s">
-        <v>243</v>
-      </c>
-      <c r="M13" s="12" t="str">
+        <v>227</v>
+      </c>
+      <c r="M13" t="str">
         <f t="shared" si="0"/>
         <v>"asteroid-chunk"</v>
       </c>
-      <c r="N13" s="12" t="s">
-        <v>250</v>
+      <c r="N13" t="s">
+        <v>232</v>
       </c>
       <c r="O13" t="s">
         <v>35</v>
       </c>
       <c r="P13" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="Q13" t="str" cm="1">
         <f t="array" ref="Q13">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</f>
-        <v>fulgora_asteroid_chunk.name = "fulgoran-asteroid-chunk"
+        <v>fulgora_asteroid_chunk.name = "astra-fulgoran-asteroid-chunk"
 fulgora_asteroid_chunk.type = "asteroid-chunk"
-fulgora_asteroid_chunk.minable = {mining_time = 0.2, result = "fulgoran-asteroid-chunk-item"}
+fulgora_asteroid_chunk.minable = {mining_time = 0.2, result = "astra-fulgoran-asteroid-chunk"}
 fulgora_asteroid_chunk.order = "f"
 fulgora_asteroid_chunk.icon = "__Astra-Asteroids__/graphics/fulgoran_asteroid_chunk.png"</v>
       </c>
@@ -4436,7 +4461,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA672A5-FC41-4490-AF8C-1F6ADD4F213B}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B1:AQ58"/>
+  <dimension ref="B1:AQ59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -4445,20 +4470,14 @@
     <col min="4" max="4" width="6.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="27.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="44.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="63.625" style="2" customWidth="1"/>
     <col min="9" max="9" width="13.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
-    <col min="11" max="12" width="11.125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="27.5" style="2" customWidth="1"/>
-    <col min="15" max="16" width="8.5" style="2" customWidth="1"/>
-    <col min="17" max="18" width="9.375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="11.125" style="2" customWidth="1"/>
-    <col min="20" max="22" width="9.375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="10.75" style="2" customWidth="1"/>
-    <col min="24" max="27" width="9.375" style="2" customWidth="1"/>
-    <col min="28" max="28" width="20.5" style="2" customWidth="1"/>
-    <col min="29" max="32" width="9.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.125" style="2" customWidth="1"/>
+    <col min="12" max="17" width="9.75" style="2" customWidth="1"/>
+    <col min="18" max="23" width="13.25" style="2" customWidth="1"/>
+    <col min="24" max="32" width="13.125" style="2" customWidth="1"/>
     <col min="33" max="33" width="15.5" style="2" customWidth="1"/>
     <col min="34" max="35" width="9.375" style="2" customWidth="1"/>
     <col min="36" max="36" width="11.25" style="2" hidden="1" customWidth="1"/>
@@ -4471,143 +4490,133 @@
     <row r="1" spans="2:43" ht="16.5" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:43" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="B2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="18" t="str" cm="1">
+        <v>210</v>
+      </c>
+      <c r="C2" s="17" t="str" cm="1">
         <f t="array" ref="C2">_xlfn.TEXTJOIN("
 ", TRUE, _xlfn._xlws.FILTER("local " &amp; Table7[Variable''s Name] &amp; " = " &amp; IF(Table7[Advanced?], advRecipeCopy, baseRecipeCopy), ISBLANK(Table7[Unwritten?])))</f>
         <v>local crude_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
 local vulcanus_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
 local nauvis_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
 local fulgoran_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
+local crude_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
 local vulcanis_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
 local nauvis_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
-local fulgoran_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
-local vulcanus_special_crushing = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
-local fulgoran_special_crushing = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])</v>
+local fulgoran_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])</v>
       </c>
     </row>
     <row r="3" spans="2:43" ht="16.5" customHeight="1" thickTop="1" thickBot="1"/>
     <row r="4" spans="2:43" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="B4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C4" s="13" t="str" cm="1">
+        <v>211</v>
+      </c>
+      <c r="C4" s="12" t="str" cm="1">
         <f t="array" ref="C4">_xlfn.TEXTJOIN("
 ", TRUE, _xlfn._xlws.FILTER(Table7[Whole String], ISBLANK(Table7[Unwritten?])))</f>
-        <v>crude_asteroid_chunk_crushing.name = "crude-asteroid-chunk-crushing"
+        <v>crude_asteroid_chunk_crushing.name = "astra-crude-asteroid-crushing"
 crude_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
 crude_asteroid_chunk_crushing.order = "a"
 crude_asteroid_chunk_crushing.enabled = false
 crude_asteroid_chunk_crushing.energy_required = 2
-crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "crude-asteroid-chunk-item", amount = 1 } }
+crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }
 crude_asteroid_chunk_crushing.results = { 
-    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 } 
 }
-vulcanus_asteroid_chunk_crushing.name = "vulcanus-asteroid-chunk-crushing"
+vulcanus_asteroid_chunk_crushing.name = "astra-vulcanus-asteroid-crushing"
 vulcanus_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
 vulcanus_asteroid_chunk_crushing.order = "v"
 vulcanus_asteroid_chunk_crushing.enabled = false
 vulcanus_asteroid_chunk_crushing.energy_required = 2
-vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }
 vulcanus_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
-    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }
-nauvis_asteroid_chunk_crushing.name = "nauvis-asteroid-chunk-crushing"
+nauvis_asteroid_chunk_crushing.name = "astra-nauvis-asteroid-crushing"
 nauvis_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
 nauvis_asteroid_chunk_crushing.order = "n"
 nauvis_asteroid_chunk_crushing.enabled = false
 nauvis_asteroid_chunk_crushing.energy_required = 2
-nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }
 nauvis_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }
-fulgoran_asteroid_chunk_crushing.name = "fulgoran-asteroid-chunk-crushing"
+fulgoran_asteroid_chunk_crushing.name = "astra-fulgoran-asteroid-crushing"
 fulgoran_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
 fulgoran_asteroid_chunk_crushing.order = "f"
 fulgoran_asteroid_chunk_crushing.enabled = false
 fulgoran_asteroid_chunk_crushing.energy_required = 2
-fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }
 fulgoran_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
-    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }
-vulcanis_asteroid_chunk_crushing_adv.name = "vulcanis-asteroid-chunk-crushing-adv"
+crude_asteroid_chunk_crushing_adv.name = "astra-advanced-crude-asteroid-crushing"
+crude_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+crude_asteroid_chunk_crushing_adv.order = "a"
+crude_asteroid_chunk_crushing_adv.enabled = FALSE
+crude_asteroid_chunk_crushing_adv.energy_required = 5
+crude_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }
+crude_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}
+vulcanis_asteroid_chunk_crushing_adv.name = "astra-advanced-vulcanis-asteroid-crushing"
 vulcanis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
 vulcanis_asteroid_chunk_crushing_adv.order = "v"
 vulcanis_asteroid_chunk_crushing_adv.enabled = false
 vulcanis_asteroid_chunk_crushing_adv.energy_required = 5
-vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }
 vulcanis_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }
-nauvis_asteroid_chunk_crushing_adv.name = "nauvis-asteroid-chunk-crushing-adv"
+nauvis_asteroid_chunk_crushing_adv.name = "astra-advanced-nauvis-asteroid-crushing"
 nauvis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
 nauvis_asteroid_chunk_crushing_adv.order = "n"
 nauvis_asteroid_chunk_crushing_adv.enabled = false
 nauvis_asteroid_chunk_crushing_adv.energy_required = 5
-nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }
 nauvis_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }
-fulgoran_asteroid_chunk_crushing_adv.name = "fulgoran-asteroid-chunk-crushing-adv"
+fulgoran_asteroid_chunk_crushing_adv.name = "astra-advanced-fulgoran-asteroid-crushing"
 fulgoran_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
 fulgoran_asteroid_chunk_crushing_adv.order = "f"
 fulgoran_asteroid_chunk_crushing_adv.enabled = false
 fulgoran_asteroid_chunk_crushing_adv.energy_required = 5
-fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }
 fulgoran_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
     { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
-    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
-}
-vulcanus_special_crushing.name = "vulcanus-special-crushing"
-vulcanus_special_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
-vulcanus_special_crushing.order = "v"
-vulcanus_special_crushing.enabled = false
-vulcanus_special_crushing.energy_required = 5
-vulcanus_special_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
-vulcanus_special_crushing.results = { 
-    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
-}
-fulgoran_special_crushing.name = "fulgoran-special-crushing"
-fulgoran_special_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
-fulgoran_special_crushing.order = "f"
-fulgoran_special_crushing.enabled = false
-fulgoran_special_crushing.energy_required = 10
-fulgoran_special_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk-item", amount = 1 } }
-fulgoran_special_crushing.results = { 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>225</v>
+      <c r="G4" s="13" t="s">
+        <v>203</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:43" ht="16.5" customHeight="1" thickTop="1">
-      <c r="G5" s="14" t="s">
-        <v>226</v>
+      <c r="G5" s="13" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="2:43">
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:43" s="1" customFormat="1" ht="52.5" customHeight="1">
@@ -4615,13 +4624,13 @@
         <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>30</v>
@@ -4633,108 +4642,108 @@
         <v>32</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="AO7" s="1" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="2:43" ht="18.75" customHeight="1">
       <c r="C8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>13</v>
@@ -4744,29 +4753,29 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="L8" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="M8" s="17"/>
+      <c r="L8" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="M8" s="16"/>
       <c r="N8" s="2">
         <v>1</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R8" s="2">
         <v>5</v>
@@ -4778,10 +4787,10 @@
         <v>1</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="W8" s="2">
         <v>1</v>
@@ -4824,7 +4833,7 @@
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN8" s="15" t="str" cm="1">
+      <c r="AN8" s="14" t="str" cm="1">
         <f t="array" ref="AN8" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -4832,7 +4841,7 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO8" s="15" t="str" cm="1">
+      <c r="AO8" s="14" t="str" cm="1">
         <f t="array" ref="AO8" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -4842,7 +4851,7 @@
     { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
 }</v>
       </c>
-      <c r="AP8" s="16" t="str" cm="1">
+      <c r="AP8" s="15" t="str" cm="1">
         <f t="array" ref="AP8">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -4869,7 +4878,7 @@
     </row>
     <row r="9" spans="2:43" ht="18.75" customHeight="1">
       <c r="C9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>13</v>
@@ -4879,21 +4888,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K9" s="2">
         <v>2</v>
       </c>
-      <c r="L9" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="17"/>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16"/>
       <c r="N9" s="2">
         <v>1</v>
       </c>
@@ -4935,7 +4944,7 @@
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN9" s="15" t="str" cm="1">
+      <c r="AN9" s="14" t="str" cm="1">
         <f t="array" ref="AN9" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -4943,14 +4952,14 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO9" s="15" t="e" cm="1" vm="1">
+      <c r="AO9" s="14" t="e" cm="1" vm="2">
         <f t="array" ref="AO9" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP9" s="16" t="e" cm="1" vm="2">
+      <c r="AP9" s="15" t="e" cm="1" vm="3">
         <f t="array" ref="AP9">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -4960,60 +4969,63 @@
     </row>
     <row r="10" spans="2:43" ht="18.75" customHeight="1">
       <c r="C10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K10" s="2">
         <v>2</v>
       </c>
-      <c r="L10" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="M10" s="17"/>
+      <c r="L10" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="M10" s="16"/>
       <c r="N10" s="2">
         <v>1</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="R10" s="2">
         <v>5</v>
       </c>
       <c r="S10" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" s="2">
         <v>1</v>
       </c>
+      <c r="U10" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="V10" s="2" t="s">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="W10" s="2">
         <v>5</v>
       </c>
       <c r="X10" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y10" s="2">
         <v>1</v>
@@ -5024,15 +5036,15 @@
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 }</v>
-      </c>
-      <c r="AK10" t="b" cm="1">
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }</v>
+      </c>
+      <c r="AK10" t="str" cm="1">
         <f t="array" ref="AK10">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
-        <v>0</v>
+        <v>{ type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 }</v>
       </c>
       <c r="AL10" t="b" cm="1">
         <f t="array" ref="AL10">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
@@ -5050,42 +5062,44 @@
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="15" t="str" cm="1">
+      <c r="AN10" s="14" t="str" cm="1">
         <f t="array" ref="AN10" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "crude-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO10" s="15" t="str" cm="1">
+        <v>{ { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO10" s="14" t="str" cm="1">
         <f t="array" ref="AO10" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>{ 
-    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 } 
 }</v>
       </c>
-      <c r="AP10" s="16" t="str" cm="1">
+      <c r="AP10" s="15" t="str" cm="1">
         <f t="array" ref="AP10">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>crude_asteroid_chunk_crushing.name = "crude-asteroid-chunk-crushing"
+        <v>crude_asteroid_chunk_crushing.name = "astra-crude-asteroid-crushing"
 crude_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
 crude_asteroid_chunk_crushing.order = "a"
 crude_asteroid_chunk_crushing.enabled = false
 crude_asteroid_chunk_crushing.energy_required = 2
-crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "crude-asteroid-chunk-item", amount = 1 } }
+crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }
 crude_asteroid_chunk_crushing.results = { 
-    { type = "item", name = "solid-fuel", amount_min = 5, amount_max = 15, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 } 
 }</v>
       </c>
     </row>
     <row r="11" spans="2:43" ht="18.75" customHeight="1">
       <c r="C11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>13</v>
@@ -5095,21 +5109,21 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K11" s="2">
         <v>2</v>
       </c>
-      <c r="L11" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="M11" s="17"/>
+      <c r="L11" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="M11" s="16"/>
       <c r="N11" s="2">
         <v>1</v>
       </c>
@@ -5151,7 +5165,7 @@
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN11" s="15" t="str" cm="1">
+      <c r="AN11" s="14" t="str" cm="1">
         <f t="array" ref="AN11" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -5159,14 +5173,14 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO11" s="15" t="e" cm="1" vm="1">
+      <c r="AO11" s="14" t="e" cm="1" vm="2">
         <f t="array" ref="AO11" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP11" s="16" t="e" cm="1" vm="2">
+      <c r="AP11" s="15" t="e" cm="1" vm="3">
         <f t="array" ref="AP11">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -5176,42 +5190,42 @@
     </row>
     <row r="12" spans="2:43" ht="18.75" customHeight="1">
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K12" s="2">
         <v>2</v>
       </c>
-      <c r="L12" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="M12" s="17"/>
+      <c r="L12" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="M12" s="16"/>
       <c r="N12" s="2">
         <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R12" s="2">
         <v>4</v>
@@ -5223,10 +5237,10 @@
         <v>1</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W12" s="2">
         <v>1</v>
@@ -5238,10 +5252,10 @@
         <v>0.15</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF12" s="2" t="s">
-        <v>210</v>
+        <v>159</v>
+      </c>
+      <c r="AF12" s="16" t="s">
+        <v>234</v>
       </c>
       <c r="AG12" s="2">
         <v>1</v>
@@ -5282,17 +5296,17 @@
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN12" s="15" t="str" cm="1">
+        <v>{ type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN12" s="14" t="str" cm="1">
         <f t="array" ref="AN12" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO12" s="15" t="str" cm="1">
+        <v>{ { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO12" s="14" t="str" cm="1">
         <f t="array" ref="AO12" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -5300,65 +5314,65 @@
         <v>{ 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
-    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP12" s="16" t="str" cm="1">
+      <c r="AP12" s="15" t="str" cm="1">
         <f t="array" ref="AP12">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>vulcanus_asteroid_chunk_crushing.name = "vulcanus-asteroid-chunk-crushing"
+        <v>vulcanus_asteroid_chunk_crushing.name = "astra-vulcanus-asteroid-crushing"
 vulcanus_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
 vulcanus_asteroid_chunk_crushing.order = "v"
 vulcanus_asteroid_chunk_crushing.enabled = false
 vulcanus_asteroid_chunk_crushing.energy_required = 2
-vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }
 vulcanus_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 1, amount_max = 2, probability = 0.15 }, 
-    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
     <row r="13" spans="2:43" ht="18.75" customHeight="1">
       <c r="C13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K13" s="2">
         <v>2</v>
       </c>
-      <c r="L13" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="M13" s="17"/>
+      <c r="L13" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="M13" s="16"/>
       <c r="N13" s="2">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R13" s="2">
         <v>5</v>
@@ -5370,10 +5384,10 @@
         <v>1</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="W13" s="2">
         <v>1</v>
@@ -5385,10 +5399,10 @@
         <v>0.1</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF13" s="2" t="s">
-        <v>211</v>
+        <v>159</v>
+      </c>
+      <c r="AF13" s="16" t="s">
+        <v>235</v>
       </c>
       <c r="AG13" s="2">
         <v>1</v>
@@ -5429,17 +5443,17 @@
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN13" s="15" t="str" cm="1">
+        <v>{ type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN13" s="14" t="str" cm="1">
         <f t="array" ref="AN13" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO13" s="15" t="str" cm="1">
+        <v>{ { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO13" s="14" t="str" cm="1">
         <f t="array" ref="AO13" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -5447,30 +5461,30 @@
         <v>{ 
     { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP13" s="16" t="str" cm="1">
+      <c r="AP13" s="15" t="str" cm="1">
         <f t="array" ref="AP13">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>nauvis_asteroid_chunk_crushing.name = "nauvis-asteroid-chunk-crushing"
+        <v>nauvis_asteroid_chunk_crushing.name = "astra-nauvis-asteroid-crushing"
 nauvis_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
 nauvis_asteroid_chunk_crushing.order = "n"
 nauvis_asteroid_chunk_crushing.enabled = false
 nauvis_asteroid_chunk_crushing.energy_required = 2
-nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }
 nauvis_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 5, amount_max = 10, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 1, probability = 0.1 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
     <row r="14" spans="2:43" ht="18.75" customHeight="1">
       <c r="C14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -5480,35 +5494,35 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>176</v>
+        <v>250</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K14" s="2">
         <v>2</v>
       </c>
-      <c r="L14" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="M14" s="17"/>
+      <c r="L14" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="M14" s="16"/>
       <c r="N14" s="2">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R14" s="2">
         <v>3</v>
@@ -5520,10 +5534,10 @@
         <v>1</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="W14" s="2">
         <v>1</v>
@@ -5535,10 +5549,10 @@
         <v>0.05</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AB14" s="2">
         <v>1</v>
@@ -5550,10 +5564,10 @@
         <v>0.05</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF14" s="2" t="s">
-        <v>212</v>
+        <v>159</v>
+      </c>
+      <c r="AF14" s="16" t="s">
+        <v>236</v>
       </c>
       <c r="AG14" s="2">
         <v>1</v>
@@ -5594,17 +5608,17 @@
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN14" s="15" t="str" cm="1">
+        <v>{ type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN14" s="14" t="str" cm="1">
         <f t="array" ref="AN14" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO14" s="15" t="str" cm="1">
+        <v>{ { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO14" s="14" t="str" cm="1">
         <f t="array" ref="AO14" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -5613,66 +5627,66 @@
     { type = "item", name = "stone", amount_min = 3, amount_max = 5, probability = 1 }, 
     { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
     { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP14" s="16" t="str" cm="1">
+      <c r="AP14" s="15" t="str" cm="1">
         <f t="array" ref="AP14">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>gleba_asteroid_chunk_crushing.name = "gleba-asteroid-chunk-crushing"
+        <v>gleba_asteroid_chunk_crushing.name = "astra-gleba-asteroid-crushing"
 gleba_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/gleba_crushing_basic.png"
 gleba_asteroid_chunk_crushing.order = "g"
 gleba_asteroid_chunk_crushing.enabled = false
 gleba_asteroid_chunk_crushing.energy_required = 2
-gleba_asteroid_chunk_crushing.ingredients = { { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }
+gleba_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }
 gleba_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 3, amount_max = 5, probability = 1 }, 
     { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
     { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
     <row r="15" spans="2:43" ht="18.75" customHeight="1">
       <c r="C15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K15" s="2">
         <v>2</v>
       </c>
-      <c r="L15" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="M15" s="17"/>
+      <c r="L15" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="M15" s="16"/>
       <c r="N15" s="2">
         <v>1</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R15" s="2">
         <v>4</v>
@@ -5684,10 +5698,10 @@
         <v>1</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="W15" s="2">
         <v>2</v>
@@ -5699,10 +5713,10 @@
         <v>1</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF15" s="2" t="s">
-        <v>213</v>
+        <v>159</v>
+      </c>
+      <c r="AF15" s="16" t="s">
+        <v>237</v>
       </c>
       <c r="AG15" s="2">
         <v>1</v>
@@ -5743,17 +5757,17 @@
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN15" s="15" t="str" cm="1">
+        <v>{ type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN15" s="14" t="str" cm="1">
         <f t="array" ref="AN15" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO15" s="15" t="str" cm="1">
+        <v>{ { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO15" s="14" t="str" cm="1">
         <f t="array" ref="AO15" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -5761,30 +5775,30 @@
         <v>{ 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
-    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP15" s="16" t="str" cm="1">
+      <c r="AP15" s="15" t="str" cm="1">
         <f t="array" ref="AP15">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>fulgoran_asteroid_chunk_crushing.name = "fulgoran-asteroid-chunk-crushing"
+        <v>fulgoran_asteroid_chunk_crushing.name = "astra-fulgoran-asteroid-crushing"
 fulgoran_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
 fulgoran_asteroid_chunk_crushing.order = "f"
 fulgoran_asteroid_chunk_crushing.enabled = false
 fulgoran_asteroid_chunk_crushing.energy_required = 2
-fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }
 fulgoran_asteroid_chunk_crushing.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "scrap", amount_min = 2, amount_max = 12, probability = 1 }, 
-    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
     <row r="16" spans="2:43" ht="18.75" customHeight="1">
       <c r="C16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>13</v>
@@ -5794,29 +5808,29 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K16" s="2">
         <v>5</v>
       </c>
-      <c r="L16" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="M16" s="17"/>
+      <c r="L16" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="M16" s="16"/>
       <c r="N16" s="2">
         <v>1</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R16" s="2">
         <v>3</v>
@@ -5828,10 +5842,10 @@
         <v>1</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W16" s="2">
         <v>2</v>
@@ -5843,10 +5857,10 @@
         <v>1</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AB16" s="2">
         <v>1</v>
@@ -5858,7 +5872,7 @@
         <v>0.05</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AJ16" t="str" cm="1">
         <f t="array" ref="AJ16">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
@@ -5892,7 +5906,7 @@
   " }" )</f>
         <v>{ type = "item", name = "", amount_min = "", amount_max = "", probability = "" }</v>
       </c>
-      <c r="AN16" s="15" t="str" cm="1">
+      <c r="AN16" s="14" t="str" cm="1">
         <f t="array" ref="AN16" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -5900,7 +5914,7 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO16" s="15" t="str" cm="1">
+      <c r="AO16" s="14" t="str" cm="1">
         <f t="array" ref="AO16" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -5912,7 +5926,7 @@
     { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
 }</v>
       </c>
-      <c r="AP16" s="16" t="str" cm="1">
+      <c r="AP16" s="15" t="str" cm="1">
         <f t="array" ref="AP16">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -5933,7 +5947,7 @@
     </row>
     <row r="17" spans="3:42" ht="18.75" customHeight="1">
       <c r="C17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
@@ -5943,29 +5957,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K17" s="2">
         <v>5</v>
       </c>
-      <c r="L17" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="17"/>
+      <c r="L17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="16"/>
       <c r="N17" s="2">
         <v>1</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R17" s="2">
         <v>10</v>
@@ -5977,10 +5991,10 @@
         <v>1</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="W17" s="2">
         <v>4</v>
@@ -5992,10 +6006,10 @@
         <v>1</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AB17" s="2">
         <v>1</v>
@@ -6007,7 +6021,7 @@
         <v>0.05</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AJ17" t="str" cm="1">
         <f t="array" ref="AJ17">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
@@ -6041,7 +6055,7 @@
   " }" )</f>
         <v>{ type = "item", name = "", amount_min = "", amount_max = "", probability = "" }</v>
       </c>
-      <c r="AN17" s="15" t="str" cm="1">
+      <c r="AN17" s="14" t="str" cm="1">
         <f t="array" ref="AN17" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -6049,7 +6063,7 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO17" s="15" t="str" cm="1">
+      <c r="AO17" s="14" t="str" cm="1">
         <f t="array" ref="AO17" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -6061,7 +6075,7 @@
     { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
 }</v>
       </c>
-      <c r="AP17" s="16" t="str" cm="1">
+      <c r="AP17" s="15" t="str" cm="1">
         <f t="array" ref="AP17">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -6082,7 +6096,7 @@
     </row>
     <row r="18" spans="3:42" ht="18.75" customHeight="1">
       <c r="C18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>13</v>
@@ -6092,29 +6106,29 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K18" s="2">
         <v>5</v>
       </c>
-      <c r="L18" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="M18" s="17"/>
+      <c r="L18" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="16"/>
       <c r="N18" s="2">
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R18" s="2">
         <v>5</v>
@@ -6126,10 +6140,10 @@
         <v>1</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="W18" s="2">
         <v>2</v>
@@ -6141,10 +6155,10 @@
         <v>1</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AB18" s="2">
         <v>1</v>
@@ -6156,7 +6170,7 @@
         <v>0.05</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AJ18" t="str" cm="1">
         <f t="array" ref="AJ18">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
@@ -6190,7 +6204,7 @@
   " }" )</f>
         <v>{ type = "item", name = "", amount_min = "", amount_max = "", probability = "" }</v>
       </c>
-      <c r="AN18" s="15" t="str" cm="1">
+      <c r="AN18" s="14" t="str" cm="1">
         <f t="array" ref="AN18" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
@@ -6198,7 +6212,7 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO18" s="15" t="str" cm="1">
+      <c r="AO18" s="14" t="str" cm="1">
         <f t="array" ref="AO18" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
@@ -6210,7 +6224,7 @@
     { type = "item", name = "", amount_min = "", amount_max = "", probability = "" } 
 }</v>
       </c>
-      <c r="AP18" s="16" t="str" cm="1">
+      <c r="AP18" s="15" t="str" cm="1">
         <f t="array" ref="AP18">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -6231,72 +6245,71 @@
     </row>
     <row r="19" spans="3:42" ht="18.75" customHeight="1">
       <c r="C19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="2" t="b">
-        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>243</v>
+      </c>
+      <c r="E19" s="19" t="b">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>216</v>
+        <v>245</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>40</v>
+        <v>171</v>
+      </c>
+      <c r="J19" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="K19" s="2">
         <v>5</v>
       </c>
-      <c r="L19" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="M19" s="17"/>
+      <c r="L19" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="M19" s="16"/>
       <c r="N19" s="2">
         <v>1</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>68</v>
+        <v>242</v>
       </c>
       <c r="R19" s="2">
+        <v>5</v>
+      </c>
+      <c r="S19" s="2">
+        <v>10</v>
+      </c>
+      <c r="T19" s="2">
+        <v>1</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="W19" s="2">
+        <v>5</v>
+      </c>
+      <c r="X19" s="2">
         <v>8</v>
       </c>
-      <c r="S19" s="2">
-        <v>8</v>
-      </c>
-      <c r="T19" s="2">
-        <v>1</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W19" s="2">
-        <v>10</v>
-      </c>
-      <c r="X19" s="2">
-        <v>10</v>
-      </c>
       <c r="Y19" s="2">
         <v>1</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="AG19" s="2">
         <v>1</v>
@@ -6307,473 +6320,620 @@
       <c r="AI19" s="2">
         <v>0.05</v>
       </c>
-      <c r="AJ19" t="str" cm="1">
+      <c r="AJ19" s="20" t="str" cm="1">
         <f t="array" ref="AJ19">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 }</v>
+      </c>
+      <c r="AK19" s="20" t="str" cm="1">
+        <f t="array" ref="AK19">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }</v>
+      </c>
+      <c r="AL19" s="20" t="b" cm="1">
+        <f t="array" ref="AL19">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="20" t="str" cm="1">
+        <f t="array" ref="AM19">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>{ type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN19" s="21" t="str" cm="1">
+        <f t="array" ref="AN19" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO19" s="21" t="str" cm="1">
+        <f t="array" ref="AO19" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>{ 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+      <c r="AP19" s="22" t="str" cm="1">
+        <f t="array" ref="AP19">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>crude_asteroid_chunk_crushing_adv.name = "astra-advanced-crude-asteroid-crushing"
+crude_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+crude_asteroid_chunk_crushing_adv.order = "a"
+crude_asteroid_chunk_crushing_adv.enabled = FALSE
+crude_asteroid_chunk_crushing_adv.energy_required = 5
+crude_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }
+crude_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+}</v>
+      </c>
+    </row>
+    <row r="20" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="2">
+        <v>5</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R20" s="2">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2">
+        <v>8</v>
+      </c>
+      <c r="T20" s="2">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W20" s="2">
+        <v>10</v>
+      </c>
+      <c r="X20" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF20" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="AG20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AJ20" t="str" cm="1">
+        <f t="array" ref="AJ20">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }</v>
       </c>
-      <c r="AK19" t="str" cm="1">
-        <f t="array" ref="AK19">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK20" t="str" cm="1">
+        <f t="array" ref="AK20">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }</v>
       </c>
-      <c r="AL19" t="b" cm="1">
-        <f t="array" ref="AL19">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL20" t="b" cm="1">
+        <f t="array" ref="AL20">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AM19" t="str" cm="1">
-        <f t="array" ref="AM19">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM20" t="str" cm="1">
+        <f t="array" ref="AM20">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN19" s="15" t="str" cm="1">
-        <f t="array" ref="AN19" xml:space="preserve"> "{ " &amp;
+        <v>{ type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN20" s="14" t="str" cm="1">
+        <f t="array" ref="AN20" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO19" s="15" t="str" cm="1">
-        <f t="array" ref="AO19" xml:space="preserve"> "{ 
+        <v>{ { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO20" s="14" t="str" cm="1">
+        <f t="array" ref="AO20" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP19" s="16" t="str" cm="1">
-        <f t="array" ref="AP19">_xlfn.TEXTJOIN("
+      <c r="AP20" s="15" t="str" cm="1">
+        <f t="array" ref="AP20">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>vulcanis_asteroid_chunk_crushing_adv.name = "vulcanis-asteroid-chunk-crushing-adv"
+        <v>vulcanis_asteroid_chunk_crushing_adv.name = "astra-advanced-vulcanis-asteroid-crushing"
 vulcanis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
 vulcanis_asteroid_chunk_crushing_adv.order = "v"
 vulcanis_asteroid_chunk_crushing_adv.enabled = false
 vulcanis_asteroid_chunk_crushing_adv.energy_required = 5
-vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 } }
+vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }
 vulcanis_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "stone", amount_min = 8, amount_max = 8, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "vulcanic-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
-    <row r="20" spans="3:42" ht="18.75" customHeight="1">
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="2" t="b">
+    <row r="21" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>1</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="2">
+      <c r="J21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="2">
         <v>5</v>
       </c>
-      <c r="L20" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="M20" s="17"/>
-      <c r="N20" s="2">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="R20" s="2">
+      <c r="L21" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="M21" s="16"/>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R21" s="2">
         <v>4</v>
       </c>
-      <c r="S20" s="2">
+      <c r="S21" s="2">
         <v>8</v>
       </c>
-      <c r="T20" s="2">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="W20" s="2">
-        <v>1</v>
-      </c>
-      <c r="X20" s="2">
+      <c r="T21" s="2">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="W21" s="2">
+        <v>1</v>
+      </c>
+      <c r="X21" s="2">
         <v>13</v>
       </c>
-      <c r="Y20" s="2">
+      <c r="Y21" s="2">
         <v>0.4</v>
       </c>
-      <c r="AE20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF20" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="AG20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="2">
+      <c r="AE21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF21" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI21" s="2">
         <v>0.05</v>
       </c>
-      <c r="AJ20" t="str" cm="1">
-        <f t="array" ref="AJ20">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+      <c r="AJ21" t="str" cm="1">
+        <f t="array" ref="AJ21">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }</v>
       </c>
-      <c r="AK20" t="str" cm="1">
-        <f t="array" ref="AK20">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK21" t="str" cm="1">
+        <f t="array" ref="AK21">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }</v>
       </c>
-      <c r="AL20" t="b" cm="1">
-        <f t="array" ref="AL20">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL21" t="b" cm="1">
+        <f t="array" ref="AL21">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AM20" t="str" cm="1">
-        <f t="array" ref="AM20">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM21" t="str" cm="1">
+        <f t="array" ref="AM21">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN20" s="15" t="str" cm="1">
-        <f t="array" ref="AN20" xml:space="preserve"> "{ " &amp;
+        <v>{ type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN21" s="14" t="str" cm="1">
+        <f t="array" ref="AN21" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO20" s="15" t="str" cm="1">
-        <f t="array" ref="AO20" xml:space="preserve"> "{ 
+        <v>{ { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO21" s="14" t="str" cm="1">
+        <f t="array" ref="AO21" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP20" s="16" t="str" cm="1">
-        <f t="array" ref="AP20">_xlfn.TEXTJOIN("
+      <c r="AP21" s="15" t="str" cm="1">
+        <f t="array" ref="AP21">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>nauvis_asteroid_chunk_crushing_adv.name = "nauvis-asteroid-chunk-crushing-adv"
+        <v>nauvis_asteroid_chunk_crushing_adv.name = "astra-advanced-nauvis-asteroid-crushing"
 nauvis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
 nauvis_asteroid_chunk_crushing_adv.order = "n"
 nauvis_asteroid_chunk_crushing_adv.enabled = false
 nauvis_asteroid_chunk_crushing_adv.energy_required = 5
-nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }
+nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }
 nauvis_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 8, probability = 1 }, 
     { type = "item", name = "uranium-ore", amount_min = 1, amount_max = 13, probability = 0.4 }, 
-    { type = "item", name = "nauvis-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
-    <row r="21" spans="3:42" ht="18.75" customHeight="1">
-      <c r="C21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" s="2" t="s">
+    <row r="22" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="2" t="b">
+      <c r="E22" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>1</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" s="2">
+      <c r="F22" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="2">
         <v>5</v>
       </c>
-      <c r="L21" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="M21" s="17"/>
-      <c r="N21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF21" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="AG21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI21" s="2">
+      <c r="L22" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF22" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="2">
         <v>0.05</v>
       </c>
-      <c r="AJ21" t="b" cm="1">
-        <f t="array" ref="AJ21">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+      <c r="AJ22" t="b" cm="1">
+        <f t="array" ref="AJ22">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AK21" t="b" cm="1">
-        <f t="array" ref="AK21">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK22" t="b" cm="1">
+        <f t="array" ref="AK22">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AL21" t="b" cm="1">
-        <f t="array" ref="AL21">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL22" t="b" cm="1">
+        <f t="array" ref="AL22">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AM21" t="str" cm="1">
-        <f t="array" ref="AM21">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM22" t="str" cm="1">
+        <f t="array" ref="AM22">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN21" s="15" t="str" cm="1">
-        <f t="array" ref="AN21" xml:space="preserve"> "{ " &amp;
+        <v>{ type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN22" s="14" t="str" cm="1">
+        <f t="array" ref="AN22" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO21" s="15" t="str" cm="1">
-        <f t="array" ref="AO21" xml:space="preserve"> "{ 
+        <v>{ { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO22" s="14" t="str" cm="1">
+        <f t="array" ref="AO22" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>{ 
-    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP21" s="16" t="str" cm="1">
-        <f t="array" ref="AP21">_xlfn.TEXTJOIN("
+      <c r="AP22" s="15" t="str" cm="1">
+        <f t="array" ref="AP22">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>gleba_asteroid_chunk_crushing_adv.name = "gleba-asteroid-chunk-crushing-adv"
+        <v>gleba_asteroid_chunk_crushing_adv.name = "astra-advanced-gleba-asteroid-crushing"
 gleba_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/gleba_crushing_basic.png"
 gleba_asteroid_chunk_crushing_adv.order = "g"
 gleba_asteroid_chunk_crushing_adv.enabled = false
 gleba_asteroid_chunk_crushing_adv.energy_required = 5
-gleba_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }
+gleba_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }
 gleba_asteroid_chunk_crushing_adv.results = { 
-    { type = "item", name = "gleba-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
-    <row r="22" spans="3:42" ht="18.75" customHeight="1">
-      <c r="C22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" s="2" t="b">
+    <row r="23" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>1</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22" s="2">
+      <c r="J23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="2">
         <v>5</v>
       </c>
-      <c r="L22" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="M22" s="17"/>
-      <c r="N22" s="2">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="R22" s="2">
+      <c r="L23" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="M23" s="16"/>
+      <c r="N23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R23" s="2">
         <v>4</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S23" s="2">
         <v>6</v>
       </c>
-      <c r="T22" s="2">
-        <v>1</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="W22" s="2">
+      <c r="T23" s="2">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23" s="2">
         <v>35</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X23" s="2">
         <v>75</v>
       </c>
-      <c r="Y22" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AB22" s="2">
+      <c r="Y23" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB23" s="2">
         <v>3</v>
       </c>
-      <c r="AC22" s="2">
+      <c r="AC23" s="2">
         <v>8</v>
       </c>
-      <c r="AD22" s="2">
+      <c r="AD23" s="2">
         <v>0.5</v>
       </c>
-      <c r="AE22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF22" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI22" s="2">
+      <c r="AE23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF23" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="AG23" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI23" s="2">
         <v>0.05</v>
       </c>
-      <c r="AJ22" t="str" cm="1">
-        <f t="array" ref="AJ22">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+      <c r="AJ23" t="str" cm="1">
+        <f t="array" ref="AJ23">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }</v>
       </c>
-      <c r="AK22" t="str" cm="1">
-        <f t="array" ref="AK22">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK23" t="str" cm="1">
+        <f t="array" ref="AK23">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }</v>
       </c>
-      <c r="AL22" t="str" cm="1">
-        <f t="array" ref="AL22">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL23" t="str" cm="1">
+        <f t="array" ref="AL23">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }</v>
       </c>
-      <c r="AM22" t="str" cm="1">
-        <f t="array" ref="AM22">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM23" t="str" cm="1">
+        <f t="array" ref="AM23">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
-        <v>{ type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
-      </c>
-      <c r="AN22" s="15" t="str" cm="1">
-        <f t="array" ref="AN22" xml:space="preserve"> "{ " &amp;
+        <v>{ type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+      <c r="AN23" s="14" t="str" cm="1">
+        <f t="array" ref="AN23" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO22" s="15" t="str" cm="1">
-        <f t="array" ref="AO22" xml:space="preserve"> "{ 
+        <v>{ { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO23" s="14" t="str" cm="1">
+        <f t="array" ref="AO23" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
@@ -6781,138 +6941,141 @@
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
     { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
-    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
-      <c r="AP22" s="16" t="str" cm="1">
-        <f t="array" ref="AP22">_xlfn.TEXTJOIN("
+      <c r="AP23" s="15" t="str" cm="1">
+        <f t="array" ref="AP23">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>fulgoran_asteroid_chunk_crushing_adv.name = "fulgoran-asteroid-chunk-crushing-adv"
+        <v>fulgoran_asteroid_chunk_crushing_adv.name = "astra-advanced-fulgoran-asteroid-crushing"
 fulgoran_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
 fulgoran_asteroid_chunk_crushing_adv.order = "f"
 fulgoran_asteroid_chunk_crushing_adv.enabled = false
 fulgoran_asteroid_chunk_crushing_adv.energy_required = 5
-fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 } }
+fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }
 fulgoran_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "stone", amount_min = 4, amount_max = 6, probability = 1 }, 
     { type = "item", name = "scrap", amount_min = 35, amount_max = 75, probability = 1 }, 
     { type = "item", name = "holmium-ore", amount_min = 3, amount_max = 8, probability = 0.5 }, 
-    { type = "item", name = "fulgoran-asteroid-chunk-item", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
-    <row r="23" spans="3:42" ht="18.75" customHeight="1">
-      <c r="C23" t="s">
-        <v>169</v>
-      </c>
-      <c r="E23" s="2" t="b">
+    <row r="24" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>1</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23" s="2">
+      <c r="F24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="2">
         <v>5</v>
       </c>
-      <c r="L23" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="M23" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="N23" s="2">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R23" s="2">
+      <c r="L24" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R24" s="2">
         <v>2000</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S24" s="2">
         <v>2000</v>
       </c>
-      <c r="T23" s="2">
-        <v>1</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W23" s="2">
+      <c r="T24" s="2">
+        <v>1</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W24" s="2">
         <v>12</v>
       </c>
-      <c r="X23" s="2">
+      <c r="X24" s="2">
         <v>12</v>
       </c>
-      <c r="Y23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ23" t="str" cm="1">
-        <f t="array" ref="AJ23">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+      <c r="Y24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="str" cm="1">
+        <f t="array" ref="AJ24">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }</v>
       </c>
-      <c r="AK23" t="str" cm="1">
-        <f t="array" ref="AK23">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK24" t="str" cm="1">
+        <f t="array" ref="AK24">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 }</v>
       </c>
-      <c r="AL23" t="b" cm="1">
-        <f t="array" ref="AL23">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL24" t="b" cm="1">
+        <f t="array" ref="AL24">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AM23" t="b" cm="1">
-        <f t="array" ref="AM23">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM24" t="b" cm="1">
+        <f t="array" ref="AM24">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN23" s="15" t="str" cm="1">
-        <f t="array" ref="AN23" xml:space="preserve"> "{ " &amp;
+      <c r="AN24" s="14" t="str" cm="1">
+        <f t="array" ref="AN24" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
-      </c>
-      <c r="AO23" s="15" t="str" cm="1">
-        <f t="array" ref="AO23" xml:space="preserve"> "{ 
+        <v>{ { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO24" s="14" t="str" cm="1">
+        <f t="array" ref="AO24" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
@@ -6921,198 +7084,107 @@
     { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
 }</v>
       </c>
-      <c r="AP23" s="16" t="str" cm="1">
-        <f t="array" ref="AP23">_xlfn.TEXTJOIN("
+      <c r="AP24" s="15" t="str" cm="1">
+        <f t="array" ref="AP24">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>vulcanus_special_crushing.name = "vulcanus-special-crushing"
+        <v>vulcanus_special_crushing.name = "astra-vulcanus-special-crushing"
 vulcanus_special_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
 vulcanus_special_crushing.order = "v"
 vulcanus_special_crushing.enabled = false
 vulcanus_special_crushing.energy_required = 5
-vulcanus_special_crushing.ingredients = { { type = "item", name = "vulcanic-asteroid-chunk-item", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
+vulcanus_special_crushing.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
 vulcanus_special_crushing.results = { 
     { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
     { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
 }</v>
       </c>
     </row>
-    <row r="24" spans="3:42" ht="18.75" customHeight="1">
-      <c r="C24" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="2" t="s">
+    <row r="25" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="2" t="b">
+      <c r="E25" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>1</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="I24" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K24" s="2">
+      <c r="J25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="2">
         <v>5</v>
       </c>
-      <c r="L24" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="b" cm="1">
-        <f t="array" ref="AJ24">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+      <c r="L25" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="M25" s="16"/>
+      <c r="N25" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="b" cm="1">
+        <f t="array" ref="AJ25">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AK24" t="b" cm="1">
-        <f t="array" ref="AK24">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK25" t="b" cm="1">
+        <f t="array" ref="AK25">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AL24" t="b" cm="1">
-        <f t="array" ref="AL24">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL25" t="b" cm="1">
+        <f t="array" ref="AL25">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AM24" t="b" cm="1">
-        <f t="array" ref="AM24">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM25" t="b" cm="1">
+        <f t="array" ref="AM25">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN24" s="15" t="str" cm="1">
-        <f t="array" ref="AN24" xml:space="preserve"> "{ " &amp;
+      <c r="AN25" s="14" t="str" cm="1">
+        <f t="array" ref="AN25" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "nauvis-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO24" s="15" t="e" cm="1" vm="1">
-        <f t="array" ref="AO24" xml:space="preserve"> "{ 
-    " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
-}"</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AP24" s="16" t="e" cm="1" vm="2">
-        <f t="array" ref="AP24">_xlfn.TEXTJOIN("
-", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
-" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
-" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="3:42" ht="18.75" customHeight="1">
-      <c r="C25" t="s">
-        <v>168</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="2" t="b">
-        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="2">
-        <v>10</v>
-      </c>
-      <c r="L25" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="b" cm="1">
-        <f t="array" ref="AJ25">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
-  " }" )</f>
-        <v>0</v>
-      </c>
-      <c r="AK25" t="b" cm="1">
-        <f t="array" ref="AK25">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
-  " }" )</f>
-        <v>0</v>
-      </c>
-      <c r="AL25" t="b" cm="1">
-        <f t="array" ref="AL25">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
-  " }" )</f>
-        <v>0</v>
-      </c>
-      <c r="AM25" t="b" cm="1">
-        <f t="array" ref="AM25">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
-  " }" )</f>
-        <v>0</v>
-      </c>
-      <c r="AN25" s="15" t="str" cm="1">
-        <f t="array" ref="AN25" xml:space="preserve"> "{ " &amp;
- _xlfn.TEXTJOIN(", ",
-          TRUE,
-          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
-&amp; " }"</f>
-        <v>{ { type = "item", name = "gleba-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO25" s="15" t="e" cm="1" vm="1">
+        <v>{ { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO25" s="14" t="e" cm="1" vm="2">
         <f t="array" ref="AO25" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP25" s="16" t="e" cm="1" vm="2">
+      <c r="AP25" s="15" t="e" cm="1" vm="3">
         <f t="array" ref="AP25">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -7122,129 +7194,223 @@
     </row>
     <row r="26" spans="3:42" ht="18.75" customHeight="1">
       <c r="C26" t="s">
-        <v>167</v>
+        <v>165</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
         <v>1</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>215</v>
+        <v>240</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>196</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K26" s="2">
         <v>10</v>
       </c>
-      <c r="L26" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="M26" s="17" t="s">
-        <v>214</v>
-      </c>
+      <c r="L26" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="M26" s="16"/>
       <c r="N26" s="2">
         <v>1</v>
       </c>
-      <c r="O26" s="2">
-        <v>1</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="R26" s="2">
+      <c r="AJ26" t="b" cm="1">
+        <f t="array" ref="AJ26">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b" cm="1">
+        <f t="array" ref="AK26">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AL26" t="b" cm="1">
+        <f t="array" ref="AL26">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AM26" t="b" cm="1">
+        <f t="array" ref="AM26">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
+  " }" )</f>
+        <v>0</v>
+      </c>
+      <c r="AN26" s="14" t="str" cm="1">
+        <f t="array" ref="AN26" xml:space="preserve"> "{ " &amp;
+ _xlfn.TEXTJOIN(", ",
+          TRUE,
+          "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
+&amp; " }"</f>
+        <v>{ { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO26" s="14" t="e" cm="1" vm="2">
+        <f t="array" ref="AO26" xml:space="preserve"> "{ 
+    " &amp; _xlfn.TEXTJOIN(", 
+    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+}"</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP26" s="15" t="e" cm="1" vm="3">
+        <f t="array" ref="AP26">_xlfn.TEXTJOIN("
+", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
+" &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="3:42" ht="18.75" customHeight="1">
+      <c r="C27" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="2" t="b">
+        <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="2">
+        <v>10</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N27" s="2">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2">
+        <v>1</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R27" s="2">
         <v>5</v>
       </c>
-      <c r="S26" s="2">
+      <c r="S27" s="2">
         <v>5</v>
       </c>
-      <c r="T26" s="2">
-        <v>1</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="W26" s="2">
+      <c r="T27" s="2">
+        <v>1</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="W27" s="2">
         <v>20</v>
       </c>
-      <c r="X26" s="2">
+      <c r="X27" s="2">
         <v>20</v>
       </c>
-      <c r="Y26" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA26" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB26" s="2">
+      <c r="Y27" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB27" s="2">
         <v>20</v>
       </c>
-      <c r="AC26" s="2">
+      <c r="AC27" s="2">
         <v>20</v>
       </c>
-      <c r="AD26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="str" cm="1">
-        <f t="array" ref="AJ26">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
+      <c r="AD27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="str" cm="1">
+        <f t="array" ref="AJ27">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
       </c>
-      <c r="AK26" t="str" cm="1">
-        <f t="array" ref="AK26">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
+      <c r="AK27" t="str" cm="1">
+        <f t="array" ref="AK27">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }</v>
       </c>
-      <c r="AL26" t="str" cm="1">
-        <f t="array" ref="AL26">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
+      <c r="AL27" t="str" cm="1">
+        <f t="array" ref="AL27">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</f>
         <v>{ type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 }</v>
       </c>
-      <c r="AM26" t="b" cm="1">
-        <f t="array" ref="AM26">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
+      <c r="AM27" t="b" cm="1">
+        <f t="array" ref="AM27">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</f>
         <v>0</v>
       </c>
-      <c r="AN26" s="15" t="str" cm="1">
-        <f t="array" ref="AN26" xml:space="preserve"> "{ " &amp;
+      <c r="AN27" s="14" t="str" cm="1">
+        <f t="array" ref="AN27" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</f>
-        <v>{ { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk-item", amount = 1 } }</v>
-      </c>
-      <c r="AO26" s="15" t="str" cm="1">
-        <f t="array" ref="AO26" xml:space="preserve"> "{ 
+        <v>{ { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
+      </c>
+      <c r="AO27" s="14" t="str" cm="1">
+        <f t="array" ref="AO27" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
     ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
 }"</f>
@@ -7254,17 +7420,17 @@
     { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
 }</v>
       </c>
-      <c r="AP26" s="16" t="str" cm="1">
-        <f t="array" ref="AP26">_xlfn.TEXTJOIN("
+      <c r="AP27" s="15" t="str" cm="1">
+        <f t="array" ref="AP27">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>fulgoran_special_crushing.name = "fulgoran-special-crushing"
+        <v>fulgoran_special_crushing.name = "astra-fulgoran-special-crushing"
 fulgoran_special_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
 fulgoran_special_crushing.order = "f"
 fulgoran_special_crushing.enabled = false
 fulgoran_special_crushing.energy_required = 10
-fulgoran_special_crushing.ingredients = { { type = "item", name = "fulgoran-asteroid-chunk-item", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk-item", amount = 1 } }
+fulgoran_special_crushing.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }
 fulgoran_special_crushing.results = { 
     { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
     { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
@@ -7272,152 +7438,147 @@
 }</v>
       </c>
     </row>
-    <row r="31" spans="3:42">
-      <c r="E31" s="17"/>
-    </row>
     <row r="32" spans="3:42">
-      <c r="E32" s="17"/>
+      <c r="E32" s="16"/>
     </row>
     <row r="33" spans="5:42">
-      <c r="E33" s="17"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34" spans="5:42">
-      <c r="E34" s="17"/>
-      <c r="AP34" t="s">
-        <v>189</v>
-      </c>
+      <c r="E34" s="16"/>
     </row>
     <row r="35" spans="5:42">
-      <c r="E35" s="17"/>
-      <c r="O35" s="2" t="str" cm="1">
-        <f t="array" ref="O35">_xlfn.TEXTJOIN(", ", TRUE, IF(NOT(ISNUMBER(P35:V35)), """" &amp; P35:V35 &amp; """", P35:V35))</f>
+      <c r="E35" s="16"/>
+      <c r="AP35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="5:42">
+      <c r="E36" s="16"/>
+      <c r="O36" s="2" t="str" cm="1">
+        <f t="array" ref="O36">_xlfn.TEXTJOIN(", ", TRUE, IF(NOT(ISNUMBER(P36:V36)), """" &amp; P36:V36 &amp; """", P36:V36))</f>
         <v>"item", "ice", 5, 5, 1, "item", "oxide-asteroid-chunk"</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R35" s="2">
+      <c r="P36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R36" s="2">
         <v>5</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S36" s="2">
         <v>5</v>
       </c>
-      <c r="T35" s="2">
-        <v>1</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP35" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="36" spans="5:42">
-      <c r="E36" s="17"/>
-      <c r="O36" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(", ", TRUE, P36:V36)</f>
+      <c r="T36" s="2">
+        <v>1</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="5:42">
+      <c r="E37" s="16"/>
+      <c r="O37" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(", ", TRUE, P37:V37)</f>
         <v>item, iron-ore, 10, 10, 1, item, copper-ore</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="R36" s="2">
+      <c r="P37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R37" s="2">
         <v>10</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S37" s="2">
         <v>10</v>
       </c>
-      <c r="T36" s="2">
-        <v>1</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP36" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="37" spans="5:42">
-      <c r="E37" s="17"/>
+      <c r="T37" s="2">
+        <v>1</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="AP37" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="5:42">
-      <c r="E38" s="17"/>
+      <c r="E38" s="16"/>
       <c r="AP38" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="5:42">
-      <c r="E39" s="17"/>
+      <c r="E39" s="16"/>
       <c r="AP39" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="5:42">
-      <c r="E40" s="17"/>
+      <c r="E40" s="16"/>
       <c r="AP40" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="5:42">
-      <c r="E41" s="17"/>
+      <c r="E41" s="16"/>
       <c r="AP41" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="5:42">
-      <c r="E42" s="17"/>
+      <c r="E42" s="16"/>
       <c r="AP42" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="5:42">
-      <c r="AL43" t="s">
-        <v>99</v>
+      <c r="E43" s="16"/>
+      <c r="AP43" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="5:42">
       <c r="AL44" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="5:42">
       <c r="AL45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="5:42">
       <c r="AL46" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="5:42">
       <c r="AL47" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="5:42">
       <c r="AL48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="38:38">
       <c r="AL49" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="38:38">
@@ -7427,12 +7588,12 @@
     </row>
     <row r="51" spans="38:38">
       <c r="AL51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="38:38">
       <c r="AL52" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="38:38">
@@ -7442,12 +7603,12 @@
     </row>
     <row r="54" spans="38:38">
       <c r="AL54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="38:38">
       <c r="AL55" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="38:38">
@@ -7457,21 +7618,26 @@
     </row>
     <row r="57" spans="38:38">
       <c r="AL57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="38:38">
       <c r="AL58" t="s">
-        <v>98</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="38:38">
+      <c r="AL59" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AL47:AL58">
-    <sortCondition ref="AL47:AL58"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AL48:AL59">
+    <sortCondition ref="AL48:AL59"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA14:AM14 F8:AM13 F14:Y14 C8:E26 F15:AM26 AP8:AP26">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="C8:E27 AP8:AP27 F14:Y14 AA14:AE14 F8:AM12 F13:AE13 F15:AE15 AF13:AM15 F16:AM18 F20:AM27 AE19:AM19 F19:Y19">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEN($D8) &gt; 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7521,7 +7687,7 @@
     <row r="5" spans="2:11" ht="15">
       <c r="B5" s="10"/>
       <c r="C5" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -7532,25 +7698,25 @@
         <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="15">
       <c r="B6" s="10"/>
       <c r="C6" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" ref="I6:I15" si="0">"""item"""</f>
@@ -7567,16 +7733,16 @@
     <row r="7" spans="2:11" ht="15">
       <c r="B7" s="10"/>
       <c r="C7" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>130</v>
-      </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
@@ -7593,16 +7759,16 @@
     <row r="8" spans="2:11" ht="15">
       <c r="B8" s="10"/>
       <c r="C8" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="0"/>
@@ -7619,16 +7785,16 @@
     <row r="9" spans="2:11" ht="15">
       <c r="B9" s="10"/>
       <c r="C9" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="0"/>
@@ -7645,16 +7811,16 @@
     <row r="10" spans="2:11" ht="15">
       <c r="B10" s="10"/>
       <c r="C10" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="0"/>
@@ -7671,16 +7837,16 @@
     <row r="11" spans="2:11" ht="15">
       <c r="B11" s="10"/>
       <c r="C11" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="0"/>
@@ -7697,16 +7863,16 @@
     <row r="12" spans="2:11" ht="15">
       <c r="B12" s="10"/>
       <c r="C12" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
@@ -7723,16 +7889,16 @@
     <row r="13" spans="2:11" ht="15">
       <c r="B13" s="10"/>
       <c r="C13" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="0"/>
@@ -7749,16 +7915,16 @@
     <row r="14" spans="2:11" ht="15">
       <c r="B14" s="10"/>
       <c r="C14" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="0"/>
@@ -7775,16 +7941,16 @@
     <row r="15" spans="2:11" ht="15">
       <c r="B15" s="10"/>
       <c r="C15" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="0"/>
@@ -7801,7 +7967,7 @@
     <row r="16" spans="2:11" ht="15">
       <c r="B16" s="10"/>
       <c r="C16" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>

--- a/Astra Notes.xlsx
+++ b/Astra Notes.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gwen\Documents\GitHub\Factorio-Astra-Asteroids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB34B3ED-8EF0-4EE0-A22C-575C8BE4DE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773FF3E3-F152-4A0C-9E7D-050331793804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{19A80CD4-A61D-4139-863E-8E630E8C5493}"/>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{B83F7878-8263-4A97-A1DF-A9E638B23B4E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{B83F7878-8263-4A97-A1DF-A9E638B23B4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,7 +74,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -90,25 +89,35 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="366">
   <si>
     <t>Metallic</t>
   </si>
@@ -14662,6 +14671,9 @@
   </si>
   <si>
     <t>"k[fulgora].z[special]"</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
 </sst>
 </file>
@@ -14838,7 +14850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -14908,11 +14920,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="119">
+  <dxfs count="120">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -15070,10 +15093,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -16222,23 +16241,23 @@
     <dataField name="Sum of EV" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="118">
+    <format dxfId="119">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="117">
+    <format dxfId="118">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="116">
+    <format dxfId="117">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="115">
+    <format dxfId="116">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="114">
+    <format dxfId="115">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="19">
@@ -16265,16 +16284,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="113">
+    <format dxfId="114">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="112">
+    <format dxfId="113">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="111">
+    <format dxfId="112">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="110">
+    <format dxfId="111">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="19">
@@ -16301,10 +16320,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="109">
+    <format dxfId="110">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="108">
+    <format dxfId="109">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="5">
@@ -16317,13 +16336,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="107">
+    <format dxfId="108">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="106">
+    <format dxfId="107">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="105">
+    <format dxfId="106">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="5">
@@ -16336,7 +16355,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="104">
+    <format dxfId="105">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -16427,7 +16446,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
     <v>1</v>
     <v>8</v>
@@ -16438,11 +16457,15 @@
     <v>13</v>
     <v>3</v>
   </rv>
+  <rv s="2">
+    <v>13</v>
+    <v>1</v>
+  </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <s t="_error">
     <k n="colOffset" t="i"/>
     <k n="errorType" t="i"/>
@@ -16453,54 +16476,58 @@
     <k n="errorType" t="i"/>
     <k n="subType" t="i"/>
   </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="propagated" t="b"/>
+  </s>
 </rvStructures>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}" name="Table4" displayName="Table4" ref="B3:AB25" totalsRowShown="0" headerRowDxfId="104">
   <autoFilter ref="B3:AB25" xr:uid="{9A0BFF85-5E25-44F5-989C-05E81AFBA27C}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{B1A354A2-D591-4F7C-89E1-AB75527E5993}" name="Recipe"/>
-    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="102">
+    <tableColumn id="27" xr3:uid="{1411294A-B7C7-4726-B55B-8DABEE6ED457}" name="energy_required" dataDxfId="103">
       <calculatedColumnFormula>INDEX(Table7[energy_required], MATCH(Table4[[#This Row],[Recipe]], Table7[Recipe], 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="101"/>
-    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="100"/>
-    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="99"/>
-    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="98"/>
-    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="97"/>
-    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="95">
+    <tableColumn id="2" xr3:uid="{7F80CA45-0C9C-4D9D-A37C-6DF3AD5E0BEB}" name="iron-ore" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{AC60A2AA-9D82-482D-A597-78045793B05D}" name="copper-ore" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{5029DD94-2977-4B99-94DB-19EA67D75D22}" name="carbon" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{52F010C3-27DB-43E9-A9D6-11A1C5DB092F}" name="sulfur" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{F06F185C-FC3F-465E-B9E4-758205B9F0F4}" name="ice" dataDxfId="98"/>
+    <tableColumn id="7" xr3:uid="{1554F3DE-DB8B-471F-922A-8D30297584F3}" name="calcite" dataDxfId="97"/>
+    <tableColumn id="8" xr3:uid="{E7F322CB-036A-403C-8BF8-6B20B8C6CCD1}" name="Oil Thing" dataDxfId="96">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(J$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="94">
+    <tableColumn id="26" xr3:uid="{C4622E41-2D57-42C3-A31B-EF19C158ACB5}" name="solid-fuel" dataDxfId="95">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(K$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="93"/>
-    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="91">
+    <tableColumn id="9" xr3:uid="{F529E26B-0253-4C02-95D8-95DB987CD83E}" name="coal" dataDxfId="94"/>
+    <tableColumn id="10" xr3:uid="{D18F88A9-729A-4165-BA55-675D11D2231A}" name="stone" dataDxfId="93"/>
+    <tableColumn id="11" xr3:uid="{57DAEF24-F8A7-492C-9706-2674BFBB49E1}" name="uranium-ore" dataDxfId="92">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.recipeResults, _xlfn._xlws.FILTER(Table7[[Results 1]:[Results 4]], Table7[Recipe] = Table4[[#This Row],[Recipe]]),
      IFERROR(
      _xlfn._xlws.FILTER(_xlpm.recipeResults, ISNUMBER(SEARCH(N$3, _xlpm.recipeResults))), " - ") )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="90"/>
-    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="88"/>
-    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="87"/>
-    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="86"/>
-    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="85"/>
-    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="84"/>
-    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="83"/>
-    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="82"/>
-    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="81"/>
-    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="80"/>
-    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="79"/>
-    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="78"/>
-    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="77"/>
+    <tableColumn id="23" xr3:uid="{688FF19F-43DB-4F57-B5C7-CB20C171B5A5}" name="uranium-238" dataDxfId="91"/>
+    <tableColumn id="24" xr3:uid="{8B59E641-D762-475E-BE04-0AD557DA2633}" name="uranium-235" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{49325880-AB22-406C-9EBF-F9714278E54F}" name="tungsten-ore" dataDxfId="89"/>
+    <tableColumn id="25" xr3:uid="{4B574229-0587-4E11-816D-60F689340097}" name="lava" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{876F7B27-7476-478B-9F55-220BB73A33D4}" name="scrap" dataDxfId="87"/>
+    <tableColumn id="14" xr3:uid="{1D9F494D-4B80-42A5-85C3-6484CB3803F7}" name="yumako-seed" dataDxfId="86"/>
+    <tableColumn id="15" xr3:uid="{CC0EBC6A-4432-4CBA-A41B-E7B6031BD83F}" name="jellynut-seed" dataDxfId="85"/>
+    <tableColumn id="16" xr3:uid="{2B7FB235-2E10-4FA1-BC7C-964E7947466A}" name="spoilage" dataDxfId="84"/>
+    <tableColumn id="17" xr3:uid="{CEE0F52B-14B0-48FB-AD2F-A1A1A9DACF76}" name="Dormant Pentapod Egg" dataDxfId="83"/>
+    <tableColumn id="18" xr3:uid="{F34385CF-1935-4968-8261-48F21ADB2D44}" name="(tbd) ammonia" dataDxfId="82"/>
+    <tableColumn id="19" xr3:uid="{405DEB99-0752-4FA5-BCC3-09F744698489}" name="(tbd) flourine" dataDxfId="81"/>
+    <tableColumn id="20" xr3:uid="{ADD7E20E-3FB5-4185-8AD9-7781DF09236F}" name="(tbd) lithium" dataDxfId="80"/>
+    <tableColumn id="21" xr3:uid="{82818854-DC1B-485E-9809-F8B0261BEDE0}" name="(tbd) promethium" dataDxfId="79"/>
+    <tableColumn id="22" xr3:uid="{5634330F-FEBB-4799-90EC-922642138192}" name="Holmium Solution" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16515,18 +16542,18 @@
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{EFD8865D-C9ED-4BA8-B73C-113EDAD68DA5}" name="Variable's Name"/>
     <tableColumn id="3" xr3:uid="{1A67492A-77CF-48AB-9609-594DA5CCF328}" name="name"/>
-    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="76">
+    <tableColumn id="2" xr3:uid="{587148E6-4B98-4DD4-8691-6E43006C9E89}" name="type" dataDxfId="77">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="75">
+    <tableColumn id="4" xr3:uid="{4C2D2AEB-4928-4F13-91B0-2184B98F54BD}" name="subgroup" dataDxfId="76">
       <calculatedColumnFormula>"""space-material"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{A45CDEC7-39DE-4333-8E31-011D04DA2762}" name="order"/>
     <tableColumn id="6" xr3:uid="{499C643B-C1ED-4A32-BE42-9946CC52BC6E}" name="icon"/>
-    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="74">
+    <tableColumn id="7" xr3:uid="{834AC55A-1278-424D-94B7-2EDF700340B6}" name="stack_size" dataDxfId="75">
       <calculatedColumnFormula>1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9145470B-0772-4705-8B45-24698F613F56}" name="full string" dataDxfId="73">
+    <tableColumn id="8" xr3:uid="{9145470B-0772-4705-8B45-24698F613F56}" name="full string" dataDxfId="74">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
 ", TRUE, Chunk_Items[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunk_Items[[#Headers],[name]:[stack_size]] &amp; " = " &amp; Chunk_Items[[#This Row],[name]:[stack_size]])</calculatedColumnFormula>
     </tableColumn>
@@ -16544,13 +16571,13 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9C8B2B85-651A-48F5-BE74-6B0CB5EC6401}" name="Variable's Name"/>
     <tableColumn id="3" xr3:uid="{5CB5E631-FE01-4CDD-A4B3-008A4C86A223}" name="name"/>
-    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="72">
+    <tableColumn id="2" xr3:uid="{36E1B303-2D0B-4894-BA0E-22315D6AA6E7}" name="type" dataDxfId="73">
       <calculatedColumnFormula>"""asteroid-chunk"""</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{33E8079D-0ADE-49CC-8F5F-FB561D1043C6}" name="minable" dataDxfId="72"/>
     <tableColumn id="5" xr3:uid="{2D398BB0-41AE-40CE-AA0F-6FA6647FFA57}" name="order"/>
     <tableColumn id="6" xr3:uid="{82F86FA9-1FFF-4AFF-A528-DD559BDA3930}" name="icon"/>
-    <tableColumn id="7" xr3:uid="{8D2BAF1D-A998-4CFE-AE20-A7C5A809314F}" name="full string" dataDxfId="70">
+    <tableColumn id="7" xr3:uid="{8D2BAF1D-A998-4CFE-AE20-A7C5A809314F}" name="full string" dataDxfId="71">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
 ", TRUE, Chunks[[#This Row],[Variable''s Name]] &amp; "." &amp; Chunks[[#Headers],[name]:[icon]] &amp; " = " &amp; Chunks[[#This Row],[name]:[icon]])</calculatedColumnFormula>
     </tableColumn>
@@ -16563,28 +16590,28 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E53CB6FB-2E2C-443B-95B1-3E2AFFD034E2}" name="Table7_1" displayName="Table7_1" ref="A1:Y21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Y21" xr:uid="{E53CB6FB-2E2C-443B-95B1-3E2AFFD034E2}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{25B70940-94F8-4DB8-88CD-A28BB25BF46D}" uniqueName="1" name="Recipe" queryTableFieldId="1" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{6938BA52-64B5-4541-85FE-0568CF57BE53}" uniqueName="2" name="Unwritten?" queryTableFieldId="2" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{25B70940-94F8-4DB8-88CD-A28BB25BF46D}" uniqueName="1" name="Recipe" queryTableFieldId="1" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{6938BA52-64B5-4541-85FE-0568CF57BE53}" uniqueName="2" name="Unwritten?" queryTableFieldId="2" dataDxfId="69"/>
     <tableColumn id="3" xr3:uid="{1B648304-5C74-4610-8A43-DF788A2F0682}" uniqueName="3" name="Advanced?" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{71899E0C-12BA-4960-936B-611EB515C0AC}" uniqueName="4" name="Variable's Name" queryTableFieldId="4" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{47AADCB0-91CC-4ACD-BC22-48C0ABAD5DDF}" uniqueName="5" name="name" queryTableFieldId="5" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{0AAE9926-1717-4A7C-81EF-968AF648698F}" uniqueName="6" name="Result_1_type" queryTableFieldId="6" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{B8E38A26-43C7-4117-B451-06DBBE98CF09}" uniqueName="7" name="Result_1_name" queryTableFieldId="7" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{71899E0C-12BA-4960-936B-611EB515C0AC}" uniqueName="4" name="Variable's Name" queryTableFieldId="4" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{47AADCB0-91CC-4ACD-BC22-48C0ABAD5DDF}" uniqueName="5" name="name" queryTableFieldId="5" dataDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{0AAE9926-1717-4A7C-81EF-968AF648698F}" uniqueName="6" name="Result_1_type" queryTableFieldId="6" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{B8E38A26-43C7-4117-B451-06DBBE98CF09}" uniqueName="7" name="Result_1_name" queryTableFieldId="7" dataDxfId="65"/>
     <tableColumn id="8" xr3:uid="{232E0949-6EC0-4070-B3B6-D5527152EC92}" uniqueName="8" name="Result_1_amt_min" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{406E71DF-32D1-4345-A52D-B7D3102D97F3}" uniqueName="9" name="Result_1_amt_max" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{D6695C50-86D7-422B-926F-5110F80F5466}" uniqueName="10" name="Result_1_P" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{12F89D76-7449-448D-98CC-D411D1475A3E}" uniqueName="11" name="Result_2_type" queryTableFieldId="11" dataDxfId="63"/>
-    <tableColumn id="12" xr3:uid="{586F2CF2-DA91-4E08-AD5D-AE1B76BC7EC0}" uniqueName="12" name="Result_2_name" queryTableFieldId="12" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{12F89D76-7449-448D-98CC-D411D1475A3E}" uniqueName="11" name="Result_2_type" queryTableFieldId="11" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{586F2CF2-DA91-4E08-AD5D-AE1B76BC7EC0}" uniqueName="12" name="Result_2_name" queryTableFieldId="12" dataDxfId="63"/>
     <tableColumn id="13" xr3:uid="{591FD322-8C8B-4CEA-ADEC-225C7718C7EA}" uniqueName="13" name="Result_2_amt_min" queryTableFieldId="13"/>
     <tableColumn id="14" xr3:uid="{35B09536-BD39-4556-A5A6-8B26833986F8}" uniqueName="14" name="Result_2_amt_max" queryTableFieldId="14"/>
     <tableColumn id="15" xr3:uid="{D7B93839-634E-4DAC-A31C-74371349085E}" uniqueName="15" name="Result_2_P" queryTableFieldId="15"/>
-    <tableColumn id="16" xr3:uid="{173610F8-5BDC-4DC9-8017-BD40CD5A84C2}" uniqueName="16" name="Result_3_type" queryTableFieldId="16" dataDxfId="61"/>
-    <tableColumn id="17" xr3:uid="{A26C6901-F141-49CF-93BE-A3486152942F}" uniqueName="17" name="Result_3_name" queryTableFieldId="17" dataDxfId="60"/>
+    <tableColumn id="16" xr3:uid="{173610F8-5BDC-4DC9-8017-BD40CD5A84C2}" uniqueName="16" name="Result_3_type" queryTableFieldId="16" dataDxfId="62"/>
+    <tableColumn id="17" xr3:uid="{A26C6901-F141-49CF-93BE-A3486152942F}" uniqueName="17" name="Result_3_name" queryTableFieldId="17" dataDxfId="61"/>
     <tableColumn id="18" xr3:uid="{9D777C1E-B7F3-4D13-9252-6FA1242AC1C6}" uniqueName="18" name="Result_3_amt_min" queryTableFieldId="18"/>
     <tableColumn id="19" xr3:uid="{B85EEF5E-B938-4781-8FDD-89BA612694AB}" uniqueName="19" name="Result_3_amt_max" queryTableFieldId="19"/>
     <tableColumn id="20" xr3:uid="{CF44E894-9365-4B08-A015-D19576C0C054}" uniqueName="20" name="Result_3_P" queryTableFieldId="20"/>
-    <tableColumn id="21" xr3:uid="{4191E007-5B61-405E-834E-CB82EC4E6D01}" uniqueName="21" name="Result_4_type" queryTableFieldId="21" dataDxfId="59"/>
-    <tableColumn id="22" xr3:uid="{6E00A2BA-308B-4E79-AE13-BA2B7FF3266E}" uniqueName="22" name="Result_4_name" queryTableFieldId="22" dataDxfId="58"/>
+    <tableColumn id="21" xr3:uid="{4191E007-5B61-405E-834E-CB82EC4E6D01}" uniqueName="21" name="Result_4_type" queryTableFieldId="21" dataDxfId="60"/>
+    <tableColumn id="22" xr3:uid="{6E00A2BA-308B-4E79-AE13-BA2B7FF3266E}" uniqueName="22" name="Result_4_name" queryTableFieldId="22" dataDxfId="59"/>
     <tableColumn id="23" xr3:uid="{B08DA47E-615C-42A2-B48F-E089661FB480}" uniqueName="23" name="Result_4_amt_min" queryTableFieldId="23"/>
     <tableColumn id="24" xr3:uid="{80FE8B91-761C-4A2E-84E2-899EEE89286A}" uniqueName="24" name="Result_4_amt_max" queryTableFieldId="24"/>
     <tableColumn id="25" xr3:uid="{B57634A6-34CE-4EA5-9B05-C8F84F58A41A}" uniqueName="25" name="Result_4_P" queryTableFieldId="25"/>
@@ -16594,126 +16621,126 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="C7:AP28" totalsRowShown="0" headerRowDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}" name="Table7" displayName="Table7" ref="C7:AP28" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="C7:AP28" xr:uid="{996E5AF8-4762-451C-9EC5-44266BFF352B}"/>
   <tableColumns count="40">
     <tableColumn id="1" xr3:uid="{1C7B22C3-8503-40CA-B985-0F11F98EB3C6}" name="Recipe"/>
-    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="56"/>
-    <tableColumn id="41" xr3:uid="{6E5608DA-75C3-48D4-92AF-824B8C6B9141}" name="Advanced?" dataDxfId="55">
+    <tableColumn id="12" xr3:uid="{44C30B7E-3F48-43EE-A476-EAF4BA20C75A}" name="Unwritten?" dataDxfId="57"/>
+    <tableColumn id="41" xr3:uid="{6E5608DA-75C3-48D4-92AF-824B8C6B9141}" name="Advanced?" dataDxfId="56">
       <calculatedColumnFormula>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{D73BFE2A-2B7F-460C-B8F4-2293AE8F1CDF}" name="Variable's Name" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="46"/>
-    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{8EF822E8-07FB-4876-8800-25F2A9B81873}" name="Result_1_type" dataDxfId="0">
+    <tableColumn id="39" xr3:uid="{D73BFE2A-2B7F-460C-B8F4-2293AE8F1CDF}" name="Variable's Name" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{E995243B-09A0-4B61-9891-2750A2869DC3}" name="name" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{503397F1-8755-4CF0-8F78-A9F7740B5790}" name="icon" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{68F82173-B464-4B40-AC23-3E4F9BE9F52A}" name="order" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{41FF6C48-F0D3-46AF-A21F-51ACC01FAB0C}" name="enabled" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{D9A98507-2FB7-4229-B1C0-4B1DA8557E9F}" name="energy_required" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{49007205-346D-4C29-AD68-C79FA0EA720B}" name="Ingredient 1" dataDxfId="49"/>
+    <tableColumn id="15" xr3:uid="{805B845F-9765-4945-826D-8F506E139BE2}" name="Ingredient 2" dataDxfId="48"/>
+    <tableColumn id="16" xr3:uid="{D892DCC1-CA40-40C6-A026-DE02CB8B8541}" name="Ingredient 1 Amount" dataDxfId="47"/>
+    <tableColumn id="17" xr3:uid="{043F0671-10F0-435E-93F6-76D671AC8761}" name="Ingredient 2 Amount" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{8EF822E8-07FB-4876-8800-25F2A9B81873}" name="Result_1_type" dataDxfId="2">
       <calculatedColumnFormula array="1">INDEX(Table8[type], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="20">
+    <tableColumn id="30" xr3:uid="{36B4E4F7-052E-4455-A6CA-FFCC3E9245F7}" name="Result_1_name" dataDxfId="22">
       <calculatedColumnFormula array="1">INDEX(Table8[name], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="19">
+    <tableColumn id="27" xr3:uid="{9C3D4CEF-5F40-4B68-BD87-448388551748}" name="Result_1_amt_min" dataDxfId="21">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_min], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="18">
+    <tableColumn id="26" xr3:uid="{F871C881-69CD-4795-AB43-8B752D2E5250}" name="Result_1_amt_max" dataDxfId="20">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_max], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="17">
+    <tableColumn id="28" xr3:uid="{6E355266-0C10-4989-9F5C-656E5531B809}" name="Result_1_P" dataDxfId="19">
       <calculatedColumnFormula array="1">INDEX(Table8[P], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{F666EFD4-EFAB-4ED2-9F8C-93F381615487}" name="Result_2_type" dataDxfId="15">
+    <tableColumn id="34" xr3:uid="{F666EFD4-EFAB-4ED2-9F8C-93F381615487}" name="Result_2_type" dataDxfId="17">
       <calculatedColumnFormula array="1">INDEX(Table8[type], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="14">
+    <tableColumn id="31" xr3:uid="{EBAA7D64-5ABB-4E65-8B5B-00682D717ECF}" name="Result_2_name" dataDxfId="16">
       <calculatedColumnFormula array="1">INDEX(Table8[name], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="13">
+    <tableColumn id="22" xr3:uid="{0F604324-0BE1-40EA-BC68-971D78B203CD}" name="Result_2_amt_min" dataDxfId="15">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_min], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="12">
+    <tableColumn id="29" xr3:uid="{95845240-17DF-4258-A672-6BC4AC4F0623}" name="Result_2_amt_max" dataDxfId="14">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_max], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="11">
+    <tableColumn id="23" xr3:uid="{F05C630D-F7F6-4014-91DB-C5753DF18CBC}" name="Result_2_P" dataDxfId="13">
       <calculatedColumnFormula array="1">INDEX(Table8[P], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{29FDA9C5-AC15-474C-B065-A8F35BA59418}" name="Result_3_type" dataDxfId="10">
+    <tableColumn id="35" xr3:uid="{29FDA9C5-AC15-474C-B065-A8F35BA59418}" name="Result_3_type" dataDxfId="12">
       <calculatedColumnFormula array="1">INDEX(Table8[type], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="9">
+    <tableColumn id="32" xr3:uid="{9317562F-B7E9-490E-BFBC-0F03122AB5F9}" name="Result_3_name" dataDxfId="11">
       <calculatedColumnFormula array="1">INDEX(Table8[name], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="8">
+    <tableColumn id="25" xr3:uid="{04B02B68-0016-44BE-8B0D-6E6053EB4293}" name="Result_3_amt_min" dataDxfId="10">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_min], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="7">
+    <tableColumn id="24" xr3:uid="{4A76DB66-F126-4A19-B7B9-052150F5EC16}" name="Result_3_amt_max" dataDxfId="9">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_max], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="6">
+    <tableColumn id="18" xr3:uid="{1834E88C-3996-4B83-A2D6-E4CBF6799983}" name="Result_3_P" dataDxfId="8">
       <calculatedColumnFormula array="1">INDEX(Table8[P], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{5C2D1484-E711-4E82-92DB-57B04BD66315}" name="Result_4_type" dataDxfId="5">
+    <tableColumn id="36" xr3:uid="{5C2D1484-E711-4E82-92DB-57B04BD66315}" name="Result_4_type" dataDxfId="7">
       <calculatedColumnFormula array="1">INDEX(Table8[type], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="4">
+    <tableColumn id="33" xr3:uid="{5A6880AC-0CDF-4FF5-95A6-EF019821685D}" name="Result_4_name" dataDxfId="6">
       <calculatedColumnFormula array="1">INDEX(Table8[name], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="3">
+    <tableColumn id="20" xr3:uid="{F27B8545-BFA0-4FA2-BC1B-A026F34E43F0}" name="Result_4_amt_min" dataDxfId="5">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_min], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="2">
+    <tableColumn id="19" xr3:uid="{A869DC81-85C7-4615-8A5E-CD93FEADF931}" name="Result_4_amt_max" dataDxfId="4">
       <calculatedColumnFormula array="1">INDEX(Table8[amount_max], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="1">
+    <tableColumn id="21" xr3:uid="{C5FEE21E-C6E2-49F8-AD36-B9EED8A7B149}" name="Result_4_P" dataDxfId="3">
       <calculatedColumnFormula array="1">INDEX(Table8[P], MATCH(Table7[[#This Row],[Recipe]], Table8[Recipe], 0) + 3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1" dataDxfId="44">
+    <tableColumn id="8" xr3:uid="{33C291CA-AEA3-41A6-8665-03327AB3E806}" name="Results 1" dataDxfId="45">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_1_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_1_type]:[Result_1_P]])), """" &amp; Table7[[#This Row],[Result_1_type]:[Result_1_P]] &amp; """", Table7[[#This Row],[Result_1_type]:[Result_1_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2" dataDxfId="43">
+    <tableColumn id="9" xr3:uid="{7BF645B9-19D0-4473-ACE6-12B66A8165AE}" name="Results 2" dataDxfId="44">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_2_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_2_type]:[Result_2_P]])), """" &amp; Table7[[#This Row],[Result_2_type]:[Result_2_P]] &amp; """", Table7[[#This Row],[Result_2_type]:[Result_2_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3" dataDxfId="42">
+    <tableColumn id="10" xr3:uid="{73804FC8-69EB-4E05-8650-4BB574DE531D}" name="Results 3" dataDxfId="43">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_3_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_3_type]:[Result_3_P]])), """" &amp; Table7[[#This Row],[Result_3_type]:[Result_3_P]] &amp; """", Table7[[#This Row],[Result_3_type]:[Result_3_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{6B40EA3E-9F3D-4135-BC18-3EC5AE95AEF0}" name="Results 4" dataDxfId="42">
       <calculatedColumnFormula array="1">IF(ISBLANK(Table7[[#This Row],[Result_4_type]]), FALSE, "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table7[[#This Row],[Result_4_type]:[Result_4_P]])), """" &amp; Table7[[#This Row],[Result_4_type]:[Result_4_P]] &amp; """", Table7[[#This Row],[Result_4_type]:[Result_4_P]]) ) &amp;
   " }" )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="40">
+    <tableColumn id="13" xr3:uid="{983E9E0D-A8BE-4A49-88C0-0F9647C154FB}" name="Ingredient String" dataDxfId="41">
       <calculatedColumnFormula array="1" xml:space="preserve"> "{ " &amp;
  _xlfn.TEXTJOIN(", ",
           TRUE,
           "{ type = ""item"", name = """ &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1]:[Ingredient 2]]) &amp; """, amount = " &amp; _xlfn.TRIMRANGE(Table7[[#This Row],[Ingredient 1 Amount]:[Ingredient 2 Amount]]) &amp; " }")
 &amp; " }"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{D9725653-650B-4E33-86E4-FA48D30F5455}" name="Results String" dataDxfId="39">
+    <tableColumn id="37" xr3:uid="{D9725653-650B-4E33-86E4-FA48D30F5455}" name="Results String" dataDxfId="0">
       <calculatedColumnFormula array="1" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{6A447D5A-EAF2-404F-A826-F6177D7B50D6}" name="Whole String" dataDxfId="38">
+    <tableColumn id="40" xr3:uid="{6A447D5A-EAF2-404F-A826-F6177D7B50D6}" name="Whole String" dataDxfId="40">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
@@ -16725,29 +16752,36 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EA71830A-828F-4695-B2FD-24C049275861}" name="Table8" displayName="Table8" ref="B3:K59" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
-  <autoFilter ref="B3:K59" xr:uid="{EA71830A-828F-4695-B2FD-24C049275861}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EA71830A-828F-4695-B2FD-24C049275861}" name="Table8" displayName="Table8" ref="B3:L59" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+  <autoFilter ref="B3:L59" xr:uid="{EA71830A-828F-4695-B2FD-24C049275861}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:K59">
     <sortCondition descending="1" ref="B3:B59"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{125DA46D-9742-4063-80AF-7B3BD16A90B4}" name="Recipe" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{FB3F6848-8BA0-4CF9-94C5-347F36A39CF0}" name="type" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{2F1240D4-2D99-4EA6-9B56-7EE74D6AFB8B}" name="name" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{3BB9F2BA-0C22-4457-A366-03C34CF2C7C7}" name="amount_min" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{3D12B4DB-2238-43D9-B668-BBD3ED397240}" name="amount_max" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{218ABFBF-C1D6-4C94-A67C-3C2D682E3A95}" name="P" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{5E531594-85F5-4CD1-B27E-BC7800E08050}" name="Duration" dataDxfId="29">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{125DA46D-9742-4063-80AF-7B3BD16A90B4}" name="Recipe" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{FB3F6848-8BA0-4CF9-94C5-347F36A39CF0}" name="type" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{2F1240D4-2D99-4EA6-9B56-7EE74D6AFB8B}" name="name" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{3BB9F2BA-0C22-4457-A366-03C34CF2C7C7}" name="amount_min" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{3D12B4DB-2238-43D9-B668-BBD3ED397240}" name="amount_max" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{218ABFBF-C1D6-4C94-A67C-3C2D682E3A95}" name="P" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{5E531594-85F5-4CD1-B27E-BC7800E08050}" name="Duration" dataDxfId="31">
       <calculatedColumnFormula>INDEX(Table7[energy_required], MATCH(Table8[[#This Row],[Recipe]], Table7[Recipe], 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3EF6D105-597F-4C54-B302-4F46B4BD461A}" name="EV" dataDxfId="28">
+    <tableColumn id="7" xr3:uid="{3EF6D105-597F-4C54-B302-4F46B4BD461A}" name="EV" dataDxfId="30">
       <calculatedColumnFormula>AVERAGE(Table8[[#This Row],[amount_min]], Table8[[#This Row],[amount_max]]) * Table8[[#This Row],[P]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{0DE8515B-F44B-493D-B0E5-618AD508AA55}" name="EV/s" dataDxfId="27">
+    <tableColumn id="9" xr3:uid="{0DE8515B-F44B-493D-B0E5-618AD508AA55}" name="EV/s" dataDxfId="29">
       <calculatedColumnFormula>Table8[[#This Row],[EV]] / Table8[[#This Row],[Duration]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2B62D157-F7A9-40B5-828B-0C9C0816CD17}" name="s/EV" dataDxfId="26">
+    <tableColumn id="10" xr3:uid="{2B62D157-F7A9-40B5-828B-0C9C0816CD17}" name="s/EV" dataDxfId="28">
       <calculatedColumnFormula>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{4856F71F-096D-4C64-84BD-AB3EF681F7DF}" name="string" dataDxfId="1">
+      <calculatedColumnFormula array="1">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -16759,11 +16793,11 @@
   <autoFilter ref="H5:K15" xr:uid="{8FC02366-D4DD-41A4-8050-773DDA42B27E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{959EF51D-F84A-47B3-BB90-19C907903580}" name="name"/>
-    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="25">
+    <tableColumn id="2" xr3:uid="{C3C91221-23BC-4002-9309-7C9CD86A66DB}" name="type" dataDxfId="27">
       <calculatedColumnFormula>"""item"""</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{214E8F8E-48B4-4BB8-B3A1-54F2A217D484}" name="amount"/>
-    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="24">
+    <tableColumn id="7" xr3:uid="{24D768D4-2DBF-4BCF-BF27-3E53FCF0468E}" name="line items" dataDxfId="26">
       <calculatedColumnFormula array="1">"    { " &amp; _xlfn.TEXTJOIN(", ", TRUE, Table1[[#Headers],[name]:[amount]] &amp; " = " &amp; Table1[[#This Row],[name]:[amount]]) &amp; " }"</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18687,7 +18721,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B17:AB17">
-    <cfRule type="expression" dxfId="23" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="1" stopIfTrue="1">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20367,9 +20401,6 @@
 local gleba_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
 local fulgoran_asteroid_chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
 local aquilo-asteroid-chunk_crushing = table.deepcopy(data.raw.recipe["metallic-asteroid-crushing"])
-local  = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
-local  = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
-local  = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
 local vulcanis_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
 local nauvis_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
 local gleba_asteroid_chunk_crushing_adv = table.deepcopy(data.raw.recipe["advanced-metallic-asteroid-crushing"])
@@ -20388,10 +20419,156 @@
       <c r="B4" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="12" t="e" cm="1">
+      <c r="C4" s="12" t="str" cm="1">
         <f t="array" ref="C4">_xlfn.TEXTJOIN("
 ", TRUE, _xlfn._xlws.FILTER(Table7[Whole String], ISBLANK(Table7[Unwritten?])))</f>
-        <v>#REF!</v>
+        <v>crude_asteroid_chunk_crushing.name = "astra-crude-asteroid-crushing"
+crude_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+crude_asteroid_chunk_crushing.order = "g[crude].a[basic]"
+crude_asteroid_chunk_crushing.enabled = false
+crude_asteroid_chunk_crushing.energy_required = 2
+crude_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }
+crude_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
+    { type = "item", name = "astra-oilstone", amount_min = 4, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+}
+vulcanus_asteroid_chunk_crushing.name = "astra-vulcanus-asteroid-crushing"
+vulcanus_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanus_asteroid_chunk_crushing.order = "i[vulcanus].a[basic]"
+vulcanus_asteroid_chunk_crushing.enabled = false
+vulcanus_asteroid_chunk_crushing.energy_required = 2
+vulcanus_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }
+vulcanus_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 } 
+}
+nauvis_asteroid_chunk_crushing.name = "astra-nauvis-asteroid-crushing"
+nauvis_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
+nauvis_asteroid_chunk_crushing.order = "h[nauvis].a[basic]"
+nauvis_asteroid_chunk_crushing.enabled = false
+nauvis_asteroid_chunk_crushing.energy_required = 2
+nauvis_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }
+nauvis_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "uranium-ore", amount_min = 10, amount_max = 12, probability = 1 } 
+}
+gleba_asteroid_chunk_crushing.name = "astra-gleba-asteroid-crushing"
+gleba_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/gleba_crushing_basic.png"
+gleba_asteroid_chunk_crushing.order = "j[gleba].a[basic]"
+gleba_asteroid_chunk_crushing.enabled = false
+gleba_asteroid_chunk_crushing.energy_required = 2
+gleba_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }
+gleba_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
+    { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.1 }, 
+    { type = "item", name = "spoilage", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.1 } 
+}
+fulgoran_asteroid_chunk_crushing.name = "astra-fulgoran-asteroid-crushing"
+fulgoran_asteroid_chunk_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_asteroid_chunk_crushing.order = "k[fulgora].a[basic]"
+fulgoran_asteroid_chunk_crushing.enabled = false
+fulgoran_asteroid_chunk_crushing.energy_required = 2
+fulgoran_asteroid_chunk_crushing.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }
+fulgoran_asteroid_chunk_crushing.results = { 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
+    { type = "item", name = "scrap", amount_min = 5, amount_max = 10, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 } 
+}
+aquilo-asteroid-chunk_crushing.name = "astra-aquilo-asteroid-crushing"
+aquilo-asteroid-chunk_crushing.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+aquilo-asteroid-chunk_crushing.order = "l[aquilo].a[basic]"
+aquilo-asteroid-chunk_crushing.enabled = false
+aquilo-asteroid-chunk_crushing.energy_required = 2
+aquilo-asteroid-chunk_crushing.ingredients = { { type = "item", name = "astra-aquilo-asteroid-chunk", amount = 1 } }
+aquilo-asteroid-chunk_crushing.results = { 
+    { type = "item", name = "astra-aquilo-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
+    { type = "item", name = "lithium", amount_min = 2, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+}
+vulcanis_asteroid_chunk_crushing_adv.name = "astra-advanced-vulcanis-asteroid-crushing"
+vulcanis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanis_asteroid_chunk_crushing_adv.order = "i[vulcanus].b[adv]"
+vulcanis_asteroid_chunk_crushing_adv.enabled = false
+vulcanis_asteroid_chunk_crushing_adv.energy_required = 5
+vulcanis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 } }
+vulcanis_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 14, probability = 1 } 
+}
+nauvis_asteroid_chunk_crushing_adv.name = "astra-advanced-nauvis-asteroid-crushing"
+nauvis_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/nauvis_crushing_basic.png"
+nauvis_asteroid_chunk_crushing_adv.order = "h[nauvis].b[adv]"
+nauvis_asteroid_chunk_crushing_adv.enabled = false
+nauvis_asteroid_chunk_crushing_adv.energy_required = 5
+nauvis_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }
+nauvis_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }, 
+    { type = "item", name = "uranium-235", amount_min = 1, amount_max = 1, probability = 0.3 }, 
+    { type = "item", name = "uranium-238", amount_min = 3, amount_max = 5, probability = 1 } 
+}
+gleba_asteroid_chunk_crushing_adv.name = "astra-advanced-gleba-asteroid-crushing"
+gleba_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/gleba_crushing_basic.png"
+gleba_asteroid_chunk_crushing_adv.order = "j[gleba].b[adv]"
+gleba_asteroid_chunk_crushing_adv.enabled = false
+gleba_asteroid_chunk_crushing_adv.energy_required = 5
+gleba_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }
+gleba_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 2, probability = 0.3 }, 
+    { type = "item", name = "spoilage", amount_min = 10, amount_max = 20, probability = 1 }, 
+    { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 2, probability = 0.3 } 
+}
+fulgoran_asteroid_chunk_crushing_adv.name = "astra-advanced-fulgoran-asteroid-crushing"
+fulgoran_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_asteroid_chunk_crushing_adv.order = "k[fulgora].b[adv]"
+fulgoran_asteroid_chunk_crushing_adv.enabled = false
+fulgoran_asteroid_chunk_crushing_adv.energy_required = 5
+fulgoran_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 } }
+fulgoran_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "holmium-ore", amount_min = 1, amount_max = 2, probability = 0.4 }, 
+    { type = "item", name = "scrap", amount_min = 10, amount_max = 15, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 } 
+}
+crude_asteroid_chunk_crushing_adv.name = "astra-advanced-crude-asteroid-crushing"
+crude_asteroid_chunk_crushing_adv.icon = "__Astra-Asteroids__/graphics/crude_crushing_basic.png"
+crude_asteroid_chunk_crushing_adv.order = "g[crude].b[adv]"
+crude_asteroid_chunk_crushing_adv.enabled = false
+crude_asteroid_chunk_crushing_adv.energy_required = 5
+crude_asteroid_chunk_crushing_adv.ingredients = { { type = "item", name = "astra-crude-asteroid-chunk", amount = 1 } }
+crude_asteroid_chunk_crushing_adv.results = { 
+    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
+    { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 8, probability = 1 }, 
+    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 } 
+}
+vulcanus_special_crushing.name = "astra-vulcanus-special-crushing"
+vulcanus_special_crushing.icon = "__Astra-Asteroids__/graphics/vulcanus_crushing_basic.png"
+vulcanus_special_crushing.order = "i[vulcanus].z[special]"
+vulcanus_special_crushing.enabled = false
+vulcanus_special_crushing.energy_required = 5
+vulcanus_special_crushing.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
+vulcanus_special_crushing.results = { 
+    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
+}
+fulgoran_special_crushing.name = "astra-fulgoran-special-crushing"
+fulgoran_special_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_special_crushing.order = "k[fulgora].z[special]"
+fulgoran_special_crushing.enabled = false
+fulgoran_special_crushing.energy_required = 10
+fulgoran_special_crushing.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }
+fulgoran_special_crushing.results = { 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+}</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>193</v>
@@ -20685,13 +20862,11 @@
       <c r="AO8" s="14" t="str" cm="1">
         <f t="array" ref="AO8" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "ice", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
-    { type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
 }</v>
       </c>
       <c r="AP8" s="15" t="str" cm="1">
@@ -20707,9 +20882,7 @@
 .ingredients = { { type = "item", name = "oxide-asteroid-chunk", amount = 1 } }
 .results = { 
     { type = "item", name = "ice", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
-    { type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
 }</v>
       </c>
     </row>
@@ -20866,13 +21039,10 @@
       <c r="AO9" s="14" t="str" cm="1">
         <f t="array" ref="AO9" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
-    { type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
-    { type = "item", name = "astra-oilstone", amount_min = 4, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+    { type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 } 
 }</v>
       </c>
       <c r="AP9" s="15" t="str" cm="1">
@@ -20887,10 +21057,7 @@
 .energy_required = 2
 .ingredients = { { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
 .results = { 
-    { type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
-    { type = "item", name = "astra-oilstone", amount_min = 4, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+    { type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -21050,13 +21217,12 @@
       <c r="AO10" s="14" t="str" cm="1">
         <f t="array" ref="AO10" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "astra-oilstone", amount_min = 4, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
 }</v>
       </c>
       <c r="AP10" s="15" t="str" cm="1">
@@ -21073,8 +21239,7 @@
 crude_asteroid_chunk_crushing.results = { 
     { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "astra-oilstone", amount_min = 4, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -21231,13 +21396,10 @@
       <c r="AO11" s="14" t="str" cm="1">
         <f t="array" ref="AO11" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
-    { type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 } 
+    { type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 } 
 }</v>
       </c>
       <c r="AP11" s="15" t="str" cm="1">
@@ -21252,10 +21414,7 @@
 .energy_required = 2
 .ingredients = { { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }
 .results = { 
-    { type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 } 
+    { type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -21415,13 +21574,12 @@
       <c r="AO12" s="14" t="str" cm="1">
         <f t="array" ref="AO12" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 } 
 }</v>
       </c>
       <c r="AP12" s="15" t="str" cm="1">
@@ -21438,8 +21596,7 @@
 vulcanus_asteroid_chunk_crushing.results = { 
     { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -21599,13 +21756,12 @@
       <c r="AO13" s="14" t="str" cm="1">
         <f t="array" ref="AO13" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "uranium-ore", amount_min = 10, amount_max = 12, probability = 1 }, 
-    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "uranium-ore", amount_min = 10, amount_max = 12, probability = 1 } 
 }</v>
       </c>
       <c r="AP13" s="15" t="str" cm="1">
@@ -21622,8 +21778,7 @@
 nauvis_asteroid_chunk_crushing.results = { 
     { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "uranium-ore", amount_min = 10, amount_max = 12, probability = 1 }, 
-    { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "uranium-ore", amount_min = 10, amount_max = 12, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -21783,13 +21938,14 @@
       <c r="AO14" s="14" t="str" cm="1">
         <f t="array" ref="AO14" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.1 }, 
     { type = "item", name = "spoilage", amount_min = 5, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.1 } 
 }</v>
       </c>
       <c r="AP14" s="15" t="str" cm="1">
@@ -21807,7 +21963,8 @@
     { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.1 }, 
     { type = "item", name = "spoilage", amount_min = 5, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
+    { type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.1 } 
 }</v>
       </c>
     </row>
@@ -21967,13 +22124,12 @@
       <c r="AO15" s="14" t="str" cm="1">
         <f t="array" ref="AO15" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "scrap", amount_min = 5, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }, 
-    { type = "item", name = "astra-aquilo-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 } 
 }</v>
       </c>
       <c r="AP15" s="15" t="str" cm="1">
@@ -21990,8 +22146,7 @@
 fulgoran_asteroid_chunk_crushing.results = { 
     { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "scrap", amount_min = 5, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }, 
-    { type = "item", name = "astra-aquilo-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 } 
+    { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -22151,13 +22306,12 @@
       <c r="AO16" s="14" t="str" cm="1">
         <f t="array" ref="AO16" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-aquilo-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "lithium", amount_min = 2, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
 }</v>
       </c>
       <c r="AP16" s="15" t="str" cm="1">
@@ -22174,14 +22328,16 @@
 aquilo-asteroid-chunk_crushing.results = { 
     { type = "item", name = "astra-aquilo-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }, 
     { type = "item", name = "lithium", amount_min = 2, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }, 
-    { type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 } 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
 }</v>
       </c>
     </row>
     <row r="17" spans="3:42" ht="18.75" customHeight="1">
       <c r="C17" t="s">
         <v>105</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E17" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
@@ -22329,13 +22485,12 @@
       <c r="AO17" s="14" t="str" cm="1">
         <f t="array" ref="AO17" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 }, 
     { type = "item", name = "ice", amount_min = 3, amount_max = 3, probability = 1 }, 
-    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 } 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
       <c r="AP17" s="15" t="str" cm="1">
@@ -22352,14 +22507,16 @@
 .results = { 
     { type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 }, 
     { type = "item", name = "ice", amount_min = 3, amount_max = 3, probability = 1 }, 
-    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 } 
+    { type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
     <row r="18" spans="3:42" ht="18.75" customHeight="1">
       <c r="C18" t="s">
         <v>103</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E18" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
@@ -22507,13 +22664,12 @@
       <c r="AO18" s="14" t="str" cm="1">
         <f t="array" ref="AO18" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 }, 
     { type = "item", name = "iron-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 } 
+    { type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
       <c r="AP18" s="15" t="str" cm="1">
@@ -22530,14 +22686,16 @@
 .results = { 
     { type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 }, 
     { type = "item", name = "iron-ore", amount_min = 10, amount_max = 10, probability = 1 }, 
-    { type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 } 
+    { type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
 }</v>
       </c>
     </row>
     <row r="19" spans="3:42" ht="18.75" customHeight="1">
       <c r="C19" t="s">
         <v>104</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E19" s="2" t="b">
         <f>OR(ISNUMBER(SEARCH("Adv", Table7[[#This Row],[Recipe]])), ISNUMBER(SEARCH("Special", Table7[[#This Row],[Recipe]])))</f>
@@ -22685,13 +22843,12 @@
       <c r="AO19" s="14" t="str" cm="1">
         <f t="array" ref="AO19" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 }, 
     { type = "item", name = "carbonic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 }, 
-    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 } 
 }</v>
       </c>
       <c r="AP19" s="15" t="str" cm="1">
@@ -22708,8 +22865,7 @@
 .results = { 
     { type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 }, 
     { type = "item", name = "carbonic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
-    { type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 }, 
-    { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -22869,13 +23025,12 @@
       <c r="AO20" s="14" t="str" cm="1">
         <f t="array" ref="AO20" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
     { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 14, probability = 1 }, 
-    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 14, probability = 1 } 
 }</v>
       </c>
       <c r="AP20" s="15" t="str" cm="1">
@@ -22892,8 +23047,7 @@
 vulcanis_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
     { type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 14, probability = 1 }, 
-    { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 } 
+    { type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 14, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -23053,7 +23207,7 @@
       <c r="AO21" s="14" t="str" cm="1">
         <f t="array" ref="AO21" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
@@ -23237,7 +23391,7 @@
       <c r="AO22" s="14" t="str" cm="1">
         <f t="array" ref="AO22" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
@@ -23421,7 +23575,7 @@
       <c r="AO23" s="14" t="str" cm="1">
         <f t="array" ref="AO23" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
@@ -23605,13 +23759,12 @@
       <c r="AO24" s="14" t="str" cm="1">
         <f t="array" ref="AO24" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
     { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 8, probability = 1 }, 
-    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }, 
-    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 } 
+    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 } 
 }</v>
       </c>
       <c r="AP24" s="15" t="str" cm="1">
@@ -23628,8 +23781,7 @@
 crude_asteroid_chunk_crushing_adv.results = { 
     { type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }, 
     { type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 8, probability = 1 }, 
-    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }, 
-    { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 } 
+    { type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -23794,13 +23946,11 @@
       <c r="AO25" s="14" t="str" cm="1">
         <f t="array" ref="AO25" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
         <v>{ 
     { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 }, 
-    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
 }</v>
       </c>
       <c r="AP25" s="15" t="str" cm="1">
@@ -23816,9 +23966,7 @@
 vulcanus_special_crushing.ingredients = { { type = "item", name = "astra-vulcanic-asteroid-chunk", amount = 1 }, { type = "item", name = "metallic-astroid-chunk", amount = 1 } }
 vulcanus_special_crushing.results = { 
     { type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }, 
-    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 }, 
-    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
-    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 } 
+    { type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 } 
 }</v>
       </c>
     </row>
@@ -23978,19 +24126,19 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "astra-nauvis-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO26" s="14" t="e" cm="1">
+      <c r="AO26" s="14" t="e" cm="1" vm="2">
         <f t="array" ref="AO26" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AP26" s="15" t="e" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP26" s="15" t="e" cm="1" vm="3">
         <f t="array" ref="AP26">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="3:42" ht="18.75" customHeight="1">
@@ -24149,19 +24297,19 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "astra-gleba-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO27" s="14" t="e" cm="1">
+      <c r="AO27" s="14" t="e" cm="1" vm="2">
         <f t="array" ref="AO27" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AP27" s="15" t="e" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AP27" s="15" t="e" cm="1" vm="3">
         <f t="array" ref="AP27">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>#N/A</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="3:42" ht="23.25" customHeight="1">
@@ -24322,19 +24470,33 @@
 &amp; " }"</f>
         <v>{ { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }</v>
       </c>
-      <c r="AO28" s="14" t="e" cm="1">
+      <c r="AO28" s="14" t="str" cm="1">
         <f t="array" ref="AO28" xml:space="preserve"> "{ 
     " &amp; _xlfn.TEXTJOIN(", 
-    ", TRUE, _xlfn._xlws.FILTER(Table7[[#This Row],[Results 1]:[Results 4]], IFERROR(--Table7[[#This Row],[Results 1]:[Results 4]], TRUE))) &amp; " 
+    ", TRUE, _xlfn._xlws.FILTER(Table8[string], Table8[Recipe] = Table7[[#This Row],[Recipe]])) &amp; " 
 }"</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AP28" s="15" t="e" cm="1">
+        <v>{ 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+}</v>
+      </c>
+      <c r="AP28" s="15" t="str" cm="1">
         <f t="array" ref="AP28">_xlfn.TEXTJOIN("
 ", TRUE, Table7[[#This Row],[Variable''s Name]] &amp; "." &amp; Table7[[#Headers],[name]:[energy_required]] &amp; " = " &amp; Table7[[#This Row],[name]:[energy_required]]) &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".ingredients = " &amp; Table7[[#This Row],[Ingredient String]] &amp; "
 " &amp; Table7[[#This Row],[Variable''s Name]] &amp; ".results = " &amp; Table7[[#This Row],[Results String]]</f>
-        <v>#REF!</v>
+        <v>fulgoran_special_crushing.name = "astra-fulgoran-special-crushing"
+fulgoran_special_crushing.icon = "__Astra-Asteroids__/graphics/fulgora_crushing_basic.png"
+fulgoran_special_crushing.order = "k[fulgora].z[special]"
+fulgoran_special_crushing.enabled = false
+fulgoran_special_crushing.energy_required = 10
+fulgoran_special_crushing.ingredients = { { type = "item", name = "astra-fulgoran-asteroid-chunk", amount = 1 }, { type = "item", name = "carbonic-asteroid-chunk", amount = 1 } }
+fulgoran_special_crushing.results = { 
+    { type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 }, 
+    { type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 } 
+}</v>
       </c>
     </row>
     <row r="32" spans="3:42">
@@ -26460,17 +26622,17 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C8:E28 AP8:AP28 F13:AE13 AF13:AM15 F14:Y14 AA14:AE14 F15:AE15 F16:AM18 E19:Y19 AE19:AM19 F20:AM27 F8:AM12">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>LEN($D8) &gt; 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>LEN($D28) &gt; 0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>LEN($D28) &gt; 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26483,7 +26645,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0CAC3E1-19B2-497F-BF02-30D86B7FD830}">
-  <dimension ref="B3:K59"/>
+  <dimension ref="B3:L59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3.75" customWidth="1"/>
@@ -26491,6 +26653,7 @@
     <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.375" bestFit="1" customWidth="1"/>
     <col min="5" max="10" width="10.375" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
     <col min="15" max="15" width="31.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.375" bestFit="1" customWidth="1"/>
@@ -26524,7 +26687,7 @@
     <col min="47" max="47" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" s="14" customFormat="1" ht="54" customHeight="1">
+    <row r="3" spans="2:12" s="14" customFormat="1" ht="54" customHeight="1">
       <c r="B3" s="15" t="s">
         <v>23</v>
       </c>
@@ -26555,8 +26718,11 @@
       <c r="K3" s="15" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="4" spans="2:11">
+      <c r="L3" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
       <c r="B4" s="2" t="s">
         <v>102</v>
       </c>
@@ -26591,8 +26757,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="5" spans="2:11">
+      <c r="L4" s="25" t="str" cm="1">
+        <f t="array" ref="L4">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "ice", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="B5" s="2" t="s">
         <v>102</v>
       </c>
@@ -26627,8 +26801,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="2:11">
+      <c r="L5" s="25" t="str" cm="1">
+        <f t="array" ref="L5">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
       <c r="B6" s="2" t="s">
         <v>351</v>
       </c>
@@ -26663,8 +26845,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.1</v>
       </c>
-    </row>
-    <row r="7" spans="2:11">
+      <c r="L6" s="25" t="str" cm="1">
+        <f t="array" ref="L6">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "iron-ore", amount_min = 20, amount_max = 20, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
       <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
@@ -26699,8 +26889,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="2:11">
+      <c r="L7" s="25" t="str" cm="1">
+        <f t="array" ref="L7">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="B8" s="2" t="s">
         <v>49</v>
       </c>
@@ -26735,8 +26933,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="9" spans="2:11">
+      <c r="L8" s="25" t="str" cm="1">
+        <f t="array" ref="L8">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-oilstone", amount_min = 4, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
       <c r="B9" s="2" t="s">
         <v>49</v>
       </c>
@@ -26771,8 +26977,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="10" spans="2:11">
+      <c r="L9" s="25" t="str" cm="1">
+        <f t="array" ref="L9">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
       <c r="B10" s="2" t="s">
         <v>352</v>
       </c>
@@ -26807,8 +27021,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="11" spans="2:11">
+      <c r="L10" s="25" t="str" cm="1">
+        <f t="array" ref="L10">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "carbon", amount_min = 10, amount_max = 10, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
       <c r="B11" s="2" t="s">
         <v>50</v>
       </c>
@@ -26843,8 +27065,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="2:11">
+      <c r="L11" s="25" t="str" cm="1">
+        <f t="array" ref="L11">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
       <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
@@ -26879,8 +27109,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="13" spans="2:11">
+      <c r="L12" s="25" t="str" cm="1">
+        <f t="array" ref="L12">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
       <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
@@ -26915,8 +27153,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="14" spans="2:11">
+      <c r="L13" s="25" t="str" cm="1">
+        <f t="array" ref="L13">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "tungsten-ore", amount_min = 4, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
@@ -26951,8 +27197,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="2:11">
+      <c r="L14" s="25" t="str" cm="1">
+        <f t="array" ref="L14">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
@@ -26987,8 +27241,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="16" spans="2:11">
+      <c r="L15" s="25" t="str" cm="1">
+        <f t="array" ref="L15">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
       <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
@@ -27023,8 +27285,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.18181818181818182</v>
       </c>
-    </row>
-    <row r="17" spans="2:11">
+      <c r="L16" s="25" t="str" cm="1">
+        <f t="array" ref="L16">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "uranium-ore", amount_min = 10, amount_max = 12, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
       <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
@@ -27059,8 +27329,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="2:11">
+      <c r="L17" s="25" t="str" cm="1">
+        <f t="array" ref="L17">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
       <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
@@ -27095,8 +27373,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="2:11">
+      <c r="L18" s="25" t="str" cm="1">
+        <f t="array" ref="L18">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 1, probability = 0.1 }</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
       <c r="B19" s="2" t="s">
         <v>52</v>
       </c>
@@ -27131,8 +27417,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.26666666666666666</v>
       </c>
-    </row>
-    <row r="20" spans="2:11">
+      <c r="L19" s="25" t="str" cm="1">
+        <f t="array" ref="L19">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "spoilage", amount_min = 5, amount_max = 10, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
       <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
@@ -27167,8 +27461,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="21" spans="2:11">
+      <c r="L20" s="25" t="str" cm="1">
+        <f t="array" ref="L20">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
       <c r="B21" s="2" t="s">
         <v>52</v>
       </c>
@@ -27203,8 +27505,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="2:11">
+      <c r="L21" s="25" t="str" cm="1">
+        <f t="array" ref="L21">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "yumako-seed", amount_min = 1, amount_max = 1, probability = 0.1 }</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
@@ -27239,8 +27549,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="2:11">
+      <c r="L22" s="25" t="str" cm="1">
+        <f t="array" ref="L22">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
@@ -27275,8 +27593,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.26666666666666666</v>
       </c>
-    </row>
-    <row r="24" spans="2:11">
+      <c r="L23" s="25" t="str" cm="1">
+        <f t="array" ref="L23">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "scrap", amount_min = 5, amount_max = 10, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
       <c r="B24" s="2" t="s">
         <v>51</v>
       </c>
@@ -27311,8 +27637,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:11">
+      <c r="L24" s="25" t="str" cm="1">
+        <f t="array" ref="L24">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
       <c r="B25" s="2" t="s">
         <v>340</v>
       </c>
@@ -27347,8 +27681,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="2:11">
+      <c r="L25" s="25" t="str" cm="1">
+        <f t="array" ref="L25">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-aquilo-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.2 }</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
       <c r="B26" s="2" t="s">
         <v>340</v>
       </c>
@@ -27383,8 +27725,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.5714285714285714</v>
       </c>
-    </row>
-    <row r="27" spans="2:11">
+      <c r="L26" s="25" t="str" cm="1">
+        <f t="array" ref="L26">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "lithium", amount_min = 2, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" s="2" t="s">
         <v>340</v>
       </c>
@@ -27419,8 +27769,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="28" spans="2:11">
+      <c r="L27" s="25" t="str" cm="1">
+        <f t="array" ref="L27">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
       <c r="B28" s="2" t="s">
         <v>105</v>
       </c>
@@ -27455,8 +27813,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>2.5</v>
       </c>
-    </row>
-    <row r="29" spans="2:11">
+      <c r="L28" s="25" t="str" cm="1">
+        <f t="array" ref="L28">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "calcite", amount_min = 2, amount_max = 2, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
       <c r="B29" s="2" t="s">
         <v>105</v>
       </c>
@@ -27491,8 +27857,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>1.6666666666666667</v>
       </c>
-    </row>
-    <row r="30" spans="2:11">
+      <c r="L29" s="25" t="str" cm="1">
+        <f t="array" ref="L29">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "ice", amount_min = 3, amount_max = 3, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
       <c r="B30" s="2" t="s">
         <v>105</v>
       </c>
@@ -27527,8 +27901,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="2:11">
+      <c r="L30" s="25" t="str" cm="1">
+        <f t="array" ref="L30">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "oxide-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
       <c r="B31" s="2" t="s">
         <v>103</v>
       </c>
@@ -27563,8 +27945,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>1.25</v>
       </c>
-    </row>
-    <row r="32" spans="2:11">
+      <c r="L31" s="25" t="str" cm="1">
+        <f t="array" ref="L31">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "copper-ore", amount_min = 4, amount_max = 4, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
       <c r="B32" s="2" t="s">
         <v>103</v>
       </c>
@@ -27599,8 +27989,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="33" spans="2:11">
+      <c r="L32" s="25" t="str" cm="1">
+        <f t="array" ref="L32">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "iron-ore", amount_min = 10, amount_max = 10, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
       <c r="B33" s="2" t="s">
         <v>103</v>
       </c>
@@ -27635,8 +28033,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:11">
+      <c r="L33" s="25" t="str" cm="1">
+        <f t="array" ref="L33">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "metallic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
       <c r="B34" s="2" t="s">
         <v>104</v>
       </c>
@@ -27671,8 +28077,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="2:11">
+      <c r="L34" s="25" t="str" cm="1">
+        <f t="array" ref="L34">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "carbon", amount_min = 5, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
       <c r="B35" s="2" t="s">
         <v>104</v>
       </c>
@@ -27707,8 +28121,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="2:11">
+      <c r="L35" s="25" t="str" cm="1">
+        <f t="array" ref="L35">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "carbonic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
       <c r="B36" s="2" t="s">
         <v>104</v>
       </c>
@@ -27743,8 +28165,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>2.5</v>
       </c>
-    </row>
-    <row r="37" spans="2:11">
+      <c r="L36" s="25" t="str" cm="1">
+        <f t="array" ref="L36">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "sulfur", amount_min = 2, amount_max = 2, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
       <c r="B37" s="2" t="s">
         <v>160</v>
       </c>
@@ -27779,8 +28209,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="2:11">
+      <c r="L37" s="25" t="str" cm="1">
+        <f t="array" ref="L37">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-vulcanic-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
       <c r="B38" s="2" t="s">
         <v>160</v>
       </c>
@@ -27815,8 +28253,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="2:11">
+      <c r="L38" s="25" t="str" cm="1">
+        <f t="array" ref="L38">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
       <c r="B39" s="2" t="s">
         <v>160</v>
       </c>
@@ -27851,8 +28297,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="40" spans="2:11">
+      <c r="L39" s="25" t="str" cm="1">
+        <f t="array" ref="L39">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "tungsten-ore", amount_min = 10, amount_max = 14, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
       <c r="B40" s="2" t="s">
         <v>46</v>
       </c>
@@ -27887,8 +28341,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="2:11">
+      <c r="L40" s="25" t="str" cm="1">
+        <f t="array" ref="L40">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-nauvis-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
       <c r="B41" s="2" t="s">
         <v>46</v>
       </c>
@@ -27923,8 +28385,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:11">
+      <c r="L41" s="25" t="str" cm="1">
+        <f t="array" ref="L41">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
       <c r="B42" s="2" t="s">
         <v>46</v>
       </c>
@@ -27959,8 +28429,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>16.666666666666668</v>
       </c>
-    </row>
-    <row r="43" spans="2:11">
+      <c r="L42" s="25" t="str" cm="1">
+        <f t="array" ref="L42">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "uranium-235", amount_min = 1, amount_max = 1, probability = 0.3 }</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
       <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
@@ -27995,8 +28473,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>1.25</v>
       </c>
-    </row>
-    <row r="44" spans="2:11">
+      <c r="L43" s="25" t="str" cm="1">
+        <f t="array" ref="L43">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "uranium-238", amount_min = 3, amount_max = 5, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
       <c r="B44" s="2" t="s">
         <v>161</v>
       </c>
@@ -28031,8 +28517,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:11">
+      <c r="L44" s="25" t="str" cm="1">
+        <f t="array" ref="L44">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-gleba-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
       <c r="B45" s="2" t="s">
         <v>161</v>
       </c>
@@ -28067,8 +28561,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>11.111111111111111</v>
       </c>
-    </row>
-    <row r="46" spans="2:11">
+      <c r="L45" s="25" t="str" cm="1">
+        <f t="array" ref="L45">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "jellynut-seed", amount_min = 1, amount_max = 2, probability = 0.3 }</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
       <c r="B46" s="2" t="s">
         <v>161</v>
       </c>
@@ -28103,8 +28605,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="47" spans="2:11">
+      <c r="L46" s="25" t="str" cm="1">
+        <f t="array" ref="L46">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "spoilage", amount_min = 10, amount_max = 20, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
       <c r="B47" s="2" t="s">
         <v>161</v>
       </c>
@@ -28139,8 +28649,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>11.111111111111111</v>
       </c>
-    </row>
-    <row r="48" spans="2:11">
+      <c r="L47" s="25" t="str" cm="1">
+        <f t="array" ref="L47">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "yumako-seed", amount_min = 1, amount_max = 2, probability = 0.3 }</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
       <c r="B48" s="2" t="s">
         <v>162</v>
       </c>
@@ -28175,8 +28693,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="2:11">
+      <c r="L48" s="25" t="str" cm="1">
+        <f t="array" ref="L48">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-fulgoran-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12">
       <c r="B49" s="2" t="s">
         <v>162</v>
       </c>
@@ -28211,8 +28737,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>8.3333333333333321</v>
       </c>
-    </row>
-    <row r="50" spans="2:11">
+      <c r="L49" s="25" t="str" cm="1">
+        <f t="array" ref="L49">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "holmium-ore", amount_min = 1, amount_max = 2, probability = 0.4 }</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12">
       <c r="B50" s="2" t="s">
         <v>162</v>
       </c>
@@ -28247,8 +28781,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="51" spans="2:11">
+      <c r="L50" s="25" t="str" cm="1">
+        <f t="array" ref="L50">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "scrap", amount_min = 10, amount_max = 15, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12">
       <c r="B51" s="2" t="s">
         <v>162</v>
       </c>
@@ -28283,8 +28825,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="2:11">
+      <c r="L51" s="25" t="str" cm="1">
+        <f t="array" ref="L51">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 0, amount_max = 0, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12">
       <c r="B52" s="2" t="s">
         <v>233</v>
       </c>
@@ -28319,8 +28869,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="2:11">
+      <c r="L52" s="25" t="str" cm="1">
+        <f t="array" ref="L52">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-crude-asteroid-chunk", amount_min = 1, amount_max = 1, probability = 0.05 }</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12">
       <c r="B53" s="2" t="s">
         <v>233</v>
       </c>
@@ -28355,8 +28913,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.76923076923076916</v>
       </c>
-    </row>
-    <row r="54" spans="2:11">
+      <c r="L53" s="25" t="str" cm="1">
+        <f t="array" ref="L53">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "astra-oilstone", amount_min = 5, amount_max = 8, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12">
       <c r="B54" s="2" t="s">
         <v>233</v>
       </c>
@@ -28391,8 +28957,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.76923076923076916</v>
       </c>
-    </row>
-    <row r="55" spans="2:11">
+      <c r="L54" s="25" t="str" cm="1">
+        <f t="array" ref="L54">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "coal", amount_min = 5, amount_max = 8, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12">
       <c r="B55" s="2" t="s">
         <v>166</v>
       </c>
@@ -28427,8 +29001,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>2.5000000000000001E-3</v>
       </c>
-    </row>
-    <row r="56" spans="2:11">
+      <c r="L55" s="25" t="str" cm="1">
+        <f t="array" ref="L55">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "fluid", name = "lava", amount_min = 2000, amount_max = 2000, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12">
       <c r="B56" s="2" t="s">
         <v>166</v>
       </c>
@@ -28463,8 +29045,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="57" spans="2:11">
+      <c r="L56" s="25" t="str" cm="1">
+        <f t="array" ref="L56">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "tungsten-ore", amount_min = 12, amount_max = 12, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12">
       <c r="B57" s="2" t="s">
         <v>164</v>
       </c>
@@ -28499,8 +29089,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="2:11">
+      <c r="L57" s="25" t="str" cm="1">
+        <f t="array" ref="L57">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "fluid", name = "heavy-oil", amount_min = 20, amount_max = 20, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12">
       <c r="B58" s="2" t="s">
         <v>164</v>
       </c>
@@ -28535,8 +29133,16 @@
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="59" spans="2:11">
+      <c r="L58" s="25" t="str" cm="1">
+        <f t="array" ref="L58">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "fluid", name = "holmium-solution", amount_min = 20, amount_max = 20, probability = 1 }</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12">
       <c r="B59" s="2" t="s">
         <v>164</v>
       </c>
@@ -28570,6 +29176,14 @@
       <c r="K59" s="2">
         <f>IFERROR(1/Table8[[#This Row],[EV/s]], 0)</f>
         <v>2</v>
+      </c>
+      <c r="L59" s="25" t="str" cm="1">
+        <f t="array" ref="L59">"{ " &amp;
+_xlfn.TEXTJOIN(", ",
+          TRUE,
+          {"type","name","amount_min","amount_max","probability"} &amp; " = " &amp; IF(NOT(ISNUMBER(Table8[[#This Row],[type]:[P]])), """" &amp; Table8[[#This Row],[type]:[P]] &amp; """", Table8[[#This Row],[type]:[P]]) ) &amp;
+" }"</f>
+        <v>{ type = "item", name = "stone", amount_min = 5, amount_max = 5, probability = 1 }</v>
       </c>
     </row>
   </sheetData>
